--- a/Extra Data for project/Questions files/Questions Full Data.xlsx
+++ b/Extra Data for project/Questions files/Questions Full Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F680BE-E173-40F0-BBCA-5BDB7C150B00}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0763913C-6D17-488B-885D-AF1AC15F4F1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{669F632A-8C17-464B-B497-7F400C39EC04}"/>
   </bookViews>
@@ -256,9 +256,6 @@
   </si>
   <si>
     <t>الالتزام اليومي ضروري للحفاظ على نتائج 5S.</t>
-  </si>
-  <si>
-    <t>Safty</t>
   </si>
   <si>
     <t xml:space="preserve">mcq </t>
@@ -745,6 +742,9 @@
   </si>
   <si>
     <t>ما هي الجهة المختصه بتحديد نسبة خصم المنتجات؟</t>
+  </si>
+  <si>
+    <t>Safety</t>
   </si>
 </sst>
 </file>
@@ -1294,31 +1294,31 @@
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>165</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -1931,25 +1931,25 @@
         <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="D27" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="E27" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="F27" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="G27" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="H27" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="H27" s="5" t="s">
-        <v>82</v>
       </c>
       <c r="I27" s="5" t="s">
         <v>13</v>
@@ -1960,25 +1960,25 @@
         <v>27</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D28" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="F28" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="G28" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="H28" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="H28" s="5" t="s">
-        <v>87</v>
       </c>
       <c r="I28" s="5" t="s">
         <v>13</v>
@@ -1989,25 +1989,25 @@
         <v>28</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C29" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D29" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="F29" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="G29" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="H29" s="5" t="s">
         <v>91</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>92</v>
       </c>
       <c r="I29" s="5" t="s">
         <v>7</v>
@@ -2018,25 +2018,25 @@
         <v>29</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C30" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D30" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E30" s="5" t="s">
+      <c r="F30" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="F30" s="5" t="s">
+      <c r="G30" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="H30" s="5" t="s">
         <v>96</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>97</v>
       </c>
       <c r="I30" s="5" t="s">
         <v>13</v>
@@ -2047,25 +2047,25 @@
         <v>30</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C31" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D31" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="F31" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="F31" s="5" t="s">
+      <c r="G31" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="G31" s="5" t="s">
+      <c r="H31" s="5" t="s">
         <v>101</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>102</v>
       </c>
       <c r="I31" s="5" t="s">
         <v>13</v>
@@ -2076,25 +2076,25 @@
         <v>31</v>
       </c>
       <c r="B32" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C32" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C32" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D32" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="E32" s="5" t="s">
+      <c r="F32" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F32" s="5" t="s">
+      <c r="G32" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="H32" s="5" t="s">
         <v>106</v>
-      </c>
-      <c r="H32" s="5" t="s">
-        <v>107</v>
       </c>
       <c r="I32" s="5" t="s">
         <v>7</v>
@@ -2105,25 +2105,25 @@
         <v>32</v>
       </c>
       <c r="B33" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D33" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="E33" s="5" t="s">
+      <c r="F33" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F33" s="5" t="s">
+      <c r="G33" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="G33" s="5" t="s">
+      <c r="H33" s="5" t="s">
         <v>111</v>
-      </c>
-      <c r="H33" s="5" t="s">
-        <v>112</v>
       </c>
       <c r="I33" s="5" t="s">
         <v>13</v>
@@ -2134,25 +2134,25 @@
         <v>33</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D34" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="F34" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="G34" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="H34" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="H34" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="I34" s="5" t="s">
         <v>13</v>
@@ -2163,25 +2163,25 @@
         <v>34</v>
       </c>
       <c r="B35" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D35" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="E35" s="5" t="s">
+      <c r="F35" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="F35" s="5" t="s">
+      <c r="G35" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="G35" s="5" t="s">
+      <c r="H35" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>122</v>
       </c>
       <c r="I35" s="5" t="s">
         <v>7</v>
@@ -2192,13 +2192,13 @@
         <v>35</v>
       </c>
       <c r="B36" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D36" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>7</v>
@@ -2207,10 +2207,10 @@
         <v>13</v>
       </c>
       <c r="G36" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="H36" s="5" t="s">
         <v>124</v>
-      </c>
-      <c r="H36" s="5" t="s">
-        <v>125</v>
       </c>
       <c r="I36" s="5" t="s">
         <v>13</v>
@@ -2221,25 +2221,25 @@
         <v>36</v>
       </c>
       <c r="B37" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D37" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="F37" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="G37" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="H37" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="H37" s="5" t="s">
-        <v>130</v>
       </c>
       <c r="I37" s="5" t="s">
         <v>7</v>
@@ -2250,25 +2250,25 @@
         <v>37</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C38" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D38" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="F38" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="G38" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="H38" s="5" t="s">
         <v>134</v>
-      </c>
-      <c r="H38" s="5" t="s">
-        <v>135</v>
       </c>
       <c r="I38" s="5" t="s">
         <v>13</v>
@@ -2279,25 +2279,25 @@
         <v>38</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C39" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="E39" s="5" t="s">
+      <c r="F39" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="F39" s="5" t="s">
+      <c r="G39" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G39" s="5" t="s">
+      <c r="H39" s="5" t="s">
         <v>139</v>
-      </c>
-      <c r="H39" s="5" t="s">
-        <v>140</v>
       </c>
       <c r="I39" s="5" t="s">
         <v>7</v>
@@ -2308,25 +2308,25 @@
         <v>39</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D40" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F40" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="F40" s="5" t="s">
+      <c r="G40" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="5" t="s">
         <v>142</v>
-      </c>
-      <c r="G40" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>143</v>
       </c>
       <c r="I40" s="5" t="s">
         <v>13</v>
@@ -2337,22 +2337,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C41" s="5" t="s">
-        <v>77</v>
-      </c>
       <c r="D41" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="E41" s="5" t="s">
+      <c r="F41" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="F41" s="5" t="s">
+      <c r="G41" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="G41" s="5" t="s">
-        <v>147</v>
       </c>
       <c r="H41" s="5" t="s">
         <v>12</v>
@@ -2366,13 +2366,13 @@
         <v>41</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C42" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
@@ -2387,13 +2387,13 @@
         <v>42</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C43" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -2408,13 +2408,13 @@
         <v>43</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C44" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
@@ -2429,13 +2429,13 @@
         <v>44</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C45" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
@@ -2450,13 +2450,13 @@
         <v>45</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C46" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
@@ -2471,13 +2471,13 @@
         <v>46</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C47" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
@@ -2492,13 +2492,13 @@
         <v>47</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C48" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
@@ -2513,13 +2513,13 @@
         <v>48</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C49" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
@@ -2534,13 +2534,13 @@
         <v>49</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C50" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
@@ -2555,13 +2555,13 @@
         <v>50</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>76</v>
+        <v>213</v>
       </c>
       <c r="C51" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
@@ -2576,25 +2576,25 @@
         <v>51</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C52" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="C52" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="F52" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="G52" s="6" t="s">
+      <c r="H52" s="6" t="s">
         <v>171</v>
-      </c>
-      <c r="H52" s="6" t="s">
-        <v>172</v>
       </c>
       <c r="I52" s="3" t="s">
         <v>13</v>
@@ -2605,28 +2605,28 @@
         <v>52</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D53" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="G53" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="G53" s="6" t="s">
+      <c r="H53" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="H53" s="6" t="s">
-        <v>177</v>
-      </c>
       <c r="I53" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
@@ -2634,25 +2634,25 @@
         <v>53</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D54" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E54" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="F54" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F54" s="6" t="s">
+      <c r="G54" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G54" s="6" t="s">
+      <c r="H54" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I54" s="3" t="s">
         <v>7</v>
@@ -2663,13 +2663,13 @@
         <v>54</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E55" s="7">
         <v>16</v>
@@ -2684,7 +2684,7 @@
         <v>10</v>
       </c>
       <c r="I55" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="42.75" x14ac:dyDescent="0.25">
@@ -2692,25 +2692,25 @@
         <v>55</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D56" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E56" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="F56" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F56" s="6" t="s">
+      <c r="G56" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="G56" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>187</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>188</v>
       </c>
       <c r="I56" s="3" t="s">
         <v>7</v>
@@ -2721,13 +2721,13 @@
         <v>56</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E57" s="9">
         <v>0.1</v>
@@ -2750,25 +2750,25 @@
         <v>57</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="E58" s="4" t="s">
+      <c r="F58" s="4" t="s">
         <v>191</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="G58" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="G58" s="4" t="s">
+      <c r="H58" s="4" t="s">
         <v>193</v>
-      </c>
-      <c r="H58" s="4" t="s">
-        <v>194</v>
       </c>
       <c r="I58" s="4" t="s">
         <v>13</v>
@@ -2779,13 +2779,13 @@
         <v>58</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
@@ -2800,13 +2800,13 @@
         <v>59</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C60" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
@@ -2821,25 +2821,25 @@
         <v>60</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="E61" s="4" t="s">
+      <c r="F61" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="G61" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="G61" s="4" t="s">
+      <c r="H61" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="I61" s="4" t="s">
         <v>13</v>
@@ -2850,13 +2850,13 @@
         <v>61</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E62" s="9">
         <v>0.3</v>
@@ -2871,7 +2871,7 @@
         <v>0.45</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="71.25" x14ac:dyDescent="0.25">
@@ -2879,28 +2879,28 @@
         <v>62</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D63" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E63" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="F63" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="F63" s="6" t="s">
+      <c r="G63" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="G63" s="6" t="s">
+      <c r="H63" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="H63" s="6" t="s">
-        <v>207</v>
-      </c>
       <c r="I63" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
@@ -2908,25 +2908,25 @@
         <v>63</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D64" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="E64" s="11" t="s">
         <v>208</v>
       </c>
-      <c r="E64" s="11" t="s">
+      <c r="F64" s="11" t="s">
         <v>209</v>
       </c>
-      <c r="F64" s="11" t="s">
+      <c r="G64" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G64" s="11" t="s">
+      <c r="H64" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="H64" s="11" t="s">
-        <v>212</v>
       </c>
       <c r="I64" s="5" t="s">
         <v>7</v>
@@ -2937,28 +2937,28 @@
         <v>64</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>1</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F65" s="11" t="s">
+        <v>209</v>
+      </c>
+      <c r="G65" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="G65" s="11" t="s">
-        <v>211</v>
-      </c>
       <c r="H65" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">

--- a/Extra Data for project/Questions files/Questions Full Data.xlsx
+++ b/Extra Data for project/Questions files/Questions Full Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0763913C-6D17-488B-885D-AF1AC15F4F1B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91D5186A-4D10-4DD8-9C66-DE376E25040E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{669F632A-8C17-464B-B497-7F400C39EC04}"/>
   </bookViews>

--- a/Extra Data for project/Questions files/Questions Full Data.xlsx
+++ b/Extra Data for project/Questions files/Questions Full Data.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E8011E-B746-437B-AD85-28FB090198B5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E753807-C38A-4809-98F1-34B4F8406390}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{669F632A-8C17-464B-B497-7F400C39EC04}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$I$1</definedName>
@@ -2628,25 +2627,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -2679,13 +2666,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <color theme="1"/>
@@ -2700,42 +2680,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor theme="4" tint="0.79998168889431442"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="22">
@@ -3011,287 +2961,157 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3774,5922 +3594,5922 @@
   <dimension ref="A1:I225"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="58"/>
-    <col min="2" max="2" width="19.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.140625" style="58"/>
-    <col min="4" max="4" width="52.85546875" style="58" customWidth="1"/>
-    <col min="5" max="5" width="84.28515625" style="58" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.5703125" style="58" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" style="58" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.7109375" style="58" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" style="58" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="58"/>
+    <col min="1" max="1" width="9.140625" style="18"/>
+    <col min="2" max="2" width="19.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" style="18"/>
+    <col min="4" max="4" width="52.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="84.28515625" style="18" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.5703125" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.140625" style="18" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.7109375" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" style="18" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="18"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="F1" s="58" t="s">
+      <c r="F1" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="G1" s="58" t="s">
+      <c r="G1" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="H1" s="58" t="s">
+      <c r="H1" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="I1" s="58" t="s">
+      <c r="I1" s="18" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="58">
-        <v>1</v>
-      </c>
-      <c r="B2" s="58" t="s">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="58" t="s">
+      <c r="C2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="58" t="s">
+      <c r="G2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="58" t="s">
+      <c r="H2" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="58" t="s">
+      <c r="I2" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" s="58">
+      <c r="A3" s="18">
         <v>2</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="58" t="s">
+      <c r="C3" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="58" t="s">
+      <c r="G3" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="H3" s="58" t="s">
+      <c r="H3" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="58" t="s">
+      <c r="I3" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="58">
+      <c r="A4" s="18">
         <v>3</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="58" t="s">
+      <c r="C4" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G4" s="58" t="s">
+      <c r="G4" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="58" t="s">
+      <c r="H4" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="58" t="s">
+      <c r="I4" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="58">
+      <c r="A5" s="18">
         <v>4</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C5" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" s="58" t="s">
+      <c r="C5" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="G5" s="58" t="s">
+      <c r="G5" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="58" t="s">
+      <c r="H5" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="I5" s="58" t="s">
+      <c r="I5" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="58">
+      <c r="A6" s="18">
         <v>5</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="58" t="s">
+      <c r="C6" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D6" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G6" s="58" t="s">
+      <c r="G6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="58" t="s">
+      <c r="H6" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="58" t="s">
+      <c r="I6" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="58">
+      <c r="A7" s="18">
         <v>6</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="58" t="s">
+      <c r="C7" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="58" t="s">
+      <c r="G7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="58" t="s">
+      <c r="H7" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="58" t="s">
+      <c r="I7" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8" s="58">
+      <c r="A8" s="18">
         <v>7</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="58" t="s">
+      <c r="C8" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G8" s="58" t="s">
+      <c r="G8" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="58" t="s">
+      <c r="H8" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I8" s="58" t="s">
+      <c r="I8" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="58">
+      <c r="A9" s="18">
         <v>8</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C9" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="58" t="s">
+      <c r="C9" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="58" t="s">
+      <c r="G9" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="I9" s="58" t="s">
+      <c r="I9" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="58">
+      <c r="A10" s="18">
         <v>9</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D10" s="58" t="s">
+      <c r="C10" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="H10" s="58" t="s">
+      <c r="H10" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I10" s="58" t="s">
+      <c r="I10" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="58">
+      <c r="A11" s="18">
         <v>10</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D11" s="58" t="s">
+      <c r="C11" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="G11" s="58" t="s">
+      <c r="G11" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="I11" s="58" t="s">
+      <c r="I11" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="58">
+      <c r="A12" s="18">
         <v>11</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D12" s="58" t="s">
+      <c r="C12" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="G12" s="58" t="s">
+      <c r="G12" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="I12" s="58" t="s">
+      <c r="I12" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="58">
+      <c r="A13" s="18">
         <v>12</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C13" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D13" s="58" t="s">
+      <c r="C13" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D13" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G13" s="58" t="s">
+      <c r="G13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="58" t="s">
+      <c r="I13" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14" s="58">
+      <c r="A14" s="18">
         <v>13</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D14" s="58" t="s">
+      <c r="C14" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D14" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="G14" s="58" t="s">
+      <c r="G14" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="H14" s="58" t="s">
+      <c r="H14" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="I14" s="58" t="s">
+      <c r="I14" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A15" s="58">
+      <c r="A15" s="18">
         <v>14</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D15" s="58" t="s">
+      <c r="C15" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="G15" s="58" t="s">
+      <c r="G15" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="I15" s="58" t="s">
+      <c r="I15" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="58">
+      <c r="A16" s="18">
         <v>15</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C16" s="58" t="s">
-        <v>1</v>
-      </c>
-      <c r="D16" s="58" t="s">
+      <c r="C16" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="D16" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="G16" s="58" t="s">
+      <c r="G16" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H16" s="58" t="s">
+      <c r="H16" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="I16" s="58" t="s">
+      <c r="I16" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="58">
+      <c r="A17" s="18">
         <v>16</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="I17" s="58">
+      <c r="I17" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="58">
+      <c r="A18" s="18">
         <v>17</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="I18" s="58">
+      <c r="I18" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="58">
+      <c r="A19" s="18">
         <v>18</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="I19" s="58">
+      <c r="I19" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="58">
+      <c r="A20" s="18">
         <v>19</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="I20" s="58">
+      <c r="I20" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="58">
+      <c r="A21" s="18">
         <v>20</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="58">
+      <c r="I21" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22" s="58">
+      <c r="A22" s="18">
         <v>21</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I22" s="58">
+      <c r="I22" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="58">
+      <c r="A23" s="18">
         <v>22</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="I23" s="58">
+      <c r="I23" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="58">
+      <c r="A24" s="18">
         <v>23</v>
       </c>
-      <c r="B24" s="58" t="s">
+      <c r="B24" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="58" t="s">
+      <c r="C24" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D24" s="58" t="s">
+      <c r="D24" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I24" s="58">
+      <c r="I24" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="58">
+      <c r="A25" s="18">
         <v>24</v>
       </c>
-      <c r="B25" s="58" t="s">
+      <c r="B25" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D25" s="58" t="s">
+      <c r="D25" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="I25" s="58">
+      <c r="I25" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="58">
+      <c r="A26" s="18">
         <v>25</v>
       </c>
-      <c r="B26" s="58" t="s">
+      <c r="B26" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C26" s="58" t="s">
+      <c r="C26" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D26" s="58" t="s">
+      <c r="D26" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="I26" s="58">
+      <c r="I26" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="58">
+      <c r="A27" s="18">
         <v>26</v>
       </c>
-      <c r="B27" s="59" t="s">
+      <c r="B27" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D27" s="58" t="s">
+      <c r="D27" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="E27" s="58" t="s">
+      <c r="E27" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="F27" s="58" t="s">
+      <c r="F27" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="G27" s="58" t="s">
+      <c r="G27" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H27" s="58" t="s">
+      <c r="H27" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="I27" s="58" t="s">
+      <c r="I27" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28" s="58">
+      <c r="A28" s="18">
         <v>27</v>
       </c>
-      <c r="B28" s="59" t="s">
+      <c r="B28" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C28" s="58" t="s">
+      <c r="C28" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D28" s="58" t="s">
+      <c r="D28" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="E28" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="F28" s="58" t="s">
+      <c r="F28" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="G28" s="58" t="s">
+      <c r="G28" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="H28" s="58" t="s">
+      <c r="H28" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="I28" s="58" t="s">
+      <c r="I28" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="58">
+      <c r="A29" s="18">
         <v>28</v>
       </c>
-      <c r="B29" s="59" t="s">
+      <c r="B29" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C29" s="58" t="s">
+      <c r="C29" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D29" s="58" t="s">
+      <c r="D29" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E29" s="58" t="s">
+      <c r="E29" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="F29" s="58" t="s">
+      <c r="F29" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="G29" s="58" t="s">
+      <c r="G29" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="H29" s="58" t="s">
+      <c r="H29" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="I29" s="58" t="s">
+      <c r="I29" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="58">
+      <c r="A30" s="18">
         <v>29</v>
       </c>
-      <c r="B30" s="59" t="s">
+      <c r="B30" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C30" s="58" t="s">
+      <c r="C30" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D30" s="58" t="s">
+      <c r="D30" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="E30" s="58" t="s">
+      <c r="E30" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="F30" s="58" t="s">
+      <c r="F30" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="G30" s="58" t="s">
+      <c r="G30" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="H30" s="58" t="s">
+      <c r="H30" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="I30" s="58" t="s">
+      <c r="I30" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="58">
+      <c r="A31" s="18">
         <v>30</v>
       </c>
-      <c r="B31" s="59" t="s">
+      <c r="B31" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C31" s="58" t="s">
+      <c r="C31" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="58" t="s">
+      <c r="D31" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="E31" s="58" t="s">
+      <c r="E31" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="F31" s="58" t="s">
+      <c r="F31" s="18" t="s">
         <v>99</v>
       </c>
-      <c r="G31" s="58" t="s">
+      <c r="G31" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="H31" s="58" t="s">
+      <c r="H31" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="I31" s="58" t="s">
+      <c r="I31" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="58">
+      <c r="A32" s="18">
         <v>31</v>
       </c>
-      <c r="B32" s="59" t="s">
+      <c r="B32" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C32" s="58" t="s">
+      <c r="C32" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D32" s="58" t="s">
+      <c r="D32" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E32" s="58" t="s">
+      <c r="E32" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="F32" s="58" t="s">
+      <c r="F32" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="G32" s="58" t="s">
+      <c r="G32" s="18" t="s">
         <v>105</v>
       </c>
-      <c r="H32" s="58" t="s">
+      <c r="H32" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="I32" s="58" t="s">
+      <c r="I32" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="58">
+      <c r="A33" s="18">
         <v>32</v>
       </c>
-      <c r="B33" s="59" t="s">
+      <c r="B33" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C33" s="58" t="s">
+      <c r="C33" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="58" t="s">
+      <c r="D33" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="E33" s="58" t="s">
+      <c r="E33" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F33" s="58" t="s">
+      <c r="F33" s="18" t="s">
         <v>109</v>
       </c>
-      <c r="G33" s="58" t="s">
+      <c r="G33" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="H33" s="58" t="s">
+      <c r="H33" s="18" t="s">
         <v>111</v>
       </c>
-      <c r="I33" s="58" t="s">
+      <c r="I33" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="58">
+      <c r="A34" s="18">
         <v>33</v>
       </c>
-      <c r="B34" s="59" t="s">
+      <c r="B34" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="58" t="s">
+      <c r="C34" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D34" s="58" t="s">
+      <c r="D34" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="E34" s="58" t="s">
+      <c r="E34" s="18" t="s">
         <v>113</v>
       </c>
-      <c r="F34" s="58" t="s">
+      <c r="F34" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="G34" s="58" t="s">
+      <c r="G34" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="H34" s="58" t="s">
+      <c r="H34" s="18" t="s">
         <v>116</v>
       </c>
-      <c r="I34" s="58" t="s">
+      <c r="I34" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="58">
+      <c r="A35" s="18">
         <v>34</v>
       </c>
-      <c r="B35" s="59" t="s">
+      <c r="B35" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C35" s="58" t="s">
+      <c r="C35" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D35" s="58" t="s">
+      <c r="D35" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="58" t="s">
+      <c r="E35" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="F35" s="58" t="s">
+      <c r="F35" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="G35" s="58" t="s">
+      <c r="G35" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="H35" s="58" t="s">
+      <c r="H35" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="I35" s="58" t="s">
+      <c r="I35" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="58">
+      <c r="A36" s="18">
         <v>35</v>
       </c>
-      <c r="B36" s="59" t="s">
+      <c r="B36" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C36" s="58" t="s">
+      <c r="C36" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D36" s="58" t="s">
+      <c r="D36" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="E36" s="58" t="s">
+      <c r="E36" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F36" s="58" t="s">
+      <c r="F36" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="58" t="s">
+      <c r="G36" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="H36" s="58" t="s">
+      <c r="H36" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="I36" s="58" t="s">
+      <c r="I36" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="58">
+      <c r="A37" s="18">
         <v>36</v>
       </c>
-      <c r="B37" s="59" t="s">
+      <c r="B37" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C37" s="58" t="s">
+      <c r="C37" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D37" s="58" t="s">
+      <c r="D37" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="E37" s="58" t="s">
+      <c r="E37" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F37" s="58" t="s">
+      <c r="F37" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G37" s="58" t="s">
+      <c r="G37" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H37" s="58" t="s">
+      <c r="H37" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="I37" s="58" t="s">
+      <c r="I37" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38" s="58">
+      <c r="A38" s="18">
         <v>37</v>
       </c>
-      <c r="B38" s="59" t="s">
+      <c r="B38" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C38" s="58" t="s">
+      <c r="C38" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="58" t="s">
+      <c r="D38" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="E38" s="58" t="s">
+      <c r="E38" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="F38" s="58" t="s">
+      <c r="F38" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="G38" s="58" t="s">
+      <c r="G38" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="H38" s="58" t="s">
+      <c r="H38" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="I38" s="58" t="s">
+      <c r="I38" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A39" s="58">
+      <c r="A39" s="18">
         <v>38</v>
       </c>
-      <c r="B39" s="59" t="s">
+      <c r="B39" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C39" s="58" t="s">
+      <c r="C39" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D39" s="58" t="s">
+      <c r="D39" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="E39" s="58" t="s">
+      <c r="E39" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="F39" s="58" t="s">
+      <c r="F39" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="G39" s="58" t="s">
+      <c r="G39" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="H39" s="58" t="s">
+      <c r="H39" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="I39" s="58" t="s">
+      <c r="I39" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40" s="58">
+      <c r="A40" s="18">
         <v>39</v>
       </c>
-      <c r="B40" s="59" t="s">
+      <c r="B40" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C40" s="58" t="s">
+      <c r="C40" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D40" s="58" t="s">
+      <c r="D40" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="E40" s="58" t="s">
+      <c r="E40" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="F40" s="58" t="s">
+      <c r="F40" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="G40" s="58" t="s">
+      <c r="G40" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="58" t="s">
+      <c r="H40" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="I40" s="58" t="s">
+      <c r="I40" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A41" s="58">
+      <c r="A41" s="18">
         <v>40</v>
       </c>
-      <c r="B41" s="59" t="s">
+      <c r="B41" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C41" s="58" t="s">
+      <c r="C41" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D41" s="58" t="s">
+      <c r="D41" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E41" s="58" t="s">
+      <c r="E41" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F41" s="58" t="s">
+      <c r="F41" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="G41" s="58" t="s">
+      <c r="G41" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="H41" s="58" t="s">
+      <c r="H41" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="I41" s="58" t="s">
+      <c r="I41" s="18" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42" s="58">
+      <c r="A42" s="18">
         <v>41</v>
       </c>
-      <c r="B42" s="59" t="s">
+      <c r="B42" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C42" s="58" t="s">
+      <c r="C42" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D42" s="58" t="s">
+      <c r="D42" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="I42" s="58">
+      <c r="I42" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A43" s="58">
+      <c r="A43" s="18">
         <v>42</v>
       </c>
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C43" s="58" t="s">
+      <c r="C43" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D43" s="58" t="s">
+      <c r="D43" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="I43" s="58">
+      <c r="I43" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44" s="58">
+      <c r="A44" s="18">
         <v>43</v>
       </c>
-      <c r="B44" s="59" t="s">
+      <c r="B44" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C44" s="58" t="s">
+      <c r="C44" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D44" s="58" t="s">
+      <c r="D44" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="I44" s="58">
+      <c r="I44" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A45" s="58">
+      <c r="A45" s="18">
         <v>44</v>
       </c>
-      <c r="B45" s="59" t="s">
+      <c r="B45" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C45" s="58" t="s">
+      <c r="C45" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D45" s="58" t="s">
+      <c r="D45" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="I45" s="58">
+      <c r="I45" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46" s="58">
+      <c r="A46" s="18">
         <v>45</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C46" s="58" t="s">
+      <c r="C46" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D46" s="58" t="s">
+      <c r="D46" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="I46" s="58">
+      <c r="I46" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A47" s="58">
+      <c r="A47" s="18">
         <v>46</v>
       </c>
-      <c r="B47" s="59" t="s">
+      <c r="B47" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C47" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D47" s="58" t="s">
+      <c r="D47" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="I47" s="58">
+      <c r="I47" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48" s="58">
+      <c r="A48" s="18">
         <v>47</v>
       </c>
-      <c r="B48" s="59" t="s">
+      <c r="B48" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C48" s="58" t="s">
+      <c r="C48" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D48" s="58" t="s">
+      <c r="D48" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="I48" s="58">
+      <c r="I48" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A49" s="58">
+      <c r="A49" s="18">
         <v>48</v>
       </c>
-      <c r="B49" s="59" t="s">
+      <c r="B49" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C49" s="58" t="s">
+      <c r="C49" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D49" s="58" t="s">
+      <c r="D49" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="I49" s="58">
+      <c r="I49" s="18">
         <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50" s="58">
+      <c r="A50" s="18">
         <v>49</v>
       </c>
-      <c r="B50" s="59" t="s">
+      <c r="B50" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C50" s="58" t="s">
+      <c r="C50" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D50" s="58" t="s">
+      <c r="D50" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="I50" s="58">
+      <c r="I50" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A51" s="58">
+      <c r="A51" s="18">
         <v>50</v>
       </c>
-      <c r="B51" s="59" t="s">
+      <c r="B51" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C51" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D51" s="58" t="s">
+      <c r="D51" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="I51" s="58">
+      <c r="I51" s="18">
         <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="58">
+      <c r="A52" s="18">
         <v>51</v>
       </c>
-      <c r="B52" s="59" t="s">
+      <c r="B52" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C52" s="58" t="s">
+      <c r="C52" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D52" s="60" t="s">
+      <c r="D52" s="20" t="s">
         <v>167</v>
       </c>
-      <c r="E52" s="61" t="s">
+      <c r="E52" s="21" t="s">
         <v>168</v>
       </c>
-      <c r="F52" s="61" t="s">
+      <c r="F52" s="21" t="s">
         <v>169</v>
       </c>
-      <c r="G52" s="61" t="s">
+      <c r="G52" s="21" t="s">
         <v>170</v>
       </c>
-      <c r="H52" s="61" t="s">
+      <c r="H52" s="21" t="s">
         <v>171</v>
       </c>
-      <c r="I52" s="60" t="s">
+      <c r="I52" s="20" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="53" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A53" s="58">
+      <c r="A53" s="18">
         <v>52</v>
       </c>
-      <c r="B53" s="59" t="s">
+      <c r="B53" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C53" s="58" t="s">
+      <c r="C53" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D53" s="60" t="s">
+      <c r="D53" s="20" t="s">
         <v>172</v>
       </c>
-      <c r="E53" s="61" t="s">
+      <c r="E53" s="21" t="s">
         <v>173</v>
       </c>
-      <c r="F53" s="61" t="s">
+      <c r="F53" s="21" t="s">
         <v>174</v>
       </c>
-      <c r="G53" s="61" t="s">
+      <c r="G53" s="21" t="s">
         <v>175</v>
       </c>
-      <c r="H53" s="61" t="s">
+      <c r="H53" s="21" t="s">
         <v>176</v>
       </c>
-      <c r="I53" s="60" t="s">
+      <c r="I53" s="20" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="58">
+      <c r="A54" s="18">
         <v>53</v>
       </c>
-      <c r="B54" s="59" t="s">
+      <c r="B54" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C54" s="58" t="s">
+      <c r="C54" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D54" s="60" t="s">
+      <c r="D54" s="20" t="s">
         <v>833</v>
       </c>
-      <c r="E54" s="61" t="s">
+      <c r="E54" s="21" t="s">
         <v>834</v>
       </c>
-      <c r="F54" s="61" t="s">
+      <c r="F54" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="H54" s="61" t="s">
+      <c r="H54" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="I54" s="60" t="s">
+      <c r="I54" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A55" s="58">
+      <c r="A55" s="18">
         <v>54</v>
       </c>
-      <c r="B55" s="59" t="s">
+      <c r="B55" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C55" s="58" t="s">
+      <c r="C55" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D55" s="60" t="s">
+      <c r="D55" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E55" s="62">
+      <c r="E55" s="22">
         <v>16</v>
       </c>
-      <c r="F55" s="62">
+      <c r="F55" s="22">
         <v>4</v>
       </c>
-      <c r="G55" s="62">
+      <c r="G55" s="22">
         <v>8</v>
       </c>
-      <c r="H55" s="62">
+      <c r="H55" s="22">
         <v>10</v>
       </c>
-      <c r="I55" s="63" t="s">
+      <c r="I55" s="23" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="56" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A56" s="58">
+      <c r="A56" s="18">
         <v>55</v>
       </c>
-      <c r="B56" s="59" t="s">
+      <c r="B56" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C56" s="58" t="s">
+      <c r="C56" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D56" s="60" t="s">
+      <c r="D56" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E56" s="61" t="s">
+      <c r="E56" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="F56" s="61" t="s">
+      <c r="F56" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="G56" s="61" t="s">
+      <c r="G56" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="H56" s="61" t="s">
+      <c r="H56" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="I56" s="60" t="s">
+      <c r="I56" s="20" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A57" s="58">
+      <c r="A57" s="18">
         <v>56</v>
       </c>
-      <c r="B57" s="59" t="s">
+      <c r="B57" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C57" s="58" t="s">
+      <c r="C57" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D57" s="60" t="s">
+      <c r="D57" s="20" t="s">
         <v>835</v>
       </c>
-      <c r="E57" s="64">
+      <c r="E57" s="24">
         <v>0.1</v>
       </c>
-      <c r="F57" s="64">
+      <c r="F57" s="24">
         <v>0.25</v>
       </c>
-      <c r="G57" s="64">
+      <c r="G57" s="24">
         <v>0.15</v>
       </c>
-      <c r="H57" s="64">
+      <c r="H57" s="24">
         <v>0.2</v>
       </c>
-      <c r="I57" s="65" t="s">
+      <c r="I57" s="25" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A58" s="58">
+      <c r="A58" s="18">
         <v>57</v>
       </c>
-      <c r="B58" s="59" t="s">
+      <c r="B58" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C58" s="58" t="s">
+      <c r="C58" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D58" s="66" t="s">
+      <c r="D58" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="E58" s="66" t="s">
+      <c r="E58" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="F58" s="66" t="s">
+      <c r="F58" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="G58" s="66" t="s">
+      <c r="G58" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="H58" s="66" t="s">
+      <c r="H58" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="I58" s="66" t="s">
+      <c r="I58" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A59" s="58">
+      <c r="A59" s="18">
         <v>58</v>
       </c>
-      <c r="B59" s="59" t="s">
+      <c r="B59" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C59" s="58" t="s">
+      <c r="C59" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D59" s="66" t="s">
+      <c r="D59" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
-      <c r="G59" s="66"/>
-      <c r="H59" s="66"/>
-      <c r="I59" s="66">
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60" s="58">
+      <c r="A60" s="18">
         <v>59</v>
       </c>
-      <c r="B60" s="59" t="s">
+      <c r="B60" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C60" s="58" t="s">
+      <c r="C60" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="D60" s="66" t="s">
+      <c r="D60" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
-      <c r="G60" s="66"/>
-      <c r="H60" s="66"/>
-      <c r="I60" s="66">
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26">
         <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="58">
+      <c r="A61" s="18">
         <v>60</v>
       </c>
-      <c r="B61" s="59" t="s">
+      <c r="B61" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C61" s="58" t="s">
+      <c r="C61" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D61" s="66" t="s">
+      <c r="D61" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="E61" s="66" t="s">
+      <c r="E61" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="F61" s="66" t="s">
+      <c r="F61" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="G61" s="66" t="s">
+      <c r="G61" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="H61" s="66" t="s">
+      <c r="H61" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="I61" s="66" t="s">
+      <c r="I61" s="26" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62" s="58">
+      <c r="A62" s="18">
         <v>61</v>
       </c>
-      <c r="B62" s="59" t="s">
+      <c r="B62" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C62" s="58" t="s">
+      <c r="C62" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D62" s="60" t="s">
+      <c r="D62" s="20" t="s">
         <v>836</v>
       </c>
-      <c r="E62" s="64">
+      <c r="E62" s="24">
         <v>0.3</v>
       </c>
-      <c r="F62" s="64">
+      <c r="F62" s="24">
         <v>0.2</v>
       </c>
-      <c r="G62" s="64">
+      <c r="G62" s="24">
         <v>0.35</v>
       </c>
-      <c r="H62" s="64">
+      <c r="H62" s="24">
         <v>0.45</v>
       </c>
-      <c r="I62" s="66" t="s">
+      <c r="I62" s="26" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="A63" s="58">
+      <c r="A63" s="18">
         <v>62</v>
       </c>
-      <c r="B63" s="59" t="s">
+      <c r="B63" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C63" s="58" t="s">
+      <c r="C63" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D63" s="60" t="s">
+      <c r="D63" s="20" t="s">
         <v>198</v>
       </c>
-      <c r="E63" s="61" t="s">
+      <c r="E63" s="21" t="s">
         <v>199</v>
       </c>
-      <c r="F63" s="61" t="s">
+      <c r="F63" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="G63" s="61" t="s">
+      <c r="G63" s="21" t="s">
         <v>201</v>
       </c>
-      <c r="H63" s="61" t="s">
+      <c r="H63" s="21" t="s">
         <v>202</v>
       </c>
-      <c r="I63" s="66" t="s">
+      <c r="I63" s="26" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64" s="58">
+      <c r="A64" s="18">
         <v>63</v>
       </c>
-      <c r="B64" s="59" t="s">
+      <c r="B64" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C64" s="58" t="s">
+      <c r="C64" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D64" s="58" t="s">
+      <c r="D64" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="E64" s="67" t="s">
+      <c r="E64" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="F64" s="67" t="s">
+      <c r="F64" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="G64" s="67" t="s">
+      <c r="G64" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="H64" s="67" t="s">
+      <c r="H64" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="I64" s="58" t="s">
+      <c r="I64" s="18" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A65" s="58">
+      <c r="A65" s="18">
         <v>64</v>
       </c>
-      <c r="B65" s="59" t="s">
+      <c r="B65" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C65" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="D65" s="58" t="s">
+      <c r="C65" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="D65" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="E65" s="67" t="s">
+      <c r="E65" s="27" t="s">
         <v>207</v>
       </c>
-      <c r="F65" s="67" t="s">
+      <c r="F65" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="G65" s="67" t="s">
+      <c r="G65" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="H65" s="67" t="s">
+      <c r="H65" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="I65" s="66" t="s">
+      <c r="I65" s="26" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66" s="58">
+      <c r="A66" s="18">
         <v>65</v>
       </c>
-      <c r="B66" s="44" t="s">
+      <c r="B66" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C66" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D66" s="42" t="s">
+      <c r="C66" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E66" s="42" t="s">
+      <c r="E66" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F66" s="42" t="s">
+      <c r="F66" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="G66" s="42" t="s">
+      <c r="G66" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="H66" s="42" t="s">
+      <c r="H66" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="I66" s="45" t="s">
+      <c r="I66" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A67" s="58">
+      <c r="A67" s="18">
         <v>66</v>
       </c>
-      <c r="B67" s="44" t="s">
+      <c r="B67" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C67" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D67" s="42" t="s">
+      <c r="C67" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E67" s="42" t="s">
+      <c r="E67" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="F67" s="46" t="s">
+      <c r="F67" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="G67" s="42" t="s">
+      <c r="G67" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="H67" s="42" t="s">
+      <c r="H67" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="I67" s="47" t="s">
+      <c r="I67" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68" s="58">
+      <c r="A68" s="18">
         <v>67</v>
       </c>
-      <c r="B68" s="44" t="s">
+      <c r="B68" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C68" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D68" s="42" t="s">
+      <c r="C68" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="E68" s="42" t="s">
+      <c r="E68" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="F68" s="42" t="s">
+      <c r="F68" s="2" t="s">
         <v>223</v>
       </c>
-      <c r="G68" s="42" t="s">
+      <c r="G68" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="H68" s="42" t="s">
+      <c r="H68" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="I68" s="47" t="s">
+      <c r="I68" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A69" s="58">
+      <c r="A69" s="18">
         <v>68</v>
       </c>
-      <c r="B69" s="44" t="s">
+      <c r="B69" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C69" s="44" t="s">
+      <c r="C69" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D69" s="44" t="s">
+      <c r="D69" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="E69" s="42" t="s">
+      <c r="E69" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="F69" s="42" t="s">
+      <c r="F69" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G69" s="42" t="s">
+      <c r="G69" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H69" s="42" t="s">
+      <c r="H69" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="I69" s="47" t="s">
+      <c r="I69" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70" s="58">
+      <c r="A70" s="18">
         <v>69</v>
       </c>
-      <c r="B70" s="44" t="s">
+      <c r="B70" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C70" s="44" t="s">
+      <c r="C70" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="D70" s="42" t="s">
+      <c r="D70" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="E70" s="42" t="s">
+      <c r="E70" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="F70" s="42" t="s">
+      <c r="F70" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="G70" s="42" t="s">
+      <c r="G70" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="H70" s="42" t="s">
+      <c r="H70" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="I70" s="47" t="s">
+      <c r="I70" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A71" s="58">
+      <c r="A71" s="18">
         <v>70</v>
       </c>
-      <c r="B71" s="44" t="s">
+      <c r="B71" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C71" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" s="44" t="s">
+      <c r="C71" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="E71" s="44" t="s">
+      <c r="E71" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="F71" s="44" t="s">
+      <c r="F71" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G71" s="44" t="s">
+      <c r="G71" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="H71" s="44" t="s">
+      <c r="H71" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="I71" s="45" t="s">
+      <c r="I71" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72" s="58">
+      <c r="A72" s="18">
         <v>71</v>
       </c>
-      <c r="B72" s="44" t="s">
+      <c r="B72" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C72" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" s="42" t="s">
+      <c r="C72" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="E72" s="42" t="s">
+      <c r="E72" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="F72" s="42" t="s">
+      <c r="F72" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="G72" s="42" t="s">
+      <c r="G72" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="H72" s="42" t="s">
+      <c r="H72" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="I72" s="47" t="s">
+      <c r="I72" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A73" s="58">
+      <c r="A73" s="18">
         <v>72</v>
       </c>
-      <c r="B73" s="44" t="s">
+      <c r="B73" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C73" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" s="42" t="s">
+      <c r="C73" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E73" s="42" t="s">
+      <c r="E73" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="F73" s="42" t="s">
+      <c r="F73" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="G73" s="42" t="s">
+      <c r="G73" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="H73" s="42" t="s">
+      <c r="H73" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="I73" s="47" t="s">
+      <c r="I73" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74" s="58">
+      <c r="A74" s="18">
         <v>73</v>
       </c>
-      <c r="B74" s="44" t="s">
+      <c r="B74" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C74" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" s="42" t="s">
+      <c r="C74" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E74" s="42" t="s">
+      <c r="E74" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="F74" s="42" t="s">
+      <c r="F74" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="G74" s="42" t="s">
+      <c r="G74" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="H74" s="42" t="s">
+      <c r="H74" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="I74" s="47" t="s">
+      <c r="I74" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A75" s="58">
+      <c r="A75" s="18">
         <v>74</v>
       </c>
-      <c r="B75" s="44" t="s">
+      <c r="B75" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C75" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D75" s="42" t="s">
+      <c r="C75" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E75" s="42" t="s">
+      <c r="E75" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F75" s="42" t="s">
+      <c r="F75" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G75" s="42" t="s">
+      <c r="G75" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="H75" s="42" t="s">
+      <c r="H75" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="I75" s="45" t="s">
+      <c r="I75" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76" s="58">
+      <c r="A76" s="18">
         <v>75</v>
       </c>
-      <c r="B76" s="44" t="s">
+      <c r="B76" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C76" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D76" s="42" t="s">
+      <c r="C76" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="E76" s="42" t="s">
+      <c r="E76" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F76" s="42" t="s">
+      <c r="F76" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="G76" s="42" t="s">
+      <c r="G76" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="H76" s="42" t="s">
+      <c r="H76" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="I76" s="47" t="s">
+      <c r="I76" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A77" s="58">
+      <c r="A77" s="18">
         <v>76</v>
       </c>
-      <c r="B77" s="44" t="s">
+      <c r="B77" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C77" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D77" s="42" t="s">
+      <c r="C77" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="E77" s="42" t="s">
+      <c r="E77" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="F77" s="42" t="s">
+      <c r="F77" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="G77" s="42" t="s">
+      <c r="G77" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="H77" s="42" t="s">
+      <c r="H77" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="I77" s="47" t="s">
+      <c r="I77" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78" s="58">
+      <c r="A78" s="18">
         <v>77</v>
       </c>
-      <c r="B78" s="44" t="s">
+      <c r="B78" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C78" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D78" s="42" t="s">
+      <c r="C78" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D78" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="E78" s="42" t="s">
+      <c r="E78" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F78" s="42" t="s">
+      <c r="F78" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="G78" s="42" t="s">
+      <c r="G78" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="H78" s="42" t="s">
+      <c r="H78" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="I78" s="45" t="s">
+      <c r="I78" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A79" s="58">
+      <c r="A79" s="18">
         <v>78</v>
       </c>
-      <c r="B79" s="44" t="s">
+      <c r="B79" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C79" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D79" s="42" t="s">
+      <c r="C79" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="E79" s="42" t="s">
+      <c r="E79" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="F79" s="42" t="s">
+      <c r="F79" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G79" s="42" t="s">
+      <c r="G79" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="H79" s="42" t="s">
+      <c r="H79" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="I79" s="47" t="s">
+      <c r="I79" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80" s="58">
+      <c r="A80" s="18">
         <v>79</v>
       </c>
-      <c r="B80" s="44" t="s">
+      <c r="B80" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C80" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D80" s="42" t="s">
+      <c r="C80" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D80" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="E80" s="42" t="s">
+      <c r="E80" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F80" s="42" t="s">
+      <c r="F80" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G80" s="42" t="s">
+      <c r="G80" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="H80" s="42" t="s">
+      <c r="H80" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="I80" s="47" t="s">
+      <c r="I80" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A81" s="58">
+      <c r="A81" s="18">
         <v>80</v>
       </c>
-      <c r="B81" s="44" t="s">
+      <c r="B81" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C81" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D81" s="42" t="s">
+      <c r="C81" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D81" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="E81" s="42" t="s">
+      <c r="E81" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F81" s="42" t="s">
+      <c r="F81" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="G81" s="42" t="s">
+      <c r="G81" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H81" s="42" t="s">
+      <c r="H81" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="I81" s="47" t="s">
+      <c r="I81" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82" s="58">
+      <c r="A82" s="18">
         <v>81</v>
       </c>
-      <c r="B82" s="44" t="s">
+      <c r="B82" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C82" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D82" s="42" t="s">
+      <c r="C82" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D82" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="E82" s="42" t="s">
+      <c r="E82" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F82" s="42" t="s">
+      <c r="F82" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="G82" s="42" t="s">
+      <c r="G82" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H82" s="42" t="s">
+      <c r="H82" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="I82" s="47" t="s">
+      <c r="I82" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A83" s="58">
+      <c r="A83" s="18">
         <v>82</v>
       </c>
-      <c r="B83" s="44" t="s">
+      <c r="B83" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C83" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D83" s="42" t="s">
+      <c r="C83" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D83" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="E83" s="42" t="s">
+      <c r="E83" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F83" s="42" t="s">
+      <c r="F83" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="G83" s="42" t="s">
+      <c r="G83" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="H83" s="42" t="s">
+      <c r="H83" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="I83" s="45" t="s">
+      <c r="I83" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84" s="58">
+      <c r="A84" s="18">
         <v>83</v>
       </c>
-      <c r="B84" s="44" t="s">
+      <c r="B84" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C84" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D84" s="42" t="s">
+      <c r="C84" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E84" s="42" t="s">
+      <c r="E84" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="F84" s="42" t="s">
+      <c r="F84" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="G84" s="42" t="s">
+      <c r="G84" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="H84" s="42" t="s">
+      <c r="H84" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="I84" s="47" t="s">
+      <c r="I84" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A85" s="58">
+      <c r="A85" s="18">
         <v>84</v>
       </c>
-      <c r="B85" s="44" t="s">
+      <c r="B85" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="C85" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D85" s="42" t="s">
+      <c r="C85" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E85" s="42" t="s">
+      <c r="E85" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="F85" s="42" t="s">
+      <c r="F85" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="G85" s="42" t="s">
+      <c r="G85" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="H85" s="42" t="s">
+      <c r="H85" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="I85" s="47" t="s">
+      <c r="I85" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86" s="58">
+      <c r="A86" s="18">
         <v>85</v>
       </c>
-      <c r="B86" s="42" t="s">
+      <c r="B86" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C86" s="42" t="s">
+      <c r="C86" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D86" s="42" t="s">
+      <c r="D86" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="E86" s="48"/>
-      <c r="F86" s="49"/>
-      <c r="G86" s="49"/>
-      <c r="H86" s="50"/>
-      <c r="I86" s="47">
+      <c r="E86" s="8"/>
+      <c r="F86" s="9"/>
+      <c r="G86" s="9"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A87" s="58">
+      <c r="A87" s="18">
         <v>86</v>
       </c>
-      <c r="B87" s="42" t="s">
+      <c r="B87" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C87" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D87" s="42" t="s">
+      <c r="C87" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D87" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="E87" s="42" t="s">
+      <c r="E87" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="F87" s="42" t="s">
+      <c r="F87" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="G87" s="42" t="s">
+      <c r="G87" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="H87" s="42" t="s">
+      <c r="H87" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="I87" s="45" t="s">
+      <c r="I87" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A88" s="58">
+      <c r="A88" s="18">
         <v>87</v>
       </c>
-      <c r="B88" s="42" t="s">
+      <c r="B88" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C88" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D88" s="42" t="s">
+      <c r="C88" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D88" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="E88" s="42" t="s">
+      <c r="E88" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="F88" s="42" t="s">
+      <c r="F88" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="G88" s="42" t="s">
+      <c r="G88" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="H88" s="42" t="s">
+      <c r="H88" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="I88" s="47" t="s">
+      <c r="I88" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="58">
+      <c r="A89" s="18">
         <v>88</v>
       </c>
-      <c r="B89" s="42" t="s">
+      <c r="B89" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C89" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D89" s="42" t="s">
+      <c r="C89" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E89" s="42" t="s">
+      <c r="E89" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F89" s="42" t="s">
+      <c r="F89" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="G89" s="42" t="s">
+      <c r="G89" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="H89" s="42" t="s">
+      <c r="H89" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="I89" s="47" t="s">
+      <c r="I89" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="58">
+      <c r="A90" s="18">
         <v>89</v>
       </c>
-      <c r="B90" s="42" t="s">
+      <c r="B90" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C90" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D90" s="42" t="s">
+      <c r="C90" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D90" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="E90" s="42" t="s">
+      <c r="E90" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="F90" s="42" t="s">
+      <c r="F90" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="G90" s="42" t="s">
+      <c r="G90" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="H90" s="42" t="s">
+      <c r="H90" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="I90" s="45" t="s">
+      <c r="I90" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="58">
+      <c r="A91" s="18">
         <v>90</v>
       </c>
-      <c r="B91" s="42" t="s">
+      <c r="B91" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C91" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D91" s="42" t="s">
+      <c r="C91" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D91" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="E91" s="42" t="s">
+      <c r="E91" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="F91" s="42" t="s">
+      <c r="F91" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="G91" s="42" t="s">
+      <c r="G91" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="H91" s="42" t="s">
+      <c r="H91" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="I91" s="45" t="s">
+      <c r="I91" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="58">
+      <c r="A92" s="18">
         <v>91</v>
       </c>
-      <c r="B92" s="42" t="s">
+      <c r="B92" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C92" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D92" s="42" t="s">
+      <c r="C92" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D92" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="E92" s="44" t="s">
+      <c r="E92" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="F92" s="42" t="s">
+      <c r="F92" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="G92" s="42" t="s">
+      <c r="G92" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="H92" s="42" t="s">
+      <c r="H92" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="I92" s="47" t="s">
+      <c r="I92" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="58">
+      <c r="A93" s="18">
         <v>92</v>
       </c>
-      <c r="B93" s="42" t="s">
+      <c r="B93" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C93" s="42" t="s">
+      <c r="C93" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D93" s="42" t="s">
+      <c r="D93" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="E93" s="51"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="52"/>
-      <c r="H93" s="53"/>
-      <c r="I93" s="47">
+      <c r="E93" s="11"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="12"/>
+      <c r="H93" s="13"/>
+      <c r="I93" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="58">
+      <c r="A94" s="18">
         <v>93</v>
       </c>
-      <c r="B94" s="42" t="s">
+      <c r="B94" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C94" s="42" t="s">
+      <c r="C94" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D94" s="42" t="s">
+      <c r="D94" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E94" s="51"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="52"/>
-      <c r="H94" s="53"/>
-      <c r="I94" s="47">
+      <c r="E94" s="11"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="12"/>
+      <c r="H94" s="13"/>
+      <c r="I94" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="58">
+      <c r="A95" s="18">
         <v>94</v>
       </c>
-      <c r="B95" s="42" t="s">
+      <c r="B95" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="C95" s="42" t="s">
+      <c r="C95" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D95" s="42" t="s">
+      <c r="D95" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="E95" s="48"/>
-      <c r="F95" s="49"/>
-      <c r="G95" s="49"/>
-      <c r="H95" s="50"/>
-      <c r="I95" s="47">
+      <c r="E95" s="8"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+      <c r="H95" s="10"/>
+      <c r="I95" s="7">
         <v>1</v>
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="58">
+      <c r="A96" s="18">
         <v>95</v>
       </c>
-      <c r="B96" s="42" t="s">
+      <c r="B96" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C96" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D96" s="42" t="s">
+      <c r="C96" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D96" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="E96" s="42" t="s">
+      <c r="E96" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="F96" s="42" t="s">
+      <c r="F96" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="G96" s="42" t="s">
+      <c r="G96" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="H96" s="42" t="s">
+      <c r="H96" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="I96" s="45" t="s">
+      <c r="I96" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A97" s="58">
+      <c r="A97" s="18">
         <v>96</v>
       </c>
-      <c r="B97" s="42" t="s">
+      <c r="B97" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C97" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D97" s="42" t="s">
+      <c r="C97" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D97" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="E97" s="42" t="s">
+      <c r="E97" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="F97" s="42" t="s">
+      <c r="F97" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="G97" s="42" t="s">
+      <c r="G97" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="H97" s="42" t="s">
+      <c r="H97" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="I97" s="47" t="s">
+      <c r="I97" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A98" s="58">
+      <c r="A98" s="18">
         <v>97</v>
       </c>
-      <c r="B98" s="42" t="s">
+      <c r="B98" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C98" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D98" s="42" t="s">
+      <c r="C98" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="E98" s="42" t="s">
+      <c r="E98" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="F98" s="42" t="s">
+      <c r="F98" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="G98" s="42" t="s">
+      <c r="G98" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="H98" s="42" t="s">
+      <c r="H98" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="I98" s="47" t="s">
+      <c r="I98" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A99" s="58">
+      <c r="A99" s="18">
         <v>98</v>
       </c>
-      <c r="B99" s="42" t="s">
+      <c r="B99" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C99" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D99" s="42" t="s">
+      <c r="C99" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E99" s="42" t="s">
+      <c r="E99" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="F99" s="42" t="s">
+      <c r="F99" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G99" s="42" t="s">
+      <c r="G99" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="H99" s="42" t="s">
+      <c r="H99" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="I99" s="47" t="s">
+      <c r="I99" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A100" s="58">
+      <c r="A100" s="18">
         <v>99</v>
       </c>
-      <c r="B100" s="42" t="s">
+      <c r="B100" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C100" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D100" s="42" t="s">
+      <c r="C100" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D100" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="E100" s="42" t="s">
+      <c r="E100" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="F100" s="42" t="s">
+      <c r="F100" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="G100" s="42" t="s">
+      <c r="G100" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="H100" s="42" t="s">
+      <c r="H100" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="I100" s="45" t="s">
+      <c r="I100" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A101" s="58">
+      <c r="A101" s="18">
         <v>100</v>
       </c>
-      <c r="B101" s="42" t="s">
+      <c r="B101" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C101" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D101" s="42" t="s">
+      <c r="C101" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D101" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="E101" s="42" t="s">
+      <c r="E101" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F101" s="42" t="s">
+      <c r="F101" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="G101" s="42" t="s">
+      <c r="G101" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="H101" s="42" t="s">
+      <c r="H101" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="I101" s="47" t="s">
+      <c r="I101" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A102" s="58">
+      <c r="A102" s="18">
         <v>101</v>
       </c>
-      <c r="B102" s="42" t="s">
+      <c r="B102" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C102" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D102" s="42" t="s">
+      <c r="C102" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D102" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="E102" s="42" t="s">
+      <c r="E102" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="F102" s="42" t="s">
+      <c r="F102" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="G102" s="42" t="s">
+      <c r="G102" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="H102" s="42" t="s">
+      <c r="H102" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="I102" s="47" t="s">
+      <c r="I102" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A103" s="58">
+      <c r="A103" s="18">
         <v>102</v>
       </c>
-      <c r="B103" s="42" t="s">
+      <c r="B103" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C103" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D103" s="42" t="s">
+      <c r="C103" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="E103" s="42" t="s">
+      <c r="E103" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F103" s="42" t="s">
+      <c r="F103" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="G103" s="42" t="s">
+      <c r="G103" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="H103" s="42" t="s">
+      <c r="H103" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="I103" s="45" t="s">
+      <c r="I103" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A104" s="58">
+      <c r="A104" s="18">
         <v>103</v>
       </c>
-      <c r="B104" s="42" t="s">
+      <c r="B104" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C104" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D104" s="42" t="s">
+      <c r="C104" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D104" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="E104" s="42" t="s">
+      <c r="E104" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="F104" s="42" t="s">
+      <c r="F104" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="G104" s="42" t="s">
+      <c r="G104" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="H104" s="42" t="s">
+      <c r="H104" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="I104" s="47" t="s">
+      <c r="I104" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A105" s="58">
+      <c r="A105" s="18">
         <v>104</v>
       </c>
-      <c r="B105" s="42" t="s">
+      <c r="B105" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="C105" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D105" s="42" t="s">
+      <c r="C105" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D105" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E105" s="42" t="s">
+      <c r="E105" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F105" s="42" t="s">
+      <c r="F105" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="G105" s="42" t="s">
+      <c r="G105" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="H105" s="42" t="s">
+      <c r="H105" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="I105" s="47" t="s">
+      <c r="I105" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A106" s="58">
+      <c r="A106" s="18">
         <v>105</v>
       </c>
-      <c r="B106" s="42" t="s">
+      <c r="B106" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C106" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D106" s="42" t="s">
+      <c r="C106" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="E106" s="42" t="s">
+      <c r="E106" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="F106" s="42" t="s">
+      <c r="F106" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="G106" s="42" t="s">
+      <c r="G106" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="H106" s="42" t="s">
+      <c r="H106" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="I106" s="45" t="s">
+      <c r="I106" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A107" s="58">
+      <c r="A107" s="18">
         <v>106</v>
       </c>
-      <c r="B107" s="42" t="s">
+      <c r="B107" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C107" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D107" s="42" t="s">
+      <c r="C107" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="E107" s="42" t="s">
+      <c r="E107" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="F107" s="42" t="s">
+      <c r="F107" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="G107" s="42" t="s">
+      <c r="G107" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="H107" s="42" t="s">
+      <c r="H107" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="I107" s="47" t="s">
+      <c r="I107" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A108" s="58">
+      <c r="A108" s="18">
         <v>107</v>
       </c>
-      <c r="B108" s="42" t="s">
+      <c r="B108" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C108" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D108" s="42" t="s">
+      <c r="C108" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D108" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E108" s="42" t="s">
+      <c r="E108" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="F108" s="42" t="s">
+      <c r="F108" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G108" s="42" t="s">
+      <c r="G108" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="H108" s="42" t="s">
+      <c r="H108" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="I108" s="45" t="s">
+      <c r="I108" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A109" s="58">
+      <c r="A109" s="18">
         <v>108</v>
       </c>
-      <c r="B109" s="42" t="s">
+      <c r="B109" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C109" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D109" s="42" t="s">
+      <c r="C109" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D109" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="E109" s="42" t="s">
+      <c r="E109" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F109" s="42" t="s">
+      <c r="F109" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="G109" s="42" t="s">
+      <c r="G109" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="H109" s="42" t="s">
+      <c r="H109" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="I109" s="47" t="s">
+      <c r="I109" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A110" s="58">
+      <c r="A110" s="18">
         <v>109</v>
       </c>
-      <c r="B110" s="42" t="s">
+      <c r="B110" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C110" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D110" s="42" t="s">
+      <c r="C110" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="E110" s="42" t="s">
+      <c r="E110" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F110" s="42" t="s">
+      <c r="F110" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="G110" s="42" t="s">
+      <c r="G110" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="H110" s="42" t="s">
+      <c r="H110" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="I110" s="45" t="s">
+      <c r="I110" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A111" s="58">
+      <c r="A111" s="18">
         <v>110</v>
       </c>
-      <c r="B111" s="42" t="s">
+      <c r="B111" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C111" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D111" s="42" t="s">
+      <c r="C111" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="E111" s="42" t="s">
+      <c r="E111" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F111" s="42" t="s">
+      <c r="F111" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G111" s="42" t="s">
+      <c r="G111" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="H111" s="42" t="s">
+      <c r="H111" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="I111" s="47" t="s">
+      <c r="I111" s="7" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A112" s="58">
+      <c r="A112" s="18">
         <v>111</v>
       </c>
-      <c r="B112" s="42" t="s">
+      <c r="B112" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C112" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D112" s="42" t="s">
+      <c r="C112" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="E112" s="42" t="s">
+      <c r="E112" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="F112" s="42" t="s">
+      <c r="F112" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="G112" s="42" t="s">
+      <c r="G112" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="H112" s="42" t="s">
+      <c r="H112" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="I112" s="47" t="s">
+      <c r="I112" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A113" s="58">
+      <c r="A113" s="18">
         <v>112</v>
       </c>
-      <c r="B113" s="42" t="s">
+      <c r="B113" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C113" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D113" s="42" t="s">
+      <c r="C113" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D113" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="E113" s="42" t="s">
+      <c r="E113" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="F113" s="42" t="s">
+      <c r="F113" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="G113" s="42" t="s">
+      <c r="G113" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="H113" s="42" t="s">
+      <c r="H113" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="I113" s="45" t="s">
+      <c r="I113" s="5" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A114" s="58">
+      <c r="A114" s="18">
         <v>113</v>
       </c>
-      <c r="B114" s="42" t="s">
+      <c r="B114" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="C114" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="D114" s="42" t="s">
+      <c r="C114" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="E114" s="42" t="s">
+      <c r="E114" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="F114" s="42" t="s">
+      <c r="F114" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="G114" s="42" t="s">
+      <c r="G114" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="H114" s="42" t="s">
+      <c r="H114" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="I114" s="47" t="s">
+      <c r="I114" s="7" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="58">
+      <c r="A115" s="18">
         <v>114</v>
       </c>
-      <c r="B115" s="41" t="s">
+      <c r="B115" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="C115" s="41" t="s">
-        <v>1</v>
-      </c>
-      <c r="D115" s="42" t="s">
+      <c r="C115" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="E115" s="42" t="s">
+      <c r="E115" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="F115" s="42" t="s">
+      <c r="F115" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="G115" s="42" t="s">
+      <c r="G115" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="H115" s="42" t="s">
+      <c r="H115" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="I115" s="43" t="s">
+      <c r="I115" s="3" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="116" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A116" s="58">
+      <c r="A116" s="18">
         <v>115</v>
       </c>
-      <c r="B116" s="54" t="s">
+      <c r="B116" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C116" s="54" t="s">
+      <c r="C116" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D116" s="54" t="s">
+      <c r="D116" s="14" t="s">
         <v>449</v>
       </c>
-      <c r="E116" s="54"/>
-      <c r="F116" s="54"/>
-      <c r="G116" s="54"/>
-      <c r="H116" s="54"/>
-      <c r="I116" s="68">
+      <c r="E116" s="14"/>
+      <c r="F116" s="14"/>
+      <c r="G116" s="14"/>
+      <c r="H116" s="14"/>
+      <c r="I116" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A117" s="58">
+      <c r="A117" s="18">
         <v>116</v>
       </c>
-      <c r="B117" s="54" t="s">
+      <c r="B117" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C117" s="54" t="s">
+      <c r="C117" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D117" s="54" t="s">
+      <c r="D117" s="14" t="s">
         <v>451</v>
       </c>
-      <c r="E117" s="54"/>
-      <c r="F117" s="54"/>
-      <c r="G117" s="54"/>
-      <c r="H117" s="54"/>
-      <c r="I117" s="68">
+      <c r="E117" s="14"/>
+      <c r="F117" s="14"/>
+      <c r="G117" s="14"/>
+      <c r="H117" s="14"/>
+      <c r="I117" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A118" s="58">
+      <c r="A118" s="18">
         <v>117</v>
       </c>
-      <c r="B118" s="54" t="s">
+      <c r="B118" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C118" s="54" t="s">
+      <c r="C118" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D118" s="54" t="s">
+      <c r="D118" s="14" t="s">
         <v>452</v>
       </c>
-      <c r="E118" s="54"/>
-      <c r="F118" s="54"/>
-      <c r="G118" s="54"/>
-      <c r="H118" s="54"/>
-      <c r="I118" s="69">
+      <c r="E118" s="14"/>
+      <c r="F118" s="14"/>
+      <c r="G118" s="14"/>
+      <c r="H118" s="14"/>
+      <c r="I118" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A119" s="58">
+      <c r="A119" s="18">
         <v>118</v>
       </c>
-      <c r="B119" s="54" t="s">
+      <c r="B119" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C119" s="54" t="s">
+      <c r="C119" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D119" s="54" t="s">
+      <c r="D119" s="14" t="s">
         <v>453</v>
       </c>
-      <c r="E119" s="54"/>
-      <c r="F119" s="54"/>
-      <c r="G119" s="54"/>
-      <c r="H119" s="54"/>
-      <c r="I119" s="68">
+      <c r="E119" s="14"/>
+      <c r="F119" s="14"/>
+      <c r="G119" s="14"/>
+      <c r="H119" s="14"/>
+      <c r="I119" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A120" s="58">
+      <c r="A120" s="18">
         <v>119</v>
       </c>
-      <c r="B120" s="54" t="s">
+      <c r="B120" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C120" s="54" t="s">
+      <c r="C120" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D120" s="54" t="s">
+      <c r="D120" s="14" t="s">
         <v>454</v>
       </c>
-      <c r="E120" s="54"/>
-      <c r="F120" s="54"/>
-      <c r="G120" s="54"/>
-      <c r="H120" s="54"/>
-      <c r="I120" s="69">
+      <c r="E120" s="14"/>
+      <c r="F120" s="14"/>
+      <c r="G120" s="14"/>
+      <c r="H120" s="14"/>
+      <c r="I120" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A121" s="58">
+      <c r="A121" s="18">
         <v>120</v>
       </c>
-      <c r="B121" s="54" t="s">
+      <c r="B121" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C121" s="54" t="s">
+      <c r="C121" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="D121" s="54" t="s">
+      <c r="D121" s="14" t="s">
         <v>455</v>
       </c>
-      <c r="E121" s="54"/>
-      <c r="F121" s="54"/>
-      <c r="G121" s="54"/>
-      <c r="H121" s="54"/>
-      <c r="I121" s="68">
+      <c r="E121" s="14"/>
+      <c r="F121" s="14"/>
+      <c r="G121" s="14"/>
+      <c r="H121" s="14"/>
+      <c r="I121" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A122" s="58">
+      <c r="A122" s="18">
         <v>121</v>
       </c>
-      <c r="B122" s="54" t="s">
+      <c r="B122" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C122" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D122" s="69" t="s">
+      <c r="C122" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D122" s="29" t="s">
         <v>456</v>
       </c>
-      <c r="E122" s="69" t="s">
+      <c r="E122" s="29" t="s">
         <v>457</v>
       </c>
-      <c r="F122" s="69" t="s">
+      <c r="F122" s="29" t="s">
         <v>458</v>
       </c>
-      <c r="G122" s="69" t="s">
+      <c r="G122" s="29" t="s">
         <v>459</v>
       </c>
-      <c r="H122" s="69" t="s">
+      <c r="H122" s="29" t="s">
         <v>460</v>
       </c>
-      <c r="I122" s="68" t="s">
+      <c r="I122" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="123" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A123" s="58">
+      <c r="A123" s="18">
         <v>122</v>
       </c>
-      <c r="B123" s="54" t="s">
+      <c r="B123" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C123" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D123" s="69" t="s">
+      <c r="C123" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D123" s="29" t="s">
         <v>461</v>
       </c>
-      <c r="E123" s="69" t="s">
+      <c r="E123" s="29" t="s">
         <v>462</v>
       </c>
-      <c r="F123" s="69" t="s">
+      <c r="F123" s="29" t="s">
         <v>463</v>
       </c>
-      <c r="G123" s="69" t="s">
+      <c r="G123" s="29" t="s">
         <v>464</v>
       </c>
-      <c r="H123" s="69" t="s">
+      <c r="H123" s="29" t="s">
         <v>465</v>
       </c>
-      <c r="I123" s="68" t="s">
+      <c r="I123" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="124" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A124" s="58">
+      <c r="A124" s="18">
         <v>123</v>
       </c>
-      <c r="B124" s="54" t="s">
+      <c r="B124" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C124" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D124" s="69" t="s">
+      <c r="C124" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D124" s="29" t="s">
         <v>466</v>
       </c>
-      <c r="E124" s="69" t="s">
+      <c r="E124" s="29" t="s">
         <v>467</v>
       </c>
-      <c r="F124" s="69" t="s">
+      <c r="F124" s="29" t="s">
         <v>468</v>
       </c>
-      <c r="G124" s="69" t="s">
+      <c r="G124" s="29" t="s">
         <v>469</v>
       </c>
-      <c r="H124" s="69" t="s">
+      <c r="H124" s="29" t="s">
         <v>470</v>
       </c>
-      <c r="I124" s="68" t="s">
+      <c r="I124" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A125" s="58">
+      <c r="A125" s="18">
         <v>124</v>
       </c>
-      <c r="B125" s="54" t="s">
+      <c r="B125" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C125" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D125" s="69" t="s">
+      <c r="C125" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D125" s="29" t="s">
         <v>471</v>
       </c>
-      <c r="E125" s="69" t="s">
+      <c r="E125" s="29" t="s">
         <v>472</v>
       </c>
-      <c r="F125" s="69" t="s">
+      <c r="F125" s="29" t="s">
         <v>473</v>
       </c>
-      <c r="G125" s="69" t="s">
+      <c r="G125" s="29" t="s">
         <v>474</v>
       </c>
-      <c r="H125" s="69" t="s">
+      <c r="H125" s="29" t="s">
         <v>475</v>
       </c>
-      <c r="I125" s="68" t="s">
+      <c r="I125" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="126" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A126" s="58">
+      <c r="A126" s="18">
         <v>125</v>
       </c>
-      <c r="B126" s="54" t="s">
+      <c r="B126" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C126" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D126" s="69" t="s">
+      <c r="C126" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D126" s="29" t="s">
         <v>477</v>
       </c>
-      <c r="E126" s="69" t="s">
+      <c r="E126" s="29" t="s">
         <v>478</v>
       </c>
-      <c r="F126" s="69" t="s">
+      <c r="F126" s="29" t="s">
         <v>479</v>
       </c>
-      <c r="G126" s="69" t="s">
+      <c r="G126" s="29" t="s">
         <v>480</v>
       </c>
-      <c r="H126" s="69" t="s">
+      <c r="H126" s="29" t="s">
         <v>481</v>
       </c>
-      <c r="I126" s="68" t="s">
+      <c r="I126" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A127" s="58">
+      <c r="A127" s="18">
         <v>126</v>
       </c>
-      <c r="B127" s="54" t="s">
+      <c r="B127" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C127" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D127" s="69" t="s">
+      <c r="C127" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D127" s="29" t="s">
         <v>482</v>
       </c>
-      <c r="E127" s="69" t="s">
+      <c r="E127" s="29" t="s">
         <v>483</v>
       </c>
-      <c r="F127" s="69" t="s">
+      <c r="F127" s="29" t="s">
         <v>484</v>
       </c>
-      <c r="G127" s="69" t="s">
+      <c r="G127" s="29" t="s">
         <v>485</v>
       </c>
-      <c r="H127" s="69" t="s">
+      <c r="H127" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="I127" s="68" t="s">
+      <c r="I127" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="128" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A128" s="58">
+      <c r="A128" s="18">
         <v>127</v>
       </c>
-      <c r="B128" s="54" t="s">
+      <c r="B128" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C128" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D128" s="69" t="s">
+      <c r="C128" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D128" s="29" t="s">
         <v>831</v>
       </c>
-      <c r="E128" s="69" t="s">
+      <c r="E128" s="29" t="s">
         <v>487</v>
       </c>
-      <c r="F128" s="69" t="s">
+      <c r="F128" s="29" t="s">
         <v>488</v>
       </c>
-      <c r="G128" s="69" t="s">
+      <c r="G128" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="H128" s="69" t="s">
+      <c r="H128" s="29" t="s">
         <v>490</v>
       </c>
-      <c r="I128" s="68" t="s">
+      <c r="I128" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="129" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A129" s="58">
+      <c r="A129" s="18">
         <v>128</v>
       </c>
-      <c r="B129" s="54" t="s">
+      <c r="B129" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C129" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D129" s="69" t="s">
+      <c r="C129" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D129" s="29" t="s">
         <v>491</v>
       </c>
-      <c r="E129" s="69" t="s">
+      <c r="E129" s="29" t="s">
         <v>492</v>
       </c>
-      <c r="F129" s="69" t="s">
+      <c r="F129" s="29" t="s">
         <v>493</v>
       </c>
-      <c r="G129" s="69" t="s">
+      <c r="G129" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="H129" s="69" t="s">
+      <c r="H129" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="I129" s="68" t="s">
+      <c r="I129" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="130" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A130" s="58">
+      <c r="A130" s="18">
         <v>129</v>
       </c>
-      <c r="B130" s="54" t="s">
+      <c r="B130" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C130" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D130" s="69" t="s">
+      <c r="C130" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D130" s="29" t="s">
         <v>496</v>
       </c>
-      <c r="E130" s="69" t="s">
+      <c r="E130" s="29" t="s">
         <v>497</v>
       </c>
-      <c r="F130" s="69" t="s">
+      <c r="F130" s="29" t="s">
         <v>498</v>
       </c>
-      <c r="G130" s="69" t="s">
+      <c r="G130" s="29" t="s">
         <v>499</v>
       </c>
-      <c r="H130" s="69" t="s">
+      <c r="H130" s="29" t="s">
         <v>500</v>
       </c>
-      <c r="I130" s="68" t="s">
+      <c r="I130" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="131" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A131" s="58">
+      <c r="A131" s="18">
         <v>130</v>
       </c>
-      <c r="B131" s="54" t="s">
+      <c r="B131" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C131" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D131" s="69" t="s">
+      <c r="C131" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D131" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="E131" s="69" t="s">
+      <c r="E131" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="F131" s="69" t="s">
+      <c r="F131" s="29" t="s">
         <v>502</v>
       </c>
-      <c r="G131" s="69" t="s">
+      <c r="G131" s="29" t="s">
         <v>503</v>
       </c>
-      <c r="H131" s="69" t="s">
+      <c r="H131" s="29" t="s">
         <v>504</v>
       </c>
-      <c r="I131" s="68" t="s">
+      <c r="I131" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A132" s="58">
+      <c r="A132" s="18">
         <v>131</v>
       </c>
-      <c r="B132" s="54" t="s">
+      <c r="B132" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C132" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D132" s="69" t="s">
+      <c r="C132" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D132" s="29" t="s">
         <v>505</v>
       </c>
-      <c r="E132" s="69" t="s">
+      <c r="E132" s="29" t="s">
         <v>506</v>
       </c>
-      <c r="F132" s="69" t="s">
+      <c r="F132" s="29" t="s">
         <v>507</v>
       </c>
-      <c r="G132" s="69" t="s">
+      <c r="G132" s="29" t="s">
         <v>508</v>
       </c>
-      <c r="H132" s="69" t="s">
+      <c r="H132" s="29" t="s">
         <v>509</v>
       </c>
-      <c r="I132" s="68" t="s">
+      <c r="I132" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A133" s="58">
+      <c r="A133" s="18">
         <v>132</v>
       </c>
-      <c r="B133" s="54" t="s">
+      <c r="B133" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C133" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D133" s="69" t="s">
+      <c r="C133" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D133" s="29" t="s">
         <v>510</v>
       </c>
-      <c r="E133" s="69" t="s">
+      <c r="E133" s="29" t="s">
         <v>511</v>
       </c>
-      <c r="F133" s="69" t="s">
+      <c r="F133" s="29" t="s">
         <v>512</v>
       </c>
-      <c r="G133" s="69" t="s">
+      <c r="G133" s="29" t="s">
         <v>513</v>
       </c>
-      <c r="H133" s="69" t="s">
+      <c r="H133" s="29" t="s">
         <v>514</v>
       </c>
-      <c r="I133" s="68" t="s">
+      <c r="I133" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A134" s="58">
+      <c r="A134" s="18">
         <v>133</v>
       </c>
-      <c r="B134" s="54" t="s">
+      <c r="B134" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C134" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D134" s="69" t="s">
+      <c r="C134" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D134" s="29" t="s">
         <v>515</v>
       </c>
-      <c r="E134" s="69" t="s">
+      <c r="E134" s="29" t="s">
         <v>516</v>
       </c>
-      <c r="F134" s="69" t="s">
+      <c r="F134" s="29" t="s">
         <v>517</v>
       </c>
-      <c r="G134" s="69" t="s">
+      <c r="G134" s="29" t="s">
         <v>518</v>
       </c>
-      <c r="H134" s="69" t="s">
+      <c r="H134" s="29" t="s">
         <v>519</v>
       </c>
-      <c r="I134" s="68" t="s">
+      <c r="I134" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A135" s="58">
+      <c r="A135" s="18">
         <v>134</v>
       </c>
-      <c r="B135" s="54" t="s">
+      <c r="B135" s="14" t="s">
         <v>476</v>
       </c>
-      <c r="C135" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D135" s="69" t="s">
+      <c r="C135" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D135" s="29" t="s">
         <v>520</v>
       </c>
-      <c r="E135" s="69" t="s">
+      <c r="E135" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="F135" s="69" t="s">
+      <c r="F135" s="29" t="s">
         <v>522</v>
       </c>
-      <c r="G135" s="69" t="s">
+      <c r="G135" s="29" t="s">
         <v>523</v>
       </c>
-      <c r="H135" s="69" t="s">
+      <c r="H135" s="29" t="s">
         <v>826</v>
       </c>
-      <c r="I135" s="68" t="s">
+      <c r="I135" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A136" s="58">
+      <c r="A136" s="18">
         <v>135</v>
       </c>
-      <c r="B136" s="54" t="s">
+      <c r="B136" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C136" s="69" t="s">
+      <c r="C136" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D136" s="69" t="s">
+      <c r="D136" s="29" t="s">
         <v>525</v>
       </c>
-      <c r="E136" s="69"/>
-      <c r="F136" s="69"/>
-      <c r="G136" s="69"/>
-      <c r="H136" s="69"/>
-      <c r="I136" s="68">
+      <c r="E136" s="29"/>
+      <c r="F136" s="29"/>
+      <c r="G136" s="29"/>
+      <c r="H136" s="29"/>
+      <c r="I136" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A137" s="58">
+      <c r="A137" s="18">
         <v>136</v>
       </c>
-      <c r="B137" s="54" t="s">
+      <c r="B137" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C137" s="69" t="s">
+      <c r="C137" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D137" s="69" t="s">
+      <c r="D137" s="29" t="s">
         <v>526</v>
       </c>
-      <c r="E137" s="69"/>
-      <c r="F137" s="69"/>
-      <c r="G137" s="69"/>
-      <c r="H137" s="69"/>
-      <c r="I137" s="68">
+      <c r="E137" s="29"/>
+      <c r="F137" s="29"/>
+      <c r="G137" s="29"/>
+      <c r="H137" s="29"/>
+      <c r="I137" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A138" s="58">
+      <c r="A138" s="18">
         <v>137</v>
       </c>
-      <c r="B138" s="54" t="s">
+      <c r="B138" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C138" s="69" t="s">
+      <c r="C138" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D138" s="69" t="s">
+      <c r="D138" s="29" t="s">
         <v>527</v>
       </c>
-      <c r="E138" s="69"/>
-      <c r="F138" s="69"/>
-      <c r="G138" s="69"/>
-      <c r="H138" s="69"/>
-      <c r="I138" s="68">
+      <c r="E138" s="29"/>
+      <c r="F138" s="29"/>
+      <c r="G138" s="29"/>
+      <c r="H138" s="29"/>
+      <c r="I138" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A139" s="58">
+      <c r="A139" s="18">
         <v>138</v>
       </c>
-      <c r="B139" s="54" t="s">
+      <c r="B139" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C139" s="69" t="s">
+      <c r="C139" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D139" s="69" t="s">
+      <c r="D139" s="29" t="s">
         <v>528</v>
       </c>
-      <c r="E139" s="69"/>
-      <c r="F139" s="69"/>
-      <c r="G139" s="69"/>
-      <c r="H139" s="69"/>
-      <c r="I139" s="68">
+      <c r="E139" s="29"/>
+      <c r="F139" s="29"/>
+      <c r="G139" s="29"/>
+      <c r="H139" s="29"/>
+      <c r="I139" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A140" s="58">
+      <c r="A140" s="18">
         <v>139</v>
       </c>
-      <c r="B140" s="54" t="s">
+      <c r="B140" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C140" s="69" t="s">
+      <c r="C140" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D140" s="69" t="s">
+      <c r="D140" s="29" t="s">
         <v>529</v>
       </c>
-      <c r="E140" s="69"/>
-      <c r="F140" s="69"/>
-      <c r="G140" s="69"/>
-      <c r="H140" s="69"/>
-      <c r="I140" s="69">
+      <c r="E140" s="29"/>
+      <c r="F140" s="29"/>
+      <c r="G140" s="29"/>
+      <c r="H140" s="29"/>
+      <c r="I140" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="141" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A141" s="58">
+      <c r="A141" s="18">
         <v>140</v>
       </c>
-      <c r="B141" s="54" t="s">
+      <c r="B141" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C141" s="69" t="s">
+      <c r="C141" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D141" s="69" t="s">
+      <c r="D141" s="29" t="s">
         <v>530</v>
       </c>
-      <c r="E141" s="69" t="s">
+      <c r="E141" s="29" t="s">
         <v>531</v>
       </c>
-      <c r="F141" s="69"/>
-      <c r="G141" s="69"/>
-      <c r="H141" s="69"/>
-      <c r="I141" s="68" t="s">
+      <c r="F141" s="29"/>
+      <c r="G141" s="29"/>
+      <c r="H141" s="29"/>
+      <c r="I141" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="142" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A142" s="58">
+      <c r="A142" s="18">
         <v>141</v>
       </c>
-      <c r="B142" s="54" t="s">
+      <c r="B142" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C142" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D142" s="69" t="s">
+      <c r="C142" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D142" s="29" t="s">
         <v>532</v>
       </c>
-      <c r="E142" s="69" t="s">
+      <c r="E142" s="29" t="s">
         <v>533</v>
       </c>
-      <c r="F142" s="69" t="s">
+      <c r="F142" s="29" t="s">
         <v>534</v>
       </c>
-      <c r="G142" s="69" t="s">
+      <c r="G142" s="29" t="s">
         <v>535</v>
       </c>
-      <c r="H142" s="69" t="s">
+      <c r="H142" s="29" t="s">
         <v>536</v>
       </c>
-      <c r="I142" s="68" t="s">
+      <c r="I142" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="143" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A143" s="58">
+      <c r="A143" s="18">
         <v>142</v>
       </c>
-      <c r="B143" s="54" t="s">
+      <c r="B143" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C143" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D143" s="69" t="s">
+      <c r="C143" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D143" s="29" t="s">
         <v>537</v>
       </c>
-      <c r="E143" s="69" t="s">
+      <c r="E143" s="29" t="s">
         <v>538</v>
       </c>
-      <c r="F143" s="69" t="s">
+      <c r="F143" s="29" t="s">
         <v>539</v>
       </c>
-      <c r="G143" s="69" t="s">
+      <c r="G143" s="29" t="s">
         <v>540</v>
       </c>
-      <c r="H143" s="69" t="s">
+      <c r="H143" s="29" t="s">
         <v>827</v>
       </c>
-      <c r="I143" s="68" t="s">
+      <c r="I143" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="144" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A144" s="58">
+      <c r="A144" s="18">
         <v>143</v>
       </c>
-      <c r="B144" s="54" t="s">
+      <c r="B144" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C144" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D144" s="69" t="s">
+      <c r="C144" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D144" s="29" t="s">
         <v>541</v>
       </c>
-      <c r="E144" s="69" t="s">
+      <c r="E144" s="29" t="s">
         <v>542</v>
       </c>
-      <c r="F144" s="69" t="s">
+      <c r="F144" s="29" t="s">
         <v>543</v>
       </c>
-      <c r="G144" s="69" t="s">
+      <c r="G144" s="29" t="s">
         <v>544</v>
       </c>
-      <c r="H144" s="69" t="s">
+      <c r="H144" s="29" t="s">
         <v>545</v>
       </c>
-      <c r="I144" s="68" t="s">
+      <c r="I144" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="145" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A145" s="58">
+      <c r="A145" s="18">
         <v>144</v>
       </c>
-      <c r="B145" s="54" t="s">
+      <c r="B145" s="14" t="s">
         <v>524</v>
       </c>
-      <c r="C145" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D145" s="69" t="s">
+      <c r="C145" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D145" s="29" t="s">
         <v>546</v>
       </c>
-      <c r="E145" s="69" t="s">
+      <c r="E145" s="29" t="s">
         <v>547</v>
       </c>
-      <c r="F145" s="69" t="s">
+      <c r="F145" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="G145" s="69" t="s">
+      <c r="G145" s="29" t="s">
         <v>832</v>
       </c>
-      <c r="H145" s="69" t="s">
+      <c r="H145" s="29" t="s">
         <v>828</v>
       </c>
-      <c r="I145" s="68" t="s">
+      <c r="I145" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="146" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A146" s="58">
+      <c r="A146" s="18">
         <v>145</v>
       </c>
-      <c r="B146" s="54" t="s">
+      <c r="B146" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C146" s="69" t="s">
+      <c r="C146" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D146" s="69" t="s">
+      <c r="D146" s="29" t="s">
         <v>549</v>
       </c>
-      <c r="E146" s="69"/>
-      <c r="F146" s="69"/>
-      <c r="G146" s="69"/>
-      <c r="H146" s="69"/>
-      <c r="I146" s="68">
+      <c r="E146" s="29"/>
+      <c r="F146" s="29"/>
+      <c r="G146" s="29"/>
+      <c r="H146" s="29"/>
+      <c r="I146" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A147" s="58">
+      <c r="A147" s="18">
         <v>146</v>
       </c>
-      <c r="B147" s="54" t="s">
+      <c r="B147" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C147" s="69" t="s">
+      <c r="C147" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D147" s="69" t="s">
+      <c r="D147" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="E147" s="69"/>
-      <c r="F147" s="69"/>
-      <c r="G147" s="69"/>
-      <c r="H147" s="69"/>
-      <c r="I147" s="68">
+      <c r="E147" s="29"/>
+      <c r="F147" s="29"/>
+      <c r="G147" s="29"/>
+      <c r="H147" s="29"/>
+      <c r="I147" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A148" s="58">
+      <c r="A148" s="18">
         <v>147</v>
       </c>
-      <c r="B148" s="54" t="s">
+      <c r="B148" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C148" s="69" t="s">
+      <c r="C148" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D148" s="69" t="s">
+      <c r="D148" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="E148" s="69"/>
-      <c r="F148" s="69"/>
-      <c r="G148" s="69"/>
-      <c r="H148" s="69"/>
-      <c r="I148" s="68">
+      <c r="E148" s="29"/>
+      <c r="F148" s="29"/>
+      <c r="G148" s="29"/>
+      <c r="H148" s="29"/>
+      <c r="I148" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A149" s="58">
+      <c r="A149" s="18">
         <v>148</v>
       </c>
-      <c r="B149" s="54" t="s">
+      <c r="B149" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C149" s="69" t="s">
+      <c r="C149" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D149" s="69" t="s">
+      <c r="D149" s="29" t="s">
         <v>552</v>
       </c>
-      <c r="E149" s="69"/>
-      <c r="F149" s="69"/>
-      <c r="G149" s="69"/>
-      <c r="H149" s="69"/>
-      <c r="I149" s="68">
+      <c r="E149" s="29"/>
+      <c r="F149" s="29"/>
+      <c r="G149" s="29"/>
+      <c r="H149" s="29"/>
+      <c r="I149" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A150" s="58">
+      <c r="A150" s="18">
         <v>149</v>
       </c>
-      <c r="B150" s="54" t="s">
+      <c r="B150" s="14" t="s">
         <v>448</v>
       </c>
-      <c r="C150" s="69" t="s">
+      <c r="C150" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D150" s="69" t="s">
+      <c r="D150" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="E150" s="69"/>
-      <c r="F150" s="69"/>
-      <c r="G150" s="69"/>
-      <c r="H150" s="69"/>
-      <c r="I150" s="68">
+      <c r="E150" s="29"/>
+      <c r="F150" s="29"/>
+      <c r="G150" s="29"/>
+      <c r="H150" s="29"/>
+      <c r="I150" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A151" s="58">
+      <c r="A151" s="18">
         <v>150</v>
       </c>
-      <c r="B151" s="54" t="s">
+      <c r="B151" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C151" s="69" t="s">
+      <c r="C151" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D151" s="69" t="s">
+      <c r="D151" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="E151" s="69"/>
-      <c r="F151" s="69"/>
-      <c r="G151" s="69"/>
-      <c r="H151" s="69"/>
-      <c r="I151" s="69">
+      <c r="E151" s="29"/>
+      <c r="F151" s="29"/>
+      <c r="G151" s="29"/>
+      <c r="H151" s="29"/>
+      <c r="I151" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A152" s="58">
+      <c r="A152" s="18">
         <v>151</v>
       </c>
-      <c r="B152" s="54" t="s">
+      <c r="B152" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C152" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D152" s="69" t="s">
+      <c r="C152" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D152" s="29" t="s">
         <v>555</v>
       </c>
-      <c r="E152" s="69" t="s">
+      <c r="E152" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="F152" s="69" t="s">
+      <c r="F152" s="29" t="s">
         <v>557</v>
       </c>
-      <c r="G152" s="69" t="s">
+      <c r="G152" s="29" t="s">
         <v>558</v>
       </c>
-      <c r="H152" s="69" t="s">
+      <c r="H152" s="29" t="s">
         <v>559</v>
       </c>
-      <c r="I152" s="68" t="s">
+      <c r="I152" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A153" s="58">
+      <c r="A153" s="18">
         <v>152</v>
       </c>
-      <c r="B153" s="54" t="s">
+      <c r="B153" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C153" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D153" s="69" t="s">
+      <c r="C153" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D153" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="E153" s="69" t="s">
+      <c r="E153" s="29" t="s">
         <v>561</v>
       </c>
-      <c r="F153" s="69" t="s">
+      <c r="F153" s="29" t="s">
         <v>562</v>
       </c>
-      <c r="G153" s="69" t="s">
+      <c r="G153" s="29" t="s">
         <v>563</v>
       </c>
-      <c r="H153" s="69" t="s">
+      <c r="H153" s="29" t="s">
         <v>564</v>
       </c>
-      <c r="I153" s="68" t="s">
+      <c r="I153" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="154" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A154" s="58">
+      <c r="A154" s="18">
         <v>153</v>
       </c>
-      <c r="B154" s="54" t="s">
+      <c r="B154" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C154" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D154" s="69" t="s">
+      <c r="C154" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D154" s="29" t="s">
         <v>565</v>
       </c>
-      <c r="E154" s="69" t="s">
+      <c r="E154" s="29" t="s">
         <v>566</v>
       </c>
-      <c r="F154" s="69" t="s">
+      <c r="F154" s="29" t="s">
         <v>567</v>
       </c>
-      <c r="G154" s="69" t="s">
+      <c r="G154" s="29" t="s">
         <v>568</v>
       </c>
-      <c r="H154" s="69" t="s">
+      <c r="H154" s="29" t="s">
         <v>569</v>
       </c>
-      <c r="I154" s="68" t="s">
+      <c r="I154" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="155" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A155" s="58">
+      <c r="A155" s="18">
         <v>154</v>
       </c>
-      <c r="B155" s="54" t="s">
+      <c r="B155" s="14" t="s">
         <v>450</v>
       </c>
-      <c r="C155" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D155" s="69" t="s">
+      <c r="C155" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D155" s="29" t="s">
         <v>570</v>
       </c>
-      <c r="E155" s="69" t="s">
+      <c r="E155" s="29" t="s">
         <v>571</v>
       </c>
-      <c r="F155" s="69" t="s">
+      <c r="F155" s="29" t="s">
         <v>572</v>
       </c>
-      <c r="G155" s="69" t="s">
+      <c r="G155" s="29" t="s">
         <v>573</v>
       </c>
-      <c r="H155" s="69" t="s">
+      <c r="H155" s="29" t="s">
         <v>574</v>
       </c>
-      <c r="I155" s="68" t="s">
+      <c r="I155" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="156" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A156" s="58">
+      <c r="A156" s="18">
         <v>155</v>
       </c>
-      <c r="B156" s="54" t="s">
+      <c r="B156" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C156" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D156" s="69" t="s">
+      <c r="C156" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D156" s="29" t="s">
         <v>576</v>
       </c>
-      <c r="E156" s="69" t="s">
+      <c r="E156" s="29" t="s">
         <v>577</v>
       </c>
-      <c r="F156" s="69" t="s">
+      <c r="F156" s="29" t="s">
         <v>578</v>
       </c>
-      <c r="G156" s="69" t="s">
+      <c r="G156" s="29" t="s">
         <v>579</v>
       </c>
-      <c r="H156" s="69" t="s">
+      <c r="H156" s="29" t="s">
         <v>580</v>
       </c>
-      <c r="I156" s="68" t="s">
+      <c r="I156" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="157" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A157" s="58">
+      <c r="A157" s="18">
         <v>156</v>
       </c>
-      <c r="B157" s="54" t="s">
+      <c r="B157" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C157" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D157" s="69" t="s">
+      <c r="C157" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D157" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="E157" s="69" t="s">
+      <c r="E157" s="29" t="s">
         <v>582</v>
       </c>
-      <c r="F157" s="69" t="s">
+      <c r="F157" s="29" t="s">
         <v>583</v>
       </c>
-      <c r="G157" s="69" t="s">
+      <c r="G157" s="29" t="s">
         <v>584</v>
       </c>
-      <c r="H157" s="69" t="s">
+      <c r="H157" s="29" t="s">
         <v>585</v>
       </c>
-      <c r="I157" s="68" t="s">
+      <c r="I157" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="158" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A158" s="58">
+      <c r="A158" s="18">
         <v>157</v>
       </c>
-      <c r="B158" s="54" t="s">
+      <c r="B158" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C158" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D158" s="69" t="s">
+      <c r="C158" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D158" s="29" t="s">
         <v>586</v>
       </c>
-      <c r="E158" s="69" t="s">
+      <c r="E158" s="29" t="s">
         <v>587</v>
       </c>
-      <c r="F158" s="69" t="s">
+      <c r="F158" s="29" t="s">
         <v>588</v>
       </c>
-      <c r="G158" s="69" t="s">
+      <c r="G158" s="29" t="s">
         <v>589</v>
       </c>
-      <c r="H158" s="69" t="s">
+      <c r="H158" s="29" t="s">
         <v>590</v>
       </c>
-      <c r="I158" s="68" t="s">
+      <c r="I158" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="159" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A159" s="58">
+      <c r="A159" s="18">
         <v>158</v>
       </c>
-      <c r="B159" s="54" t="s">
+      <c r="B159" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C159" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D159" s="69" t="s">
+      <c r="C159" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D159" s="29" t="s">
         <v>591</v>
       </c>
-      <c r="E159" s="69" t="s">
+      <c r="E159" s="29" t="s">
         <v>592</v>
       </c>
-      <c r="F159" s="69" t="s">
+      <c r="F159" s="29" t="s">
         <v>593</v>
       </c>
-      <c r="G159" s="69" t="s">
+      <c r="G159" s="29" t="s">
         <v>594</v>
       </c>
-      <c r="H159" s="69" t="s">
+      <c r="H159" s="29" t="s">
         <v>595</v>
       </c>
-      <c r="I159" s="68" t="s">
+      <c r="I159" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="160" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A160" s="58">
+      <c r="A160" s="18">
         <v>159</v>
       </c>
-      <c r="B160" s="54" t="s">
+      <c r="B160" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C160" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D160" s="69" t="s">
+      <c r="C160" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D160" s="29" t="s">
         <v>596</v>
       </c>
-      <c r="E160" s="69" t="s">
+      <c r="E160" s="29" t="s">
         <v>597</v>
       </c>
-      <c r="F160" s="69" t="s">
+      <c r="F160" s="29" t="s">
         <v>598</v>
       </c>
-      <c r="G160" s="69" t="s">
+      <c r="G160" s="29" t="s">
         <v>599</v>
       </c>
-      <c r="H160" s="69" t="s">
+      <c r="H160" s="29" t="s">
         <v>600</v>
       </c>
-      <c r="I160" s="68" t="s">
+      <c r="I160" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="161" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A161" s="58">
+      <c r="A161" s="18">
         <v>160</v>
       </c>
-      <c r="B161" s="54" t="s">
+      <c r="B161" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C161" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D161" s="69" t="s">
+      <c r="C161" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D161" s="29" t="s">
         <v>601</v>
       </c>
-      <c r="E161" s="69" t="s">
+      <c r="E161" s="29" t="s">
         <v>602</v>
       </c>
-      <c r="F161" s="69" t="s">
+      <c r="F161" s="29" t="s">
         <v>603</v>
       </c>
-      <c r="G161" s="69" t="s">
+      <c r="G161" s="29" t="s">
         <v>604</v>
       </c>
-      <c r="H161" s="69" t="s">
+      <c r="H161" s="29" t="s">
         <v>605</v>
       </c>
-      <c r="I161" s="68" t="s">
+      <c r="I161" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="162" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A162" s="58">
+      <c r="A162" s="18">
         <v>161</v>
       </c>
-      <c r="B162" s="54" t="s">
+      <c r="B162" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C162" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D162" s="69" t="s">
+      <c r="C162" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D162" s="29" t="s">
         <v>606</v>
       </c>
-      <c r="E162" s="69" t="s">
+      <c r="E162" s="29" t="s">
         <v>607</v>
       </c>
-      <c r="F162" s="69" t="s">
+      <c r="F162" s="29" t="s">
         <v>608</v>
       </c>
-      <c r="G162" s="69" t="s">
+      <c r="G162" s="29" t="s">
         <v>609</v>
       </c>
-      <c r="H162" s="69" t="s">
+      <c r="H162" s="29" t="s">
         <v>610</v>
       </c>
-      <c r="I162" s="68" t="s">
+      <c r="I162" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A163" s="58">
+      <c r="A163" s="18">
         <v>162</v>
       </c>
-      <c r="B163" s="54" t="s">
+      <c r="B163" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C163" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D163" s="69" t="s">
+      <c r="C163" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D163" s="29" t="s">
         <v>611</v>
       </c>
-      <c r="E163" s="69" t="s">
+      <c r="E163" s="29" t="s">
         <v>612</v>
       </c>
-      <c r="F163" s="69" t="s">
+      <c r="F163" s="29" t="s">
         <v>613</v>
       </c>
-      <c r="G163" s="69" t="s">
+      <c r="G163" s="29" t="s">
         <v>614</v>
       </c>
-      <c r="H163" s="69" t="s">
+      <c r="H163" s="29" t="s">
         <v>615</v>
       </c>
-      <c r="I163" s="68" t="s">
+      <c r="I163" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="164" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A164" s="58">
+      <c r="A164" s="18">
         <v>163</v>
       </c>
-      <c r="B164" s="54" t="s">
+      <c r="B164" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C164" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D164" s="69" t="s">
+      <c r="C164" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D164" s="29" t="s">
         <v>616</v>
       </c>
-      <c r="E164" s="69" t="s">
+      <c r="E164" s="29" t="s">
         <v>617</v>
       </c>
-      <c r="F164" s="69" t="s">
+      <c r="F164" s="29" t="s">
         <v>618</v>
       </c>
-      <c r="G164" s="69" t="s">
+      <c r="G164" s="29" t="s">
         <v>619</v>
       </c>
-      <c r="H164" s="69" t="s">
+      <c r="H164" s="29" t="s">
         <v>620</v>
       </c>
-      <c r="I164" s="68" t="s">
+      <c r="I164" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A165" s="58">
+      <c r="A165" s="18">
         <v>164</v>
       </c>
-      <c r="B165" s="54" t="s">
+      <c r="B165" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C165" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D165" s="69" t="s">
+      <c r="C165" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D165" s="29" t="s">
         <v>621</v>
       </c>
-      <c r="E165" s="69" t="s">
+      <c r="E165" s="29" t="s">
         <v>622</v>
       </c>
-      <c r="F165" s="69" t="s">
+      <c r="F165" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="G165" s="69" t="s">
+      <c r="G165" s="29" t="s">
         <v>624</v>
       </c>
-      <c r="H165" s="69" t="s">
+      <c r="H165" s="29" t="s">
         <v>625</v>
       </c>
-      <c r="I165" s="68" t="s">
+      <c r="I165" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A166" s="58">
+      <c r="A166" s="18">
         <v>165</v>
       </c>
-      <c r="B166" s="54" t="s">
+      <c r="B166" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C166" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D166" s="69" t="s">
+      <c r="C166" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D166" s="29" t="s">
         <v>627</v>
       </c>
-      <c r="E166" s="69"/>
-      <c r="F166" s="69"/>
-      <c r="G166" s="69"/>
-      <c r="H166" s="69"/>
-      <c r="I166" s="68">
+      <c r="E166" s="29"/>
+      <c r="F166" s="29"/>
+      <c r="G166" s="29"/>
+      <c r="H166" s="29"/>
+      <c r="I166" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A167" s="58">
+      <c r="A167" s="18">
         <v>166</v>
       </c>
-      <c r="B167" s="54" t="s">
+      <c r="B167" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C167" s="69" t="s">
+      <c r="C167" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D167" s="69" t="s">
+      <c r="D167" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="E167" s="69"/>
-      <c r="F167" s="69"/>
-      <c r="G167" s="69"/>
-      <c r="H167" s="69"/>
-      <c r="I167" s="68">
+      <c r="E167" s="29"/>
+      <c r="F167" s="29"/>
+      <c r="G167" s="29"/>
+      <c r="H167" s="29"/>
+      <c r="I167" s="28">
         <v>0</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A168" s="58">
+      <c r="A168" s="18">
         <v>167</v>
       </c>
-      <c r="B168" s="54" t="s">
+      <c r="B168" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C168" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D168" s="69" t="s">
+      <c r="C168" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D168" s="29" t="s">
         <v>629</v>
       </c>
-      <c r="E168" s="69" t="s">
+      <c r="E168" s="29" t="s">
         <v>630</v>
       </c>
-      <c r="F168" s="69"/>
-      <c r="G168" s="69"/>
-      <c r="H168" s="69"/>
-      <c r="I168" s="68" t="s">
+      <c r="F168" s="29"/>
+      <c r="G168" s="29"/>
+      <c r="H168" s="29"/>
+      <c r="I168" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A169" s="58">
+      <c r="A169" s="18">
         <v>168</v>
       </c>
-      <c r="B169" s="54" t="s">
+      <c r="B169" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C169" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D169" s="69" t="s">
+      <c r="C169" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D169" s="29" t="s">
         <v>631</v>
       </c>
-      <c r="E169" s="69" t="s">
+      <c r="E169" s="29" t="s">
         <v>632</v>
       </c>
-      <c r="F169" s="69" t="s">
+      <c r="F169" s="29" t="s">
         <v>633</v>
       </c>
-      <c r="G169" s="69" t="s">
+      <c r="G169" s="29" t="s">
         <v>634</v>
       </c>
-      <c r="H169" s="69" t="s">
+      <c r="H169" s="29" t="s">
         <v>635</v>
       </c>
-      <c r="I169" s="68" t="s">
+      <c r="I169" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="170" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A170" s="58">
+      <c r="A170" s="18">
         <v>169</v>
       </c>
-      <c r="B170" s="54" t="s">
+      <c r="B170" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C170" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D170" s="69" t="s">
+      <c r="C170" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D170" s="29" t="s">
         <v>636</v>
       </c>
-      <c r="E170" s="69" t="s">
+      <c r="E170" s="29" t="s">
         <v>637</v>
       </c>
-      <c r="F170" s="69" t="s">
+      <c r="F170" s="29" t="s">
         <v>638</v>
       </c>
-      <c r="G170" s="69" t="s">
+      <c r="G170" s="29" t="s">
         <v>639</v>
       </c>
-      <c r="H170" s="69" t="s">
+      <c r="H170" s="29" t="s">
         <v>640</v>
       </c>
-      <c r="I170" s="68" t="s">
+      <c r="I170" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="171" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A171" s="58">
+      <c r="A171" s="18">
         <v>170</v>
       </c>
-      <c r="B171" s="54" t="s">
+      <c r="B171" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C171" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D171" s="69" t="s">
+      <c r="C171" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D171" s="29" t="s">
         <v>641</v>
       </c>
-      <c r="E171" s="69" t="s">
+      <c r="E171" s="29" t="s">
         <v>642</v>
       </c>
-      <c r="F171" s="69" t="s">
+      <c r="F171" s="29" t="s">
         <v>643</v>
       </c>
-      <c r="G171" s="69" t="s">
+      <c r="G171" s="29" t="s">
         <v>644</v>
       </c>
-      <c r="H171" s="69" t="s">
+      <c r="H171" s="29" t="s">
         <v>645</v>
       </c>
-      <c r="I171" s="68" t="s">
+      <c r="I171" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="172" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A172" s="58">
+      <c r="A172" s="18">
         <v>171</v>
       </c>
-      <c r="B172" s="54" t="s">
+      <c r="B172" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C172" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D172" s="69" t="s">
+      <c r="C172" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D172" s="29" t="s">
         <v>646</v>
       </c>
-      <c r="E172" s="69" t="s">
+      <c r="E172" s="29" t="s">
         <v>647</v>
       </c>
-      <c r="F172" s="69"/>
-      <c r="G172" s="69"/>
-      <c r="H172" s="69"/>
-      <c r="I172" s="68" t="s">
+      <c r="F172" s="29"/>
+      <c r="G172" s="29"/>
+      <c r="H172" s="29"/>
+      <c r="I172" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A173" s="58">
+      <c r="A173" s="18">
         <v>172</v>
       </c>
-      <c r="B173" s="54" t="s">
+      <c r="B173" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C173" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D173" s="69" t="s">
+      <c r="C173" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D173" s="29" t="s">
         <v>648</v>
       </c>
-      <c r="E173" s="69" t="s">
+      <c r="E173" s="29" t="s">
         <v>649</v>
       </c>
-      <c r="F173" s="69" t="s">
+      <c r="F173" s="29" t="s">
         <v>650</v>
       </c>
-      <c r="G173" s="69" t="s">
+      <c r="G173" s="29" t="s">
         <v>651</v>
       </c>
-      <c r="H173" s="69" t="s">
+      <c r="H173" s="29" t="s">
         <v>652</v>
       </c>
-      <c r="I173" s="68" t="s">
+      <c r="I173" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="174" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A174" s="58">
+      <c r="A174" s="18">
         <v>173</v>
       </c>
-      <c r="B174" s="54" t="s">
+      <c r="B174" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C174" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D174" s="69" t="s">
+      <c r="C174" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D174" s="29" t="s">
         <v>653</v>
       </c>
-      <c r="E174" s="69" t="s">
+      <c r="E174" s="29" t="s">
         <v>654</v>
       </c>
-      <c r="F174" s="69" t="s">
+      <c r="F174" s="29" t="s">
         <v>655</v>
       </c>
-      <c r="G174" s="69" t="s">
+      <c r="G174" s="29" t="s">
         <v>656</v>
       </c>
-      <c r="H174" s="69" t="s">
+      <c r="H174" s="29" t="s">
         <v>657</v>
       </c>
-      <c r="I174" s="68" t="s">
+      <c r="I174" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="175" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A175" s="58">
+      <c r="A175" s="18">
         <v>174</v>
       </c>
-      <c r="B175" s="54" t="s">
+      <c r="B175" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C175" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D175" s="69" t="s">
+      <c r="C175" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D175" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="E175" s="69" t="s">
+      <c r="E175" s="29" t="s">
         <v>659</v>
       </c>
-      <c r="F175" s="69" t="s">
+      <c r="F175" s="29" t="s">
         <v>660</v>
       </c>
-      <c r="G175" s="69" t="s">
+      <c r="G175" s="29" t="s">
         <v>661</v>
       </c>
-      <c r="H175" s="69" t="s">
+      <c r="H175" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="I175" s="68" t="s">
+      <c r="I175" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="176" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A176" s="58">
+      <c r="A176" s="18">
         <v>175</v>
       </c>
-      <c r="B176" s="54" t="s">
+      <c r="B176" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C176" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D176" s="69" t="s">
+      <c r="C176" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D176" s="29" t="s">
         <v>664</v>
       </c>
-      <c r="E176" s="69" t="s">
+      <c r="E176" s="29" t="s">
         <v>665</v>
       </c>
-      <c r="F176" s="69" t="s">
+      <c r="F176" s="29" t="s">
         <v>666</v>
       </c>
-      <c r="G176" s="69" t="s">
+      <c r="G176" s="29" t="s">
         <v>667</v>
       </c>
-      <c r="H176" s="69" t="s">
+      <c r="H176" s="29" t="s">
         <v>668</v>
       </c>
-      <c r="I176" s="68" t="s">
+      <c r="I176" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A177" s="58">
+      <c r="A177" s="18">
         <v>176</v>
       </c>
-      <c r="B177" s="54" t="s">
+      <c r="B177" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C177" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D177" s="69" t="s">
+      <c r="C177" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D177" s="29" t="s">
         <v>669</v>
       </c>
-      <c r="E177" s="69" t="s">
+      <c r="E177" s="29" t="s">
         <v>670</v>
       </c>
-      <c r="F177" s="69" t="s">
+      <c r="F177" s="29" t="s">
         <v>671</v>
       </c>
-      <c r="G177" s="69" t="s">
+      <c r="G177" s="29" t="s">
         <v>672</v>
       </c>
-      <c r="H177" s="69" t="s">
+      <c r="H177" s="29" t="s">
         <v>673</v>
       </c>
-      <c r="I177" s="68" t="s">
+      <c r="I177" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="178" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A178" s="58">
+      <c r="A178" s="18">
         <v>177</v>
       </c>
-      <c r="B178" s="54" t="s">
+      <c r="B178" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C178" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D178" s="69" t="s">
+      <c r="C178" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D178" s="29" t="s">
         <v>674</v>
       </c>
-      <c r="E178" s="69" t="s">
+      <c r="E178" s="29" t="s">
         <v>675</v>
       </c>
-      <c r="F178" s="69" t="s">
+      <c r="F178" s="29" t="s">
         <v>676</v>
       </c>
-      <c r="G178" s="69" t="s">
+      <c r="G178" s="29" t="s">
         <v>677</v>
       </c>
-      <c r="H178" s="69" t="s">
+      <c r="H178" s="29" t="s">
         <v>678</v>
       </c>
-      <c r="I178" s="68" t="s">
+      <c r="I178" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="179" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A179" s="58">
+      <c r="A179" s="18">
         <v>178</v>
       </c>
-      <c r="B179" s="54" t="s">
+      <c r="B179" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C179" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D179" s="69" t="s">
+      <c r="C179" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D179" s="29" t="s">
         <v>679</v>
       </c>
-      <c r="E179" s="69" t="s">
+      <c r="E179" s="29" t="s">
         <v>680</v>
       </c>
-      <c r="F179" s="69" t="s">
+      <c r="F179" s="29" t="s">
         <v>681</v>
       </c>
-      <c r="G179" s="69" t="s">
+      <c r="G179" s="29" t="s">
         <v>682</v>
       </c>
-      <c r="H179" s="69" t="s">
+      <c r="H179" s="29" t="s">
         <v>683</v>
       </c>
-      <c r="I179" s="68" t="s">
+      <c r="I179" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="180" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A180" s="58">
+      <c r="A180" s="18">
         <v>179</v>
       </c>
-      <c r="B180" s="54" t="s">
+      <c r="B180" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C180" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D180" s="69" t="s">
+      <c r="C180" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D180" s="29" t="s">
         <v>684</v>
       </c>
-      <c r="E180" s="69" t="s">
+      <c r="E180" s="29" t="s">
         <v>685</v>
       </c>
-      <c r="F180" s="69" t="s">
+      <c r="F180" s="29" t="s">
         <v>686</v>
       </c>
-      <c r="G180" s="69" t="s">
+      <c r="G180" s="29" t="s">
         <v>687</v>
       </c>
-      <c r="H180" s="69" t="s">
+      <c r="H180" s="29" t="s">
         <v>688</v>
       </c>
-      <c r="I180" s="68" t="s">
+      <c r="I180" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="181" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A181" s="58">
+      <c r="A181" s="18">
         <v>180</v>
       </c>
-      <c r="B181" s="54" t="s">
+      <c r="B181" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C181" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D181" s="69" t="s">
+      <c r="C181" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D181" s="29" t="s">
         <v>689</v>
       </c>
-      <c r="E181" s="69" t="s">
+      <c r="E181" s="29" t="s">
         <v>690</v>
       </c>
-      <c r="F181" s="69" t="s">
+      <c r="F181" s="29" t="s">
         <v>691</v>
       </c>
-      <c r="G181" s="69" t="s">
+      <c r="G181" s="29" t="s">
         <v>692</v>
       </c>
-      <c r="H181" s="69" t="s">
+      <c r="H181" s="29" t="s">
         <v>693</v>
       </c>
-      <c r="I181" s="68" t="s">
+      <c r="I181" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="182" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A182" s="58">
+      <c r="A182" s="18">
         <v>181</v>
       </c>
-      <c r="B182" s="54" t="s">
+      <c r="B182" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C182" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D182" s="69" t="s">
+      <c r="C182" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D182" s="29" t="s">
         <v>694</v>
       </c>
-      <c r="E182" s="69" t="s">
+      <c r="E182" s="29" t="s">
         <v>695</v>
       </c>
-      <c r="F182" s="69" t="s">
+      <c r="F182" s="29" t="s">
         <v>696</v>
       </c>
-      <c r="G182" s="69" t="s">
+      <c r="G182" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="H182" s="69" t="s">
+      <c r="H182" s="29" t="s">
         <v>698</v>
       </c>
-      <c r="I182" s="68" t="s">
+      <c r="I182" s="28" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="183" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A183" s="58">
+      <c r="A183" s="18">
         <v>182</v>
       </c>
-      <c r="B183" s="54" t="s">
+      <c r="B183" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C183" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D183" s="69" t="s">
+      <c r="C183" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D183" s="29" t="s">
         <v>699</v>
       </c>
-      <c r="E183" s="69" t="s">
+      <c r="E183" s="29" t="s">
         <v>700</v>
       </c>
-      <c r="F183" s="69" t="s">
+      <c r="F183" s="29" t="s">
         <v>701</v>
       </c>
-      <c r="G183" s="69" t="s">
+      <c r="G183" s="29" t="s">
         <v>702</v>
       </c>
-      <c r="H183" s="69" t="s">
+      <c r="H183" s="29" t="s">
         <v>703</v>
       </c>
-      <c r="I183" s="68" t="s">
+      <c r="I183" s="28" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="184" spans="1:9" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A184" s="58">
+      <c r="A184" s="18">
         <v>183</v>
       </c>
-      <c r="B184" s="54" t="s">
+      <c r="B184" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C184" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D184" s="69" t="s">
+      <c r="C184" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D184" s="29" t="s">
         <v>704</v>
       </c>
-      <c r="E184" s="69" t="s">
+      <c r="E184" s="29" t="s">
         <v>705</v>
       </c>
-      <c r="F184" s="69" t="s">
+      <c r="F184" s="29" t="s">
         <v>706</v>
       </c>
-      <c r="G184" s="69" t="s">
+      <c r="G184" s="29" t="s">
         <v>707</v>
       </c>
-      <c r="H184" s="69" t="s">
+      <c r="H184" s="29" t="s">
         <v>708</v>
       </c>
-      <c r="I184" s="68" t="s">
+      <c r="I184" s="28" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="185" spans="1:9" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="58">
+      <c r="A185" s="18">
         <v>184</v>
       </c>
-      <c r="B185" s="54" t="s">
+      <c r="B185" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="C185" s="69" t="s">
-        <v>1</v>
-      </c>
-      <c r="D185" s="69" t="s">
+      <c r="C185" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="D185" s="29" t="s">
         <v>709</v>
       </c>
-      <c r="E185" s="69" t="s">
+      <c r="E185" s="29" t="s">
         <v>710</v>
       </c>
-      <c r="F185" s="69" t="s">
+      <c r="F185" s="29" t="s">
         <v>711</v>
       </c>
-      <c r="G185" s="69" t="s">
+      <c r="G185" s="29" t="s">
         <v>712</v>
       </c>
-      <c r="H185" s="69" t="s">
+      <c r="H185" s="29" t="s">
         <v>713</v>
       </c>
-      <c r="I185" s="68" t="s">
+      <c r="I185" s="28" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="186" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A186" s="58">
+      <c r="A186" s="18">
         <v>185</v>
       </c>
-      <c r="B186" s="55" t="s">
+      <c r="B186" s="15" t="s">
         <v>714</v>
       </c>
-      <c r="C186" s="69" t="s">
+      <c r="C186" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D186" s="70" t="s">
+      <c r="D186" s="30" t="s">
         <v>715</v>
       </c>
-      <c r="E186" s="71"/>
-      <c r="F186" s="72"/>
-      <c r="G186" s="72"/>
-      <c r="H186" s="73"/>
-      <c r="I186" s="74">
+      <c r="E186" s="31"/>
+      <c r="F186" s="32"/>
+      <c r="G186" s="32"/>
+      <c r="H186" s="33"/>
+      <c r="I186" s="34">
         <v>1</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A187" s="58">
+      <c r="A187" s="18">
         <v>186</v>
       </c>
-      <c r="B187" s="56" t="s">
+      <c r="B187" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C187" s="69" t="s">
+      <c r="C187" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D187" s="75" t="s">
+      <c r="D187" s="35" t="s">
         <v>716</v>
       </c>
-      <c r="E187" s="76"/>
-      <c r="F187" s="77"/>
-      <c r="G187" s="77"/>
-      <c r="H187" s="78"/>
-      <c r="I187" s="79">
+      <c r="E187" s="36"/>
+      <c r="F187" s="37"/>
+      <c r="G187" s="37"/>
+      <c r="H187" s="38"/>
+      <c r="I187" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A188" s="58">
+      <c r="A188" s="18">
         <v>187</v>
       </c>
-      <c r="B188" s="56" t="s">
+      <c r="B188" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C188" s="69" t="s">
+      <c r="C188" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D188" s="75" t="s">
+      <c r="D188" s="35" t="s">
         <v>717</v>
       </c>
-      <c r="E188" s="80"/>
-      <c r="F188" s="81"/>
-      <c r="G188" s="81"/>
-      <c r="H188" s="82"/>
-      <c r="I188" s="79">
+      <c r="E188" s="40"/>
+      <c r="F188" s="41"/>
+      <c r="G188" s="41"/>
+      <c r="H188" s="42"/>
+      <c r="I188" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A189" s="58">
+      <c r="A189" s="18">
         <v>188</v>
       </c>
-      <c r="B189" s="56" t="s">
+      <c r="B189" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C189" s="69" t="s">
+      <c r="C189" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D189" s="75" t="s">
+      <c r="D189" s="35" t="s">
         <v>718</v>
       </c>
-      <c r="E189" s="80"/>
-      <c r="F189" s="81"/>
-      <c r="G189" s="81"/>
-      <c r="H189" s="82"/>
-      <c r="I189" s="79">
+      <c r="E189" s="40"/>
+      <c r="F189" s="41"/>
+      <c r="G189" s="41"/>
+      <c r="H189" s="42"/>
+      <c r="I189" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A190" s="58">
+      <c r="A190" s="18">
         <v>189</v>
       </c>
-      <c r="B190" s="56" t="s">
+      <c r="B190" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C190" s="69" t="s">
+      <c r="C190" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D190" s="75" t="s">
+      <c r="D190" s="35" t="s">
         <v>719</v>
       </c>
-      <c r="E190" s="80"/>
-      <c r="F190" s="81"/>
-      <c r="G190" s="81"/>
-      <c r="H190" s="82"/>
-      <c r="I190" s="79">
+      <c r="E190" s="40"/>
+      <c r="F190" s="41"/>
+      <c r="G190" s="41"/>
+      <c r="H190" s="42"/>
+      <c r="I190" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A191" s="58">
+      <c r="A191" s="18">
         <v>190</v>
       </c>
-      <c r="B191" s="56" t="s">
+      <c r="B191" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C191" s="83" t="s">
+      <c r="C191" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D191" s="75" t="s">
+      <c r="D191" s="35" t="s">
         <v>720</v>
       </c>
-      <c r="E191" s="75" t="s">
+      <c r="E191" s="35" t="s">
         <v>721</v>
       </c>
-      <c r="F191" s="75" t="s">
+      <c r="F191" s="35" t="s">
         <v>722</v>
       </c>
-      <c r="G191" s="75" t="s">
+      <c r="G191" s="35" t="s">
         <v>723</v>
       </c>
-      <c r="H191" s="75" t="s">
+      <c r="H191" s="35" t="s">
         <v>724</v>
       </c>
-      <c r="I191" s="79" t="s">
+      <c r="I191" s="39" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="192" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A192" s="58">
+      <c r="A192" s="18">
         <v>191</v>
       </c>
-      <c r="B192" s="56" t="s">
+      <c r="B192" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C192" s="83" t="s">
+      <c r="C192" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D192" s="75" t="s">
+      <c r="D192" s="35" t="s">
         <v>725</v>
       </c>
-      <c r="E192" s="75" t="s">
+      <c r="E192" s="35" t="s">
         <v>726</v>
       </c>
-      <c r="F192" s="75" t="s">
+      <c r="F192" s="35" t="s">
         <v>727</v>
       </c>
-      <c r="G192" s="75" t="s">
+      <c r="G192" s="35" t="s">
         <v>728</v>
       </c>
-      <c r="H192" s="75" t="s">
+      <c r="H192" s="35" t="s">
         <v>729</v>
       </c>
-      <c r="I192" s="79" t="s">
+      <c r="I192" s="39" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="193" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A193" s="58">
+      <c r="A193" s="18">
         <v>192</v>
       </c>
-      <c r="B193" s="56" t="s">
+      <c r="B193" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C193" s="83" t="s">
+      <c r="C193" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D193" s="75" t="s">
+      <c r="D193" s="35" t="s">
         <v>730</v>
       </c>
-      <c r="E193" s="75" t="s">
+      <c r="E193" s="35" t="s">
         <v>731</v>
       </c>
-      <c r="F193" s="75" t="s">
+      <c r="F193" s="35" t="s">
         <v>732</v>
       </c>
-      <c r="G193" s="75" t="s">
+      <c r="G193" s="35" t="s">
         <v>733</v>
       </c>
-      <c r="H193" s="75" t="s">
+      <c r="H193" s="35" t="s">
         <v>734</v>
       </c>
-      <c r="I193" s="79" t="s">
+      <c r="I193" s="39" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="194" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A194" s="58">
+      <c r="A194" s="18">
         <v>193</v>
       </c>
-      <c r="B194" s="56" t="s">
+      <c r="B194" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C194" s="83" t="s">
+      <c r="C194" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D194" s="75" t="s">
+      <c r="D194" s="35" t="s">
         <v>829</v>
       </c>
-      <c r="E194" s="75" t="s">
+      <c r="E194" s="35" t="s">
         <v>735</v>
       </c>
-      <c r="F194" s="75" t="s">
+      <c r="F194" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="G194" s="75" t="s">
+      <c r="G194" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="H194" s="75" t="s">
+      <c r="H194" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="I194" s="79" t="s">
+      <c r="I194" s="39" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A195" s="58">
+      <c r="A195" s="18">
         <v>194</v>
       </c>
-      <c r="B195" s="56" t="s">
+      <c r="B195" s="16" t="s">
         <v>714</v>
       </c>
-      <c r="C195" s="83" t="s">
+      <c r="C195" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D195" s="84" t="s">
+      <c r="D195" s="44" t="s">
         <v>739</v>
       </c>
-      <c r="E195" s="75" t="s">
+      <c r="E195" s="35" t="s">
         <v>740</v>
       </c>
-      <c r="F195" s="75" t="s">
+      <c r="F195" s="35" t="s">
         <v>741</v>
       </c>
-      <c r="G195" s="75" t="s">
+      <c r="G195" s="35" t="s">
         <v>742</v>
       </c>
-      <c r="H195" s="75" t="s">
+      <c r="H195" s="35" t="s">
         <v>743</v>
       </c>
-      <c r="I195" s="79" t="s">
+      <c r="I195" s="39" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A196" s="58">
+      <c r="A196" s="18">
         <v>195</v>
       </c>
-      <c r="B196" s="56" t="s">
+      <c r="B196" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C196" s="69" t="s">
+      <c r="C196" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D196" s="84" t="s">
+      <c r="D196" s="44" t="s">
         <v>745</v>
       </c>
-      <c r="E196" s="80"/>
-      <c r="F196" s="81"/>
-      <c r="G196" s="81"/>
-      <c r="H196" s="82"/>
-      <c r="I196" s="79">
+      <c r="E196" s="40"/>
+      <c r="F196" s="41"/>
+      <c r="G196" s="41"/>
+      <c r="H196" s="42"/>
+      <c r="I196" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A197" s="58">
+      <c r="A197" s="18">
         <v>196</v>
       </c>
-      <c r="B197" s="56" t="s">
+      <c r="B197" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C197" s="69" t="s">
+      <c r="C197" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D197" s="75" t="s">
+      <c r="D197" s="35" t="s">
         <v>717</v>
       </c>
-      <c r="E197" s="80"/>
-      <c r="F197" s="81"/>
-      <c r="G197" s="81"/>
-      <c r="H197" s="82"/>
-      <c r="I197" s="79">
+      <c r="E197" s="40"/>
+      <c r="F197" s="41"/>
+      <c r="G197" s="41"/>
+      <c r="H197" s="42"/>
+      <c r="I197" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A198" s="58">
+      <c r="A198" s="18">
         <v>197</v>
       </c>
-      <c r="B198" s="56" t="s">
+      <c r="B198" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C198" s="69" t="s">
+      <c r="C198" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D198" s="75" t="s">
+      <c r="D198" s="35" t="s">
         <v>746</v>
       </c>
-      <c r="E198" s="80"/>
-      <c r="F198" s="81"/>
-      <c r="G198" s="81"/>
-      <c r="H198" s="82"/>
-      <c r="I198" s="79">
+      <c r="E198" s="40"/>
+      <c r="F198" s="41"/>
+      <c r="G198" s="41"/>
+      <c r="H198" s="42"/>
+      <c r="I198" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A199" s="58">
+      <c r="A199" s="18">
         <v>198</v>
       </c>
-      <c r="B199" s="56" t="s">
+      <c r="B199" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C199" s="69" t="s">
+      <c r="C199" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D199" s="75" t="s">
+      <c r="D199" s="35" t="s">
         <v>747</v>
       </c>
-      <c r="E199" s="80"/>
-      <c r="F199" s="81"/>
-      <c r="G199" s="81"/>
-      <c r="H199" s="82"/>
-      <c r="I199" s="79">
+      <c r="E199" s="40"/>
+      <c r="F199" s="41"/>
+      <c r="G199" s="41"/>
+      <c r="H199" s="42"/>
+      <c r="I199" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A200" s="58">
+      <c r="A200" s="18">
         <v>199</v>
       </c>
-      <c r="B200" s="56" t="s">
+      <c r="B200" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C200" s="83" t="s">
+      <c r="C200" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D200" s="85" t="s">
+      <c r="D200" s="45" t="s">
         <v>748</v>
       </c>
-      <c r="E200" s="80"/>
-      <c r="F200" s="81"/>
-      <c r="G200" s="81"/>
-      <c r="H200" s="82"/>
-      <c r="I200" s="79">
+      <c r="E200" s="40"/>
+      <c r="F200" s="41"/>
+      <c r="G200" s="41"/>
+      <c r="H200" s="42"/>
+      <c r="I200" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A201" s="58">
+      <c r="A201" s="18">
         <v>200</v>
       </c>
-      <c r="B201" s="56" t="s">
+      <c r="B201" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C201" s="83" t="s">
+      <c r="C201" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D201" s="75" t="s">
+      <c r="D201" s="35" t="s">
         <v>749</v>
       </c>
-      <c r="E201" s="75" t="s">
+      <c r="E201" s="35" t="s">
         <v>750</v>
       </c>
-      <c r="F201" s="75" t="s">
+      <c r="F201" s="35" t="s">
         <v>751</v>
       </c>
-      <c r="G201" s="75" t="s">
+      <c r="G201" s="35" t="s">
         <v>752</v>
       </c>
-      <c r="H201" s="75" t="s">
+      <c r="H201" s="35" t="s">
         <v>753</v>
       </c>
-      <c r="I201" s="79" t="s">
+      <c r="I201" s="39" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="202" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A202" s="58">
+      <c r="A202" s="18">
         <v>201</v>
       </c>
-      <c r="B202" s="56" t="s">
+      <c r="B202" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C202" s="83" t="s">
+      <c r="C202" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D202" s="75" t="s">
+      <c r="D202" s="35" t="s">
         <v>754</v>
       </c>
-      <c r="E202" s="75" t="s">
+      <c r="E202" s="35" t="s">
         <v>755</v>
       </c>
-      <c r="F202" s="75" t="s">
+      <c r="F202" s="35" t="s">
         <v>756</v>
       </c>
-      <c r="G202" s="75" t="s">
+      <c r="G202" s="35" t="s">
         <v>757</v>
       </c>
-      <c r="H202" s="75" t="s">
+      <c r="H202" s="35" t="s">
         <v>758</v>
       </c>
-      <c r="I202" s="79" t="s">
+      <c r="I202" s="39" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A203" s="58">
+      <c r="A203" s="18">
         <v>202</v>
       </c>
-      <c r="B203" s="56" t="s">
+      <c r="B203" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C203" s="83" t="s">
+      <c r="C203" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D203" s="85" t="s">
+      <c r="D203" s="45" t="s">
         <v>759</v>
       </c>
-      <c r="E203" s="75" t="s">
+      <c r="E203" s="35" t="s">
         <v>760</v>
       </c>
-      <c r="F203" s="75" t="s">
+      <c r="F203" s="35" t="s">
         <v>761</v>
       </c>
-      <c r="G203" s="75" t="s">
+      <c r="G203" s="35" t="s">
         <v>762</v>
       </c>
-      <c r="H203" s="75" t="s">
+      <c r="H203" s="35" t="s">
         <v>763</v>
       </c>
-      <c r="I203" s="86" t="s">
+      <c r="I203" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A204" s="58">
+      <c r="A204" s="18">
         <v>203</v>
       </c>
-      <c r="B204" s="56" t="s">
+      <c r="B204" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C204" s="83" t="s">
+      <c r="C204" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D204" s="85" t="s">
+      <c r="D204" s="45" t="s">
         <v>764</v>
       </c>
-      <c r="E204" s="75" t="s">
+      <c r="E204" s="35" t="s">
         <v>765</v>
       </c>
-      <c r="F204" s="75" t="s">
+      <c r="F204" s="35" t="s">
         <v>766</v>
       </c>
-      <c r="G204" s="75" t="s">
+      <c r="G204" s="35" t="s">
         <v>767</v>
       </c>
-      <c r="H204" s="75" t="s">
+      <c r="H204" s="35" t="s">
         <v>768</v>
       </c>
-      <c r="I204" s="86" t="s">
+      <c r="I204" s="46" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="205" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A205" s="58">
+      <c r="A205" s="18">
         <v>204</v>
       </c>
-      <c r="B205" s="56" t="s">
+      <c r="B205" s="16" t="s">
         <v>744</v>
       </c>
-      <c r="C205" s="83" t="s">
+      <c r="C205" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D205" s="85" t="s">
+      <c r="D205" s="45" t="s">
         <v>769</v>
       </c>
-      <c r="E205" s="75" t="s">
+      <c r="E205" s="35" t="s">
         <v>770</v>
       </c>
-      <c r="F205" s="75" t="s">
+      <c r="F205" s="35" t="s">
         <v>771</v>
       </c>
-      <c r="G205" s="75" t="s">
+      <c r="G205" s="35" t="s">
         <v>772</v>
       </c>
-      <c r="H205" s="75" t="s">
+      <c r="H205" s="35" t="s">
         <v>773</v>
       </c>
-      <c r="I205" s="79" t="s">
+      <c r="I205" s="39" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A206" s="58">
+      <c r="A206" s="18">
         <v>205</v>
       </c>
-      <c r="B206" s="56" t="s">
+      <c r="B206" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C206" s="69" t="s">
+      <c r="C206" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D206" s="75" t="s">
+      <c r="D206" s="35" t="s">
         <v>775</v>
       </c>
-      <c r="E206" s="80"/>
-      <c r="F206" s="81"/>
-      <c r="G206" s="81"/>
-      <c r="H206" s="82"/>
-      <c r="I206" s="79">
+      <c r="E206" s="40"/>
+      <c r="F206" s="41"/>
+      <c r="G206" s="41"/>
+      <c r="H206" s="42"/>
+      <c r="I206" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A207" s="58">
+      <c r="A207" s="18">
         <v>206</v>
       </c>
-      <c r="B207" s="56" t="s">
+      <c r="B207" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C207" s="69" t="s">
+      <c r="C207" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D207" s="75" t="s">
+      <c r="D207" s="35" t="s">
         <v>830</v>
       </c>
-      <c r="E207" s="80"/>
-      <c r="F207" s="81"/>
-      <c r="G207" s="81"/>
-      <c r="H207" s="82"/>
-      <c r="I207" s="79">
+      <c r="E207" s="40"/>
+      <c r="F207" s="41"/>
+      <c r="G207" s="41"/>
+      <c r="H207" s="42"/>
+      <c r="I207" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A208" s="58">
+      <c r="A208" s="18">
         <v>207</v>
       </c>
-      <c r="B208" s="56" t="s">
+      <c r="B208" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C208" s="69" t="s">
+      <c r="C208" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D208" s="85" t="s">
+      <c r="D208" s="45" t="s">
         <v>776</v>
       </c>
-      <c r="E208" s="80"/>
-      <c r="F208" s="81"/>
-      <c r="G208" s="81"/>
-      <c r="H208" s="82"/>
-      <c r="I208" s="79">
+      <c r="E208" s="40"/>
+      <c r="F208" s="41"/>
+      <c r="G208" s="41"/>
+      <c r="H208" s="42"/>
+      <c r="I208" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A209" s="58">
+      <c r="A209" s="18">
         <v>208</v>
       </c>
-      <c r="B209" s="56" t="s">
+      <c r="B209" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C209" s="69" t="s">
+      <c r="C209" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D209" s="75" t="s">
+      <c r="D209" s="35" t="s">
         <v>777</v>
       </c>
-      <c r="E209" s="80"/>
-      <c r="F209" s="81"/>
-      <c r="G209" s="81"/>
-      <c r="H209" s="82"/>
-      <c r="I209" s="79">
+      <c r="E209" s="40"/>
+      <c r="F209" s="41"/>
+      <c r="G209" s="41"/>
+      <c r="H209" s="42"/>
+      <c r="I209" s="39">
         <v>1</v>
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A210" s="58">
+      <c r="A210" s="18">
         <v>209</v>
       </c>
-      <c r="B210" s="56" t="s">
+      <c r="B210" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C210" s="69" t="s">
+      <c r="C210" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D210" s="84" t="s">
+      <c r="D210" s="44" t="s">
         <v>778</v>
       </c>
-      <c r="E210" s="80"/>
-      <c r="F210" s="81"/>
-      <c r="G210" s="81"/>
-      <c r="H210" s="82"/>
-      <c r="I210" s="79">
+      <c r="E210" s="40"/>
+      <c r="F210" s="41"/>
+      <c r="G210" s="41"/>
+      <c r="H210" s="42"/>
+      <c r="I210" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A211" s="58">
+      <c r="A211" s="18">
         <v>210</v>
       </c>
-      <c r="B211" s="56" t="s">
+      <c r="B211" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C211" s="83" t="s">
+      <c r="C211" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D211" s="75" t="s">
+      <c r="D211" s="35" t="s">
         <v>779</v>
       </c>
-      <c r="E211" s="75" t="s">
+      <c r="E211" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="F211" s="75" t="s">
+      <c r="F211" s="35" t="s">
         <v>780</v>
       </c>
-      <c r="G211" s="75" t="s">
+      <c r="G211" s="35" t="s">
         <v>781</v>
       </c>
-      <c r="H211" s="75" t="s">
+      <c r="H211" s="35" t="s">
         <v>782</v>
       </c>
-      <c r="I211" s="86" t="s">
+      <c r="I211" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="212" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A212" s="58">
+      <c r="A212" s="18">
         <v>211</v>
       </c>
-      <c r="B212" s="56" t="s">
+      <c r="B212" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C212" s="83" t="s">
+      <c r="C212" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D212" s="85" t="s">
+      <c r="D212" s="45" t="s">
         <v>783</v>
       </c>
-      <c r="E212" s="75" t="s">
+      <c r="E212" s="35" t="s">
         <v>784</v>
       </c>
-      <c r="F212" s="75" t="s">
+      <c r="F212" s="35" t="s">
         <v>785</v>
       </c>
-      <c r="G212" s="75" t="s">
+      <c r="G212" s="35" t="s">
         <v>786</v>
       </c>
-      <c r="H212" s="75" t="s">
+      <c r="H212" s="35" t="s">
         <v>787</v>
       </c>
-      <c r="I212" s="86" t="s">
+      <c r="I212" s="46" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A213" s="58">
+      <c r="A213" s="18">
         <v>212</v>
       </c>
-      <c r="B213" s="56" t="s">
+      <c r="B213" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C213" s="83" t="s">
+      <c r="C213" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D213" s="85" t="s">
+      <c r="D213" s="45" t="s">
         <v>788</v>
       </c>
-      <c r="E213" s="75" t="s">
+      <c r="E213" s="35" t="s">
         <v>789</v>
       </c>
-      <c r="F213" s="84" t="s">
+      <c r="F213" s="44" t="s">
         <v>790</v>
       </c>
-      <c r="G213" s="75" t="s">
+      <c r="G213" s="35" t="s">
         <v>791</v>
       </c>
-      <c r="H213" s="75" t="s">
+      <c r="H213" s="35" t="s">
         <v>792</v>
       </c>
-      <c r="I213" s="86" t="s">
+      <c r="I213" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A214" s="58">
+      <c r="A214" s="18">
         <v>213</v>
       </c>
-      <c r="B214" s="56" t="s">
+      <c r="B214" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C214" s="83" t="s">
+      <c r="C214" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D214" s="75" t="s">
+      <c r="D214" s="35" t="s">
         <v>793</v>
       </c>
-      <c r="E214" s="75" t="s">
+      <c r="E214" s="35" t="s">
         <v>794</v>
       </c>
-      <c r="F214" s="75" t="s">
+      <c r="F214" s="35" t="s">
         <v>795</v>
       </c>
-      <c r="G214" s="75" t="s">
+      <c r="G214" s="35" t="s">
         <v>796</v>
       </c>
-      <c r="H214" s="75" t="s">
+      <c r="H214" s="35" t="s">
         <v>797</v>
       </c>
-      <c r="I214" s="86" t="s">
+      <c r="I214" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A215" s="58">
+      <c r="A215" s="18">
         <v>214</v>
       </c>
-      <c r="B215" s="56" t="s">
+      <c r="B215" s="16" t="s">
         <v>774</v>
       </c>
-      <c r="C215" s="83" t="s">
+      <c r="C215" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D215" s="85" t="s">
+      <c r="D215" s="45" t="s">
         <v>798</v>
       </c>
-      <c r="E215" s="75" t="s">
+      <c r="E215" s="35" t="s">
         <v>799</v>
       </c>
-      <c r="F215" s="75" t="s">
+      <c r="F215" s="35" t="s">
         <v>800</v>
       </c>
-      <c r="G215" s="75" t="s">
+      <c r="G215" s="35" t="s">
         <v>801</v>
       </c>
-      <c r="H215" s="75" t="s">
+      <c r="H215" s="35" t="s">
         <v>743</v>
       </c>
-      <c r="I215" s="86" t="s">
+      <c r="I215" s="46" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A216" s="58">
+      <c r="A216" s="18">
         <v>215</v>
       </c>
-      <c r="B216" s="56" t="s">
+      <c r="B216" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C216" s="69" t="s">
+      <c r="C216" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D216" s="75" t="s">
+      <c r="D216" s="35" t="s">
         <v>803</v>
       </c>
-      <c r="E216" s="80"/>
-      <c r="F216" s="81"/>
-      <c r="G216" s="81"/>
-      <c r="H216" s="82"/>
-      <c r="I216" s="87">
+      <c r="E216" s="40"/>
+      <c r="F216" s="41"/>
+      <c r="G216" s="41"/>
+      <c r="H216" s="42"/>
+      <c r="I216" s="47">
         <v>1</v>
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A217" s="58">
+      <c r="A217" s="18">
         <v>216</v>
       </c>
-      <c r="B217" s="56" t="s">
+      <c r="B217" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C217" s="69" t="s">
+      <c r="C217" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D217" s="75" t="s">
+      <c r="D217" s="35" t="s">
         <v>804</v>
       </c>
-      <c r="E217" s="80"/>
-      <c r="F217" s="81"/>
-      <c r="G217" s="81"/>
-      <c r="H217" s="82"/>
-      <c r="I217" s="79">
+      <c r="E217" s="40"/>
+      <c r="F217" s="41"/>
+      <c r="G217" s="41"/>
+      <c r="H217" s="42"/>
+      <c r="I217" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A218" s="58">
+      <c r="A218" s="18">
         <v>217</v>
       </c>
-      <c r="B218" s="56" t="s">
+      <c r="B218" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C218" s="69" t="s">
+      <c r="C218" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D218" s="75" t="s">
+      <c r="D218" s="35" t="s">
         <v>805</v>
       </c>
-      <c r="E218" s="80"/>
-      <c r="F218" s="81"/>
-      <c r="G218" s="81"/>
-      <c r="H218" s="82"/>
-      <c r="I218" s="87">
+      <c r="E218" s="40"/>
+      <c r="F218" s="41"/>
+      <c r="G218" s="41"/>
+      <c r="H218" s="42"/>
+      <c r="I218" s="47">
         <v>1</v>
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A219" s="58">
+      <c r="A219" s="18">
         <v>218</v>
       </c>
-      <c r="B219" s="56" t="s">
+      <c r="B219" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C219" s="69" t="s">
+      <c r="C219" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D219" s="75" t="s">
+      <c r="D219" s="35" t="s">
         <v>719</v>
       </c>
-      <c r="E219" s="80"/>
-      <c r="F219" s="81"/>
-      <c r="G219" s="81"/>
-      <c r="H219" s="82"/>
-      <c r="I219" s="79">
+      <c r="E219" s="40"/>
+      <c r="F219" s="41"/>
+      <c r="G219" s="41"/>
+      <c r="H219" s="42"/>
+      <c r="I219" s="39">
         <v>0</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A220" s="58">
+      <c r="A220" s="18">
         <v>219</v>
       </c>
-      <c r="B220" s="56" t="s">
+      <c r="B220" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C220" s="69" t="s">
+      <c r="C220" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="D220" s="75" t="s">
+      <c r="D220" s="35" t="s">
         <v>806</v>
       </c>
-      <c r="E220" s="80"/>
-      <c r="F220" s="81"/>
-      <c r="G220" s="81"/>
-      <c r="H220" s="82"/>
-      <c r="I220" s="87">
+      <c r="E220" s="40"/>
+      <c r="F220" s="41"/>
+      <c r="G220" s="41"/>
+      <c r="H220" s="42"/>
+      <c r="I220" s="47">
         <v>1</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A221" s="58">
+      <c r="A221" s="18">
         <v>220</v>
       </c>
-      <c r="B221" s="56" t="s">
+      <c r="B221" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C221" s="83" t="s">
+      <c r="C221" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D221" s="85" t="s">
+      <c r="D221" s="45" t="s">
         <v>807</v>
       </c>
-      <c r="E221" s="75" t="s">
+      <c r="E221" s="35" t="s">
         <v>808</v>
       </c>
-      <c r="F221" s="75" t="s">
+      <c r="F221" s="35" t="s">
         <v>809</v>
       </c>
-      <c r="G221" s="75" t="s">
+      <c r="G221" s="35" t="s">
         <v>810</v>
       </c>
-      <c r="H221" s="75" t="s">
+      <c r="H221" s="35" t="s">
         <v>811</v>
       </c>
-      <c r="I221" s="86" t="s">
+      <c r="I221" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="222" spans="1:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="A222" s="58">
+      <c r="A222" s="18">
         <v>221</v>
       </c>
-      <c r="B222" s="56" t="s">
+      <c r="B222" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C222" s="83" t="s">
+      <c r="C222" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D222" s="75" t="s">
+      <c r="D222" s="35" t="s">
         <v>829</v>
       </c>
-      <c r="E222" s="75" t="s">
+      <c r="E222" s="35" t="s">
         <v>735</v>
       </c>
-      <c r="F222" s="75" t="s">
+      <c r="F222" s="35" t="s">
         <v>736</v>
       </c>
-      <c r="G222" s="75" t="s">
+      <c r="G222" s="35" t="s">
         <v>737</v>
       </c>
-      <c r="H222" s="75" t="s">
+      <c r="H222" s="35" t="s">
         <v>738</v>
       </c>
-      <c r="I222" s="86" t="s">
+      <c r="I222" s="46" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="223" spans="1:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="A223" s="58">
+      <c r="A223" s="18">
         <v>222</v>
       </c>
-      <c r="B223" s="56" t="s">
+      <c r="B223" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C223" s="83" t="s">
+      <c r="C223" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D223" s="88" t="s">
+      <c r="D223" s="48" t="s">
         <v>812</v>
       </c>
-      <c r="E223" s="75" t="s">
+      <c r="E223" s="35" t="s">
         <v>813</v>
       </c>
-      <c r="F223" s="75" t="s">
+      <c r="F223" s="35" t="s">
         <v>43</v>
       </c>
-      <c r="G223" s="75" t="s">
+      <c r="G223" s="35" t="s">
         <v>814</v>
       </c>
-      <c r="H223" s="75" t="s">
+      <c r="H223" s="35" t="s">
         <v>815</v>
       </c>
-      <c r="I223" s="86" t="s">
+      <c r="I223" s="46" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="224" spans="1:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="A224" s="58">
+      <c r="A224" s="18">
         <v>223</v>
       </c>
-      <c r="B224" s="56" t="s">
+      <c r="B224" s="16" t="s">
         <v>802</v>
       </c>
-      <c r="C224" s="83" t="s">
+      <c r="C224" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D224" s="75" t="s">
+      <c r="D224" s="35" t="s">
         <v>816</v>
       </c>
-      <c r="E224" s="75" t="s">
+      <c r="E224" s="35" t="s">
         <v>817</v>
       </c>
-      <c r="F224" s="75" t="s">
+      <c r="F224" s="35" t="s">
         <v>818</v>
       </c>
-      <c r="G224" s="75" t="s">
+      <c r="G224" s="35" t="s">
         <v>819</v>
       </c>
-      <c r="H224" s="75" t="s">
+      <c r="H224" s="35" t="s">
         <v>820</v>
       </c>
-      <c r="I224" s="86" t="s">
+      <c r="I224" s="46" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="225" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A225" s="58">
+      <c r="A225" s="18">
         <v>224</v>
       </c>
-      <c r="B225" s="57" t="s">
+      <c r="B225" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="C225" s="83" t="s">
+      <c r="C225" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="D225" s="89" t="s">
+      <c r="D225" s="49" t="s">
         <v>821</v>
       </c>
-      <c r="E225" s="90" t="s">
+      <c r="E225" s="50" t="s">
         <v>822</v>
       </c>
-      <c r="F225" s="90" t="s">
+      <c r="F225" s="50" t="s">
         <v>823</v>
       </c>
-      <c r="G225" s="90" t="s">
+      <c r="G225" s="50" t="s">
         <v>824</v>
       </c>
-      <c r="H225" s="90" t="s">
+      <c r="H225" s="50" t="s">
         <v>825</v>
       </c>
-      <c r="I225" s="86" t="s">
+      <c r="I225" s="46" t="s">
         <v>123</v>
       </c>
     </row>
@@ -9700,1142 +9520,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7647C3D1-58C9-43F2-B348-2D14EF2C2105}">
-  <dimension ref="A2:H111"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.85546875" customWidth="1"/>
-    <col min="3" max="3" width="58.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6"/>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="94"/>
-      <c r="E3" s="94"/>
-      <c r="F3" s="94"/>
-      <c r="G3" s="94"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="93"/>
-      <c r="E4" s="93"/>
-      <c r="F4" s="93"/>
-      <c r="G4" s="93"/>
-      <c r="H4" s="5"/>
-    </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="11"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="94"/>
-      <c r="E5" s="94"/>
-      <c r="F5" s="94"/>
-      <c r="G5" s="94"/>
-      <c r="H5" s="8"/>
-    </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="93"/>
-      <c r="E6" s="93"/>
-      <c r="F6" s="93"/>
-      <c r="G6" s="93"/>
-      <c r="H6" s="5"/>
-    </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="8"/>
-    </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="5"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="10"/>
-    </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="8"/>
-    </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="8"/>
-    </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="5"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-      <c r="G12" s="5"/>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="8"/>
-    </row>
-    <row r="14" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="6"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="8"/>
-    </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="10"/>
-    </row>
-    <row r="17" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="8"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="5"/>
-      <c r="H18" s="10"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="8"/>
-    </row>
-    <row r="20" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="10"/>
-    </row>
-    <row r="21" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="8"/>
-    </row>
-    <row r="22" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="91"/>
-      <c r="E22" s="91"/>
-      <c r="F22" s="91"/>
-      <c r="G22" s="91"/>
-      <c r="H22" s="10"/>
-    </row>
-    <row r="23" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="92"/>
-      <c r="E23" s="92"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="92"/>
-      <c r="H23" s="8"/>
-    </row>
-    <row r="24" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="10"/>
-    </row>
-    <row r="25" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="92"/>
-      <c r="E25" s="92"/>
-      <c r="F25" s="92"/>
-      <c r="G25" s="92"/>
-      <c r="H25" s="8"/>
-    </row>
-    <row r="26" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="91"/>
-      <c r="E26" s="91"/>
-      <c r="F26" s="91"/>
-      <c r="G26" s="91"/>
-      <c r="H26" s="5"/>
-    </row>
-    <row r="27" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="8"/>
-    </row>
-    <row r="28" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
-      <c r="H28" s="10"/>
-    </row>
-    <row r="29" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="8"/>
-    </row>
-    <row r="30" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
-      <c r="H30" s="10"/>
-    </row>
-    <row r="31" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="8"/>
-    </row>
-    <row r="32" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="10"/>
-    </row>
-    <row r="33" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="92"/>
-      <c r="E33" s="92"/>
-      <c r="F33" s="92"/>
-      <c r="G33" s="92"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="5"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="91"/>
-      <c r="E34" s="91"/>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="10"/>
-    </row>
-    <row r="35" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A35" s="6"/>
-      <c r="B35" s="7"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="92"/>
-      <c r="H35" s="8"/>
-    </row>
-    <row r="36" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="5"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="91"/>
-      <c r="E36" s="91"/>
-      <c r="F36" s="91"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="10"/>
-    </row>
-    <row r="37" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A37" s="6"/>
-      <c r="B37" s="7"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="92"/>
-      <c r="E37" s="92"/>
-      <c r="F37" s="92"/>
-      <c r="G37" s="92"/>
-      <c r="H37" s="7"/>
-    </row>
-    <row r="38" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="5"/>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-      <c r="F38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="10"/>
-    </row>
-    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="6"/>
-      <c r="B39" s="7"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="8"/>
-    </row>
-    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
-      <c r="D40" s="5"/>
-      <c r="E40" s="5"/>
-      <c r="F40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="10"/>
-    </row>
-    <row r="41" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A41" s="6"/>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="8"/>
-    </row>
-    <row r="42" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A42" s="4"/>
-      <c r="B42" s="5"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="5"/>
-      <c r="E42" s="5"/>
-      <c r="F42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="10"/>
-    </row>
-    <row r="43" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A43" s="6"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="8"/>
-    </row>
-    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
-      <c r="B44" s="5"/>
-      <c r="C44" s="5"/>
-      <c r="D44" s="5"/>
-      <c r="E44" s="5"/>
-      <c r="F44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="10"/>
-    </row>
-    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A45" s="6"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="8"/>
-    </row>
-    <row r="46" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="5"/>
-      <c r="C46" s="5"/>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5"/>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5"/>
-      <c r="H46" s="10"/>
-    </row>
-    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A47" s="6"/>
-      <c r="B47" s="7"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="8"/>
-    </row>
-    <row r="48" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A48" s="4"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="5"/>
-      <c r="E48" s="5"/>
-      <c r="F48" s="5"/>
-      <c r="G48" s="5"/>
-      <c r="H48" s="10"/>
-    </row>
-    <row r="49" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A49" s="6"/>
-      <c r="B49" s="7"/>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="8"/>
-    </row>
-    <row r="50" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A50" s="4"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="5"/>
-      <c r="E50" s="5"/>
-      <c r="F50" s="5"/>
-      <c r="G50" s="5"/>
-      <c r="H50" s="10"/>
-    </row>
-    <row r="51" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A51" s="6"/>
-      <c r="B51" s="7"/>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="8"/>
-    </row>
-    <row r="52" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A52" s="12"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="91"/>
-      <c r="E52" s="91"/>
-      <c r="F52" s="91"/>
-      <c r="G52" s="91"/>
-      <c r="H52" s="10"/>
-    </row>
-    <row r="53" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
-      <c r="B53" s="7"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="92"/>
-      <c r="E53" s="92"/>
-      <c r="F53" s="92"/>
-      <c r="G53" s="92"/>
-      <c r="H53" s="8"/>
-    </row>
-    <row r="54" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A54" s="12"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="5"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="5"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="10"/>
-    </row>
-    <row r="55" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="7"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="7"/>
-      <c r="G55" s="7"/>
-      <c r="H55" s="8"/>
-    </row>
-    <row r="56" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A56" s="12"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-      <c r="F56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="10"/>
-    </row>
-    <row r="57" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
-      <c r="F57" s="7"/>
-      <c r="G57" s="7"/>
-      <c r="H57" s="8"/>
-    </row>
-    <row r="58" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="12"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="5"/>
-      <c r="E58" s="5"/>
-      <c r="F58" s="5"/>
-      <c r="G58" s="5"/>
-      <c r="H58" s="10"/>
-    </row>
-    <row r="59" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="7"/>
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
-      <c r="F59" s="7"/>
-      <c r="G59" s="7"/>
-      <c r="H59" s="8"/>
-    </row>
-    <row r="60" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="12"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="5"/>
-      <c r="E60" s="5"/>
-      <c r="F60" s="5"/>
-      <c r="G60" s="5"/>
-      <c r="H60" s="10"/>
-    </row>
-    <row r="61" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="7"/>
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
-      <c r="F61" s="7"/>
-      <c r="G61" s="7"/>
-      <c r="H61" s="8"/>
-    </row>
-    <row r="62" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A62" s="12"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="10"/>
-    </row>
-    <row r="63" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
-      <c r="G63" s="7"/>
-      <c r="H63" s="8"/>
-    </row>
-    <row r="64" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A64" s="12"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="5"/>
-      <c r="D64" s="5"/>
-      <c r="E64" s="5"/>
-      <c r="F64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="10"/>
-    </row>
-    <row r="65" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-      <c r="G65" s="7"/>
-      <c r="H65" s="8"/>
-    </row>
-    <row r="66" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A66" s="12"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="5"/>
-      <c r="E66" s="5"/>
-      <c r="F66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="10"/>
-    </row>
-    <row r="67" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="7"/>
-      <c r="C67" s="7"/>
-      <c r="D67" s="7"/>
-      <c r="E67" s="7"/>
-      <c r="F67" s="7"/>
-      <c r="G67" s="7"/>
-      <c r="H67" s="8"/>
-    </row>
-    <row r="68" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A68" s="12"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="5"/>
-      <c r="E68" s="5"/>
-      <c r="F68" s="5"/>
-      <c r="G68" s="5"/>
-      <c r="H68" s="10"/>
-    </row>
-    <row r="69" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="7"/>
-      <c r="C69" s="7"/>
-      <c r="D69" s="7"/>
-      <c r="E69" s="7"/>
-      <c r="F69" s="7"/>
-      <c r="G69" s="7"/>
-      <c r="H69" s="8"/>
-    </row>
-    <row r="70" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A70" s="12"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="5"/>
-      <c r="E70" s="5"/>
-      <c r="F70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="10"/>
-    </row>
-    <row r="71" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="13"/>
-      <c r="B71" s="7"/>
-      <c r="C71" s="7"/>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="7"/>
-      <c r="G71" s="7"/>
-      <c r="H71" s="8"/>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="14"/>
-      <c r="B72" s="3"/>
-      <c r="C72" s="15"/>
-      <c r="D72" s="32"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="16"/>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="3"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="35"/>
-      <c r="E73" s="36"/>
-      <c r="F73" s="36"/>
-      <c r="G73" s="37"/>
-      <c r="H73" s="19"/>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="38"/>
-      <c r="E74" s="39"/>
-      <c r="F74" s="39"/>
-      <c r="G74" s="40"/>
-      <c r="H74" s="19"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
-      <c r="B75" s="3"/>
-      <c r="C75" s="18"/>
-      <c r="D75" s="38"/>
-      <c r="E75" s="39"/>
-      <c r="F75" s="39"/>
-      <c r="G75" s="40"/>
-      <c r="H75" s="19"/>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="18"/>
-      <c r="D76" s="38"/>
-      <c r="E76" s="39"/>
-      <c r="F76" s="39"/>
-      <c r="G76" s="40"/>
-      <c r="H76" s="19"/>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="20"/>
-      <c r="C77" s="18"/>
-      <c r="D77" s="18"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="18"/>
-      <c r="G77" s="18"/>
-      <c r="H77" s="19"/>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="20"/>
-      <c r="C78" s="18"/>
-      <c r="D78" s="18"/>
-      <c r="E78" s="18"/>
-      <c r="F78" s="18"/>
-      <c r="G78" s="18"/>
-      <c r="H78" s="19"/>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="17"/>
-      <c r="B79" s="20"/>
-      <c r="C79" s="18"/>
-      <c r="D79" s="18"/>
-      <c r="E79" s="18"/>
-      <c r="F79" s="18"/>
-      <c r="G79" s="18"/>
-      <c r="H79" s="19"/>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="17"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="18"/>
-      <c r="D80" s="18"/>
-      <c r="E80" s="18"/>
-      <c r="F80" s="18"/>
-      <c r="G80" s="18"/>
-      <c r="H80" s="19"/>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="17"/>
-      <c r="B81" s="20"/>
-      <c r="C81" s="2"/>
-      <c r="D81" s="18"/>
-      <c r="E81" s="18"/>
-      <c r="F81" s="18"/>
-      <c r="G81" s="18"/>
-      <c r="H81" s="19"/>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="21"/>
-      <c r="B82" s="3"/>
-      <c r="C82" s="2"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="39"/>
-      <c r="F82" s="39"/>
-      <c r="G82" s="40"/>
-      <c r="H82" s="19"/>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="21"/>
-      <c r="B83" s="3"/>
-      <c r="C83" s="18"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="39"/>
-      <c r="F83" s="39"/>
-      <c r="G83" s="40"/>
-      <c r="H83" s="19"/>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="21"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="18"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="39"/>
-      <c r="F84" s="39"/>
-      <c r="G84" s="40"/>
-      <c r="H84" s="19"/>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="21"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="39"/>
-      <c r="F85" s="39"/>
-      <c r="G85" s="40"/>
-      <c r="H85" s="19"/>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="21"/>
-      <c r="B86" s="20"/>
-      <c r="C86" s="22"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="39"/>
-      <c r="F86" s="39"/>
-      <c r="G86" s="40"/>
-      <c r="H86" s="19"/>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="21"/>
-      <c r="B87" s="20"/>
-      <c r="C87" s="18"/>
-      <c r="D87" s="18"/>
-      <c r="E87" s="18"/>
-      <c r="F87" s="18"/>
-      <c r="G87" s="18"/>
-      <c r="H87" s="19"/>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="21"/>
-      <c r="B88" s="20"/>
-      <c r="C88" s="18"/>
-      <c r="D88" s="18"/>
-      <c r="E88" s="18"/>
-      <c r="F88" s="18"/>
-      <c r="G88" s="18"/>
-      <c r="H88" s="19"/>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="21"/>
-      <c r="B89" s="20"/>
-      <c r="C89" s="22"/>
-      <c r="D89" s="18"/>
-      <c r="E89" s="18"/>
-      <c r="F89" s="18"/>
-      <c r="G89" s="18"/>
-      <c r="H89" s="23"/>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="21"/>
-      <c r="B90" s="20"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="18"/>
-      <c r="E90" s="18"/>
-      <c r="F90" s="18"/>
-      <c r="G90" s="18"/>
-      <c r="H90" s="23"/>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="21"/>
-      <c r="B91" s="20"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="18"/>
-      <c r="E91" s="18"/>
-      <c r="F91" s="18"/>
-      <c r="G91" s="18"/>
-      <c r="H91" s="19"/>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="24"/>
-      <c r="B92" s="3"/>
-      <c r="C92" s="18"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="39"/>
-      <c r="F92" s="39"/>
-      <c r="G92" s="40"/>
-      <c r="H92" s="25"/>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="24"/>
-      <c r="B93" s="3"/>
-      <c r="C93" s="18"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="39"/>
-      <c r="F93" s="39"/>
-      <c r="G93" s="40"/>
-      <c r="H93" s="25"/>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="24"/>
-      <c r="B94" s="3"/>
-      <c r="C94" s="22"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="39"/>
-      <c r="F94" s="39"/>
-      <c r="G94" s="40"/>
-      <c r="H94" s="25"/>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="24"/>
-      <c r="B95" s="3"/>
-      <c r="C95" s="18"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="39"/>
-      <c r="F95" s="39"/>
-      <c r="G95" s="40"/>
-      <c r="H95" s="25"/>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="24"/>
-      <c r="B96" s="3"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="39"/>
-      <c r="F96" s="39"/>
-      <c r="G96" s="40"/>
-      <c r="H96" s="25"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="24"/>
-      <c r="B97" s="20"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="18"/>
-      <c r="G97" s="18"/>
-      <c r="H97" s="23"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="24"/>
-      <c r="B98" s="20"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-      <c r="F98" s="18"/>
-      <c r="G98" s="18"/>
-      <c r="H98" s="23"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="24"/>
-      <c r="B99" s="20"/>
-      <c r="C99" s="22"/>
-      <c r="D99" s="18"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="18"/>
-      <c r="G99" s="18"/>
-      <c r="H99" s="23"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="24"/>
-      <c r="B100" s="20"/>
-      <c r="C100" s="18"/>
-      <c r="D100" s="18"/>
-      <c r="E100" s="18"/>
-      <c r="F100" s="18"/>
-      <c r="G100" s="18"/>
-      <c r="H100" s="23"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="24"/>
-      <c r="B101" s="20"/>
-      <c r="C101" s="22"/>
-      <c r="D101" s="18"/>
-      <c r="E101" s="18"/>
-      <c r="F101" s="18"/>
-      <c r="G101" s="18"/>
-      <c r="H101" s="23"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="26"/>
-      <c r="B102" s="3"/>
-      <c r="C102" s="18"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="39"/>
-      <c r="F102" s="39"/>
-      <c r="G102" s="40"/>
-      <c r="H102" s="23"/>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="26"/>
-      <c r="B103" s="3"/>
-      <c r="C103" s="18"/>
-      <c r="D103" s="38"/>
-      <c r="E103" s="39"/>
-      <c r="F103" s="39"/>
-      <c r="G103" s="40"/>
-      <c r="H103" s="25"/>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="26"/>
-      <c r="B104" s="3"/>
-      <c r="C104" s="18"/>
-      <c r="D104" s="38"/>
-      <c r="E104" s="39"/>
-      <c r="F104" s="39"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="27"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="26"/>
-      <c r="B105" s="3"/>
-      <c r="C105" s="18"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="39"/>
-      <c r="F105" s="39"/>
-      <c r="G105" s="40"/>
-      <c r="H105" s="25"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="26"/>
-      <c r="B106" s="3"/>
-      <c r="C106" s="18"/>
-      <c r="D106" s="38"/>
-      <c r="E106" s="39"/>
-      <c r="F106" s="39"/>
-      <c r="G106" s="40"/>
-      <c r="H106" s="23"/>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="26"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="22"/>
-      <c r="D107" s="18"/>
-      <c r="E107" s="18"/>
-      <c r="F107" s="18"/>
-      <c r="G107" s="18"/>
-      <c r="H107" s="23"/>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="26"/>
-      <c r="B108" s="20"/>
-      <c r="C108" s="18"/>
-      <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
-      <c r="H108" s="23"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="26"/>
-      <c r="B109" s="20"/>
-      <c r="C109" s="28"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="23"/>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="26"/>
-      <c r="B110" s="20"/>
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="23"/>
-    </row>
-    <row r="111" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="29"/>
-      <c r="B111" s="20"/>
-      <c r="C111" s="30"/>
-      <c r="D111" s="31"/>
-      <c r="E111" s="31"/>
-      <c r="F111" s="31"/>
-      <c r="G111" s="31"/>
-      <c r="H111" s="23"/>
-    </row>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="D23:G23"/>
-    <mergeCell ref="D36:G36"/>
-    <mergeCell ref="D4:G4"/>
-    <mergeCell ref="D6:G6"/>
-    <mergeCell ref="D26:G26"/>
-    <mergeCell ref="D2:G2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="D5:G5"/>
-    <mergeCell ref="D7:G7"/>
-    <mergeCell ref="D22:G22"/>
-    <mergeCell ref="D52:G52"/>
-    <mergeCell ref="D53:G53"/>
-    <mergeCell ref="D24:G24"/>
-    <mergeCell ref="D25:G25"/>
-    <mergeCell ref="D32:G32"/>
-    <mergeCell ref="D33:G33"/>
-    <mergeCell ref="D34:G34"/>
-    <mergeCell ref="D35:G35"/>
-    <mergeCell ref="D37:G37"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/Extra Data for project/Questions files/Questions Full Data.xlsx
+++ b/Extra Data for project/Questions files/Questions Full Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FAFB1BC-283D-4A90-ABF1-3C45F9F13A87}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817DEB56-94E4-4B10-AC0D-D7B56166C45E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{669F632A-8C17-464B-B497-7F400C39EC04}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2101" uniqueCount="1167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="1165">
   <si>
     <t>5S</t>
   </si>
@@ -1620,12 +1620,6 @@
     <t>هل يتم وضع شحم على سوستة باب الغسيل والعصر</t>
   </si>
   <si>
-    <t>لماذا يتم وضع استرتش على باب الغسيل والعصر</t>
-  </si>
-  <si>
-    <t>لحماية الباب من الخدوش</t>
-  </si>
-  <si>
     <t>فيم يستخدم مفتاح التحويل</t>
   </si>
   <si>
@@ -1917,12 +1911,6 @@
     <t xml:space="preserve">هل يتم تركيب وصلة شفافة بامب فى جميع الموديلات بنفس الحجم </t>
   </si>
   <si>
-    <t>مالفرق بين الغسالة والعادية 12 ك والبامب 12ك</t>
-  </si>
-  <si>
-    <t>الفرق فى تركيب الوصلة الشفافة فى الغسالة البامب</t>
-  </si>
-  <si>
     <t>مالفرق بين خرطوم البامب 7/10/12</t>
   </si>
   <si>
@@ -1966,9 +1954,6 @@
   </si>
   <si>
     <t>الحفاظ على الخرطوم من الثني أثناء التصريف</t>
-  </si>
-  <si>
-    <t>ما فائدة مفك تربيط وصلة الصرف 7/10</t>
   </si>
   <si>
     <t xml:space="preserve">ربط غطاء وصلة الصرف لتحقيق العزم المطلوب </t>
@@ -3829,6 +3814,15 @@
       </rPr>
       <t>كجم</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> يتم وضع استرتش على باب الغسيل والعصر للحفاظ عليها من الخدش</t>
+  </si>
+  <si>
+    <t>مالفرق بين الغسالة والعادية 12 ك والبامب 12ك هو تركيب الوصلة الشفافة في الغسالة االبامب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">هل فائدة مفك تربيط وصلة الصرف 7/10 هي ربط غطاء وصلة الصرف لتحقيق العزم المطلوب </t>
   </si>
 </sst>
 </file>
@@ -4392,21 +4386,6 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41C0B1BB-6F04-448A-B009-4F47191C9A95}" name="Table1" displayName="Table1" ref="A1:I327" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I327" xr:uid="{94338B67-F8B2-4F47-928D-55299C6CC79B}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Clinching"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="8">
-      <filters>
-        <filter val="A"/>
-        <filter val="B"/>
-        <filter val="C"/>
-        <filter val="D"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5C073B83-7C73-4184-8CC7-F33AC31FB225}" name="Q_ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{5A4F9621-DF8D-4586-86DF-8B411C00F3E2}" name="Category" dataDxfId="7"/>
@@ -4723,11 +4702,11 @@
   <sheetFormatPr defaultColWidth="25.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="20" style="3" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="62.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="34.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="33.42578125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="63.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="40.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="34.7109375" style="3" customWidth="1"/>
     <col min="8" max="8" width="30" style="3" customWidth="1"/>
     <col min="9" max="9" width="13.42578125" style="3" customWidth="1"/>
@@ -4763,7 +4742,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>1</v>
       </c>
@@ -4792,7 +4771,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>2</v>
       </c>
@@ -4821,7 +4800,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>3</v>
       </c>
@@ -4850,7 +4829,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>4</v>
       </c>
@@ -4879,7 +4858,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>5</v>
       </c>
@@ -4908,7 +4887,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>6</v>
       </c>
@@ -4937,7 +4916,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>7</v>
       </c>
@@ -4966,7 +4945,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>8</v>
       </c>
@@ -4995,7 +4974,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>9</v>
       </c>
@@ -5024,7 +5003,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>10</v>
       </c>
@@ -5053,7 +5032,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>11</v>
       </c>
@@ -5082,7 +5061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>12</v>
       </c>
@@ -5111,7 +5090,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>13</v>
       </c>
@@ -5140,7 +5119,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>14</v>
       </c>
@@ -5169,7 +5148,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>15</v>
       </c>
@@ -5198,7 +5177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>16</v>
       </c>
@@ -5219,7 +5198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>17</v>
       </c>
@@ -5240,7 +5219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>18</v>
       </c>
@@ -5261,7 +5240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>19</v>
       </c>
@@ -5282,7 +5261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>20</v>
       </c>
@@ -5303,7 +5282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>21</v>
       </c>
@@ -5324,7 +5303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="14">
         <v>22</v>
       </c>
@@ -5345,7 +5324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14">
         <v>23</v>
       </c>
@@ -5366,7 +5345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="14">
         <v>24</v>
       </c>
@@ -5387,7 +5366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14">
         <v>25</v>
       </c>
@@ -5408,7 +5387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>26</v>
       </c>
@@ -5437,7 +5416,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>27</v>
       </c>
@@ -5466,7 +5445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>28</v>
       </c>
@@ -5495,7 +5474,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>29</v>
       </c>
@@ -5524,7 +5503,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>30</v>
       </c>
@@ -5553,7 +5532,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="32" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>31</v>
       </c>
@@ -5582,7 +5561,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>32</v>
       </c>
@@ -5611,7 +5590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="34" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>33</v>
       </c>
@@ -5640,7 +5619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>34</v>
       </c>
@@ -5669,7 +5648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>35</v>
       </c>
@@ -5698,7 +5677,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>36</v>
       </c>
@@ -5727,7 +5706,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>37</v>
       </c>
@@ -5756,7 +5735,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>38</v>
       </c>
@@ -5785,7 +5764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>39</v>
       </c>
@@ -5814,7 +5793,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>40</v>
       </c>
@@ -5843,7 +5822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>41</v>
       </c>
@@ -5864,7 +5843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>42</v>
       </c>
@@ -5885,7 +5864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>43</v>
       </c>
@@ -5906,7 +5885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>44</v>
       </c>
@@ -5927,7 +5906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>45</v>
       </c>
@@ -5948,7 +5927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>46</v>
       </c>
@@ -5969,7 +5948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>47</v>
       </c>
@@ -5990,7 +5969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>48</v>
       </c>
@@ -6011,7 +5990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>49</v>
       </c>
@@ -6032,7 +6011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>50</v>
       </c>
@@ -6053,7 +6032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="14">
         <v>51</v>
       </c>
@@ -6082,7 +6061,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="14">
         <v>52</v>
       </c>
@@ -6111,7 +6090,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="14">
         <v>53</v>
       </c>
@@ -6122,10 +6101,10 @@
         <v>76</v>
       </c>
       <c r="D54" s="16" t="s">
-        <v>833</v>
+        <v>828</v>
       </c>
       <c r="E54" s="17" t="s">
-        <v>834</v>
+        <v>829</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>177</v>
@@ -6140,7 +6119,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="14">
         <v>54</v>
       </c>
@@ -6169,7 +6148,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="14">
         <v>55</v>
       </c>
@@ -6198,7 +6177,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="14">
         <v>56</v>
       </c>
@@ -6209,7 +6188,7 @@
         <v>76</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>835</v>
+        <v>830</v>
       </c>
       <c r="E57" s="20">
         <v>0.1</v>
@@ -6227,7 +6206,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="14">
         <v>57</v>
       </c>
@@ -6256,7 +6235,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="14">
         <v>58</v>
       </c>
@@ -6277,7 +6256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="14">
         <v>59</v>
       </c>
@@ -6298,7 +6277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="14">
         <v>60</v>
       </c>
@@ -6327,7 +6306,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="14">
         <v>61</v>
       </c>
@@ -6338,7 +6317,7 @@
         <v>76</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>836</v>
+        <v>831</v>
       </c>
       <c r="E62" s="20">
         <v>0.3</v>
@@ -6356,7 +6335,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="14">
         <v>62</v>
       </c>
@@ -6385,7 +6364,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="14">
         <v>63</v>
       </c>
@@ -6414,7 +6393,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="14">
         <v>64</v>
       </c>
@@ -6443,7 +6422,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>65</v>
       </c>
@@ -6472,7 +6451,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>66</v>
       </c>
@@ -6501,7 +6480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>67</v>
       </c>
@@ -6530,7 +6509,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>68</v>
       </c>
@@ -6559,7 +6538,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>69</v>
       </c>
@@ -6588,7 +6567,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5">
         <v>70</v>
       </c>
@@ -6617,7 +6596,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5">
         <v>71</v>
       </c>
@@ -6646,7 +6625,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="5">
         <v>72</v>
       </c>
@@ -6675,7 +6654,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5">
         <v>73</v>
       </c>
@@ -6704,7 +6683,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5">
         <v>74</v>
       </c>
@@ -6733,7 +6712,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="14">
         <v>75</v>
       </c>
@@ -6762,7 +6741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="14">
         <v>76</v>
       </c>
@@ -6791,7 +6770,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="14">
         <v>77</v>
       </c>
@@ -6820,7 +6799,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="14">
         <v>78</v>
       </c>
@@ -6849,7 +6828,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="14">
         <v>79</v>
       </c>
@@ -6878,7 +6857,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="81" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="14">
         <v>80</v>
       </c>
@@ -6907,7 +6886,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="82" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="14">
         <v>81</v>
       </c>
@@ -6936,7 +6915,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="83" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="14">
         <v>82</v>
       </c>
@@ -6965,7 +6944,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="14">
         <v>83</v>
       </c>
@@ -6994,7 +6973,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="14">
         <v>84</v>
       </c>
@@ -7023,7 +7002,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5">
         <v>85</v>
       </c>
@@ -7044,7 +7023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5">
         <v>86</v>
       </c>
@@ -7073,7 +7052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5">
         <v>87</v>
       </c>
@@ -7102,7 +7081,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="89" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5">
         <v>88</v>
       </c>
@@ -7131,7 +7110,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="90" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5">
         <v>89</v>
       </c>
@@ -7160,7 +7139,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="91" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5">
         <v>90</v>
       </c>
@@ -7189,7 +7168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="92" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5">
         <v>91</v>
       </c>
@@ -7218,7 +7197,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="93" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5">
         <v>92</v>
       </c>
@@ -7239,7 +7218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="5">
         <v>93</v>
       </c>
@@ -7260,7 +7239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="5">
         <v>94</v>
       </c>
@@ -7281,7 +7260,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="14">
         <v>95</v>
       </c>
@@ -7310,7 +7289,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="14">
         <v>96</v>
       </c>
@@ -7339,7 +7318,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="14">
         <v>97</v>
       </c>
@@ -7368,7 +7347,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="99" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="14">
         <v>98</v>
       </c>
@@ -7397,7 +7376,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="100" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="14">
         <v>99</v>
       </c>
@@ -7426,7 +7405,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="14">
         <v>100</v>
       </c>
@@ -7455,7 +7434,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="14">
         <v>101</v>
       </c>
@@ -7484,7 +7463,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="14">
         <v>102</v>
       </c>
@@ -7513,7 +7492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="14">
         <v>103</v>
       </c>
@@ -7542,7 +7521,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="14">
         <v>104</v>
       </c>
@@ -7571,7 +7550,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="106" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5">
         <v>105</v>
       </c>
@@ -7600,7 +7579,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="5">
         <v>106</v>
       </c>
@@ -7629,7 +7608,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="108" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5">
         <v>107</v>
       </c>
@@ -7658,7 +7637,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5">
         <v>108</v>
       </c>
@@ -7687,7 +7666,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="110" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5">
         <v>109</v>
       </c>
@@ -7716,7 +7695,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5">
         <v>110</v>
       </c>
@@ -7745,7 +7724,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5">
         <v>111</v>
       </c>
@@ -7774,7 +7753,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5">
         <v>112</v>
       </c>
@@ -7803,7 +7782,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5">
         <v>113</v>
       </c>
@@ -7832,7 +7811,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5">
         <v>114</v>
       </c>
@@ -7861,7 +7840,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="14">
         <v>116</v>
       </c>
@@ -7882,7 +7861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="14">
         <v>117</v>
       </c>
@@ -7903,7 +7882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="14">
         <v>118</v>
       </c>
@@ -7924,7 +7903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="14">
         <v>119</v>
       </c>
@@ -7945,7 +7924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="14">
         <v>120</v>
       </c>
@@ -7966,7 +7945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="14">
         <v>150</v>
       </c>
@@ -7977,7 +7956,7 @@
         <v>65</v>
       </c>
       <c r="D121" s="14" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="E121" s="14"/>
       <c r="F121" s="14"/>
@@ -7987,7 +7966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="14">
         <v>151</v>
       </c>
@@ -7998,25 +7977,25 @@
         <v>1</v>
       </c>
       <c r="D122" s="14" t="s">
+        <v>553</v>
+      </c>
+      <c r="E122" s="14" t="s">
+        <v>554</v>
+      </c>
+      <c r="F122" s="14" t="s">
         <v>555</v>
       </c>
-      <c r="E122" s="14" t="s">
+      <c r="G122" s="14" t="s">
         <v>556</v>
       </c>
-      <c r="F122" s="14" t="s">
+      <c r="H122" s="14" t="s">
         <v>557</v>
-      </c>
-      <c r="G122" s="14" t="s">
-        <v>558</v>
-      </c>
-      <c r="H122" s="14" t="s">
-        <v>559</v>
       </c>
       <c r="I122" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="123" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="14">
         <v>152</v>
       </c>
@@ -8027,25 +8006,25 @@
         <v>1</v>
       </c>
       <c r="D123" s="14" t="s">
+        <v>558</v>
+      </c>
+      <c r="E123" s="14" t="s">
+        <v>559</v>
+      </c>
+      <c r="F123" s="14" t="s">
         <v>560</v>
       </c>
-      <c r="E123" s="14" t="s">
+      <c r="G123" s="14" t="s">
         <v>561</v>
       </c>
-      <c r="F123" s="14" t="s">
+      <c r="H123" s="14" t="s">
         <v>562</v>
-      </c>
-      <c r="G123" s="14" t="s">
-        <v>563</v>
-      </c>
-      <c r="H123" s="14" t="s">
-        <v>564</v>
       </c>
       <c r="I123" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="14">
         <v>153</v>
       </c>
@@ -8056,25 +8035,25 @@
         <v>1</v>
       </c>
       <c r="D124" s="14" t="s">
+        <v>563</v>
+      </c>
+      <c r="E124" s="14" t="s">
+        <v>564</v>
+      </c>
+      <c r="F124" s="14" t="s">
         <v>565</v>
       </c>
-      <c r="E124" s="14" t="s">
+      <c r="G124" s="14" t="s">
         <v>566</v>
       </c>
-      <c r="F124" s="14" t="s">
+      <c r="H124" s="14" t="s">
         <v>567</v>
-      </c>
-      <c r="G124" s="14" t="s">
-        <v>568</v>
-      </c>
-      <c r="H124" s="14" t="s">
-        <v>569</v>
       </c>
       <c r="I124" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="14">
         <v>154</v>
       </c>
@@ -8085,25 +8064,25 @@
         <v>1</v>
       </c>
       <c r="D125" s="14" t="s">
+        <v>568</v>
+      </c>
+      <c r="E125" s="14" t="s">
+        <v>569</v>
+      </c>
+      <c r="F125" s="14" t="s">
         <v>570</v>
       </c>
-      <c r="E125" s="14" t="s">
+      <c r="G125" s="14" t="s">
         <v>571</v>
       </c>
-      <c r="F125" s="14" t="s">
+      <c r="H125" s="14" t="s">
         <v>572</v>
-      </c>
-      <c r="G125" s="14" t="s">
-        <v>573</v>
-      </c>
-      <c r="H125" s="14" t="s">
-        <v>574</v>
       </c>
       <c r="I125" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5">
         <v>115</v>
       </c>
@@ -8124,7 +8103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="5">
         <v>121</v>
       </c>
@@ -8153,7 +8132,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5">
         <v>122</v>
       </c>
@@ -8182,7 +8161,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="129" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="5">
         <v>123</v>
       </c>
@@ -8211,7 +8190,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:9" ht="19.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5">
         <v>124</v>
       </c>
@@ -8240,7 +8219,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="131" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5">
         <v>145</v>
       </c>
@@ -8251,7 +8230,7 @@
         <v>65</v>
       </c>
       <c r="D131" s="5" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
@@ -8261,7 +8240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="5">
         <v>146</v>
       </c>
@@ -8272,7 +8251,7 @@
         <v>65</v>
       </c>
       <c r="D132" s="5" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
@@ -8282,7 +8261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5">
         <v>147</v>
       </c>
@@ -8293,7 +8272,7 @@
         <v>65</v>
       </c>
       <c r="D133" s="5" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
@@ -8303,7 +8282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5">
         <v>148</v>
       </c>
@@ -8314,7 +8293,7 @@
         <v>65</v>
       </c>
       <c r="D134" s="5" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
@@ -8324,7 +8303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5">
         <v>149</v>
       </c>
@@ -8335,7 +8314,7 @@
         <v>65</v>
       </c>
       <c r="D135" s="5" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
@@ -8345,7 +8324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="14">
         <v>125</v>
       </c>
@@ -8374,7 +8353,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="137" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="14">
         <v>126</v>
       </c>
@@ -8403,7 +8382,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="138" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="14">
         <v>127</v>
       </c>
@@ -8414,7 +8393,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>831</v>
+        <v>826</v>
       </c>
       <c r="E138" s="14" t="s">
         <v>487</v>
@@ -8432,7 +8411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="139" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="14">
         <v>128</v>
       </c>
@@ -8461,7 +8440,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="140" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="14">
         <v>129</v>
       </c>
@@ -8490,7 +8469,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="141" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="14">
         <v>130</v>
       </c>
@@ -8519,7 +8498,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="14">
         <v>131</v>
       </c>
@@ -8548,7 +8527,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="143" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="14">
         <v>132</v>
       </c>
@@ -8577,7 +8556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="14">
         <v>133</v>
       </c>
@@ -8606,7 +8585,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="145" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="14">
         <v>134</v>
       </c>
@@ -8629,13 +8608,13 @@
         <v>523</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>826</v>
+        <v>821</v>
       </c>
       <c r="I145" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="146" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5">
         <v>135</v>
       </c>
@@ -8656,7 +8635,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="5">
         <v>136</v>
       </c>
@@ -8677,7 +8656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5">
         <v>137</v>
       </c>
@@ -8698,7 +8677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5">
         <v>138</v>
       </c>
@@ -8719,7 +8698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5">
         <v>139</v>
       </c>
@@ -8740,7 +8719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5">
         <v>140</v>
       </c>
@@ -8751,19 +8730,17 @@
         <v>65</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>530</v>
-      </c>
-      <c r="E151" s="5" t="s">
-        <v>531</v>
-      </c>
+        <v>1162</v>
+      </c>
+      <c r="E151" s="5"/>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
-      <c r="I151" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I151" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5">
         <v>141</v>
       </c>
@@ -8774,25 +8751,25 @@
         <v>1</v>
       </c>
       <c r="D152" s="5" t="s">
+        <v>530</v>
+      </c>
+      <c r="E152" s="5" t="s">
+        <v>531</v>
+      </c>
+      <c r="F152" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="E152" s="5" t="s">
+      <c r="G152" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="F152" s="5" t="s">
+      <c r="H152" s="5" t="s">
         <v>534</v>
-      </c>
-      <c r="G152" s="5" t="s">
-        <v>535</v>
-      </c>
-      <c r="H152" s="5" t="s">
-        <v>536</v>
       </c>
       <c r="I152" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5">
         <v>142</v>
       </c>
@@ -8803,25 +8780,25 @@
         <v>1</v>
       </c>
       <c r="D153" s="5" t="s">
+        <v>535</v>
+      </c>
+      <c r="E153" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="F153" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="E153" s="5" t="s">
+      <c r="G153" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="F153" s="5" t="s">
-        <v>539</v>
-      </c>
-      <c r="G153" s="5" t="s">
-        <v>540</v>
-      </c>
       <c r="H153" s="5" t="s">
-        <v>827</v>
+        <v>822</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5">
         <v>143</v>
       </c>
@@ -8832,25 +8809,25 @@
         <v>1</v>
       </c>
       <c r="D154" s="5" t="s">
+        <v>539</v>
+      </c>
+      <c r="E154" s="5" t="s">
+        <v>540</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="E154" s="5" t="s">
+      <c r="G154" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="F154" s="5" t="s">
+      <c r="H154" s="5" t="s">
         <v>543</v>
-      </c>
-      <c r="G154" s="5" t="s">
-        <v>544</v>
-      </c>
-      <c r="H154" s="5" t="s">
-        <v>545</v>
       </c>
       <c r="I154" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="155" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5">
         <v>144</v>
       </c>
@@ -8861,326 +8838,326 @@
         <v>1</v>
       </c>
       <c r="D155" s="5" t="s">
+        <v>544</v>
+      </c>
+      <c r="E155" s="5" t="s">
+        <v>545</v>
+      </c>
+      <c r="F155" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="E155" s="5" t="s">
-        <v>547</v>
-      </c>
-      <c r="F155" s="5" t="s">
-        <v>548</v>
-      </c>
       <c r="G155" s="5" t="s">
-        <v>832</v>
+        <v>827</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>828</v>
+        <v>823</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="156" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="14">
         <v>155</v>
       </c>
       <c r="B156" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="C156" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D156" s="14" t="s">
+        <v>574</v>
+      </c>
+      <c r="E156" s="14" t="s">
         <v>575</v>
       </c>
-      <c r="C156" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D156" s="14" t="s">
+      <c r="F156" s="14" t="s">
         <v>576</v>
       </c>
-      <c r="E156" s="14" t="s">
+      <c r="G156" s="14" t="s">
         <v>577</v>
       </c>
-      <c r="F156" s="14" t="s">
+      <c r="H156" s="14" t="s">
         <v>578</v>
-      </c>
-      <c r="G156" s="14" t="s">
-        <v>579</v>
-      </c>
-      <c r="H156" s="14" t="s">
-        <v>580</v>
       </c>
       <c r="I156" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="157" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="14">
         <v>156</v>
       </c>
       <c r="B157" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C157" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D157" s="14" t="s">
+        <v>579</v>
+      </c>
+      <c r="E157" s="14" t="s">
+        <v>580</v>
+      </c>
+      <c r="F157" s="14" t="s">
         <v>581</v>
       </c>
-      <c r="E157" s="14" t="s">
+      <c r="G157" s="14" t="s">
         <v>582</v>
       </c>
-      <c r="F157" s="14" t="s">
+      <c r="H157" s="14" t="s">
         <v>583</v>
-      </c>
-      <c r="G157" s="14" t="s">
-        <v>584</v>
-      </c>
-      <c r="H157" s="14" t="s">
-        <v>585</v>
       </c>
       <c r="I157" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="158" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="14">
         <v>157</v>
       </c>
       <c r="B158" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C158" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D158" s="14" t="s">
+        <v>584</v>
+      </c>
+      <c r="E158" s="14" t="s">
+        <v>585</v>
+      </c>
+      <c r="F158" s="14" t="s">
         <v>586</v>
       </c>
-      <c r="E158" s="14" t="s">
+      <c r="G158" s="14" t="s">
         <v>587</v>
       </c>
-      <c r="F158" s="14" t="s">
+      <c r="H158" s="14" t="s">
         <v>588</v>
-      </c>
-      <c r="G158" s="14" t="s">
-        <v>589</v>
-      </c>
-      <c r="H158" s="14" t="s">
-        <v>590</v>
       </c>
       <c r="I158" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="159" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="14">
         <v>158</v>
       </c>
       <c r="B159" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C159" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D159" s="14" t="s">
+        <v>589</v>
+      </c>
+      <c r="E159" s="14" t="s">
+        <v>590</v>
+      </c>
+      <c r="F159" s="14" t="s">
         <v>591</v>
       </c>
-      <c r="E159" s="14" t="s">
+      <c r="G159" s="14" t="s">
         <v>592</v>
       </c>
-      <c r="F159" s="14" t="s">
+      <c r="H159" s="14" t="s">
         <v>593</v>
-      </c>
-      <c r="G159" s="14" t="s">
-        <v>594</v>
-      </c>
-      <c r="H159" s="14" t="s">
-        <v>595</v>
       </c>
       <c r="I159" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="14">
         <v>159</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C160" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D160" s="14" t="s">
+        <v>594</v>
+      </c>
+      <c r="E160" s="14" t="s">
+        <v>595</v>
+      </c>
+      <c r="F160" s="14" t="s">
         <v>596</v>
       </c>
-      <c r="E160" s="14" t="s">
+      <c r="G160" s="14" t="s">
         <v>597</v>
       </c>
-      <c r="F160" s="14" t="s">
+      <c r="H160" s="14" t="s">
         <v>598</v>
-      </c>
-      <c r="G160" s="14" t="s">
-        <v>599</v>
-      </c>
-      <c r="H160" s="14" t="s">
-        <v>600</v>
       </c>
       <c r="I160" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="161" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="14">
         <v>160</v>
       </c>
       <c r="B161" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C161" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D161" s="14" t="s">
+        <v>599</v>
+      </c>
+      <c r="E161" s="14" t="s">
+        <v>600</v>
+      </c>
+      <c r="F161" s="14" t="s">
         <v>601</v>
       </c>
-      <c r="E161" s="14" t="s">
+      <c r="G161" s="14" t="s">
         <v>602</v>
       </c>
-      <c r="F161" s="14" t="s">
+      <c r="H161" s="14" t="s">
         <v>603</v>
-      </c>
-      <c r="G161" s="14" t="s">
-        <v>604</v>
-      </c>
-      <c r="H161" s="14" t="s">
-        <v>605</v>
       </c>
       <c r="I161" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="14">
         <v>161</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C162" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D162" s="14" t="s">
+        <v>604</v>
+      </c>
+      <c r="E162" s="14" t="s">
+        <v>605</v>
+      </c>
+      <c r="F162" s="14" t="s">
         <v>606</v>
       </c>
-      <c r="E162" s="14" t="s">
+      <c r="G162" s="14" t="s">
         <v>607</v>
       </c>
-      <c r="F162" s="14" t="s">
+      <c r="H162" s="14" t="s">
         <v>608</v>
-      </c>
-      <c r="G162" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="H162" s="14" t="s">
-        <v>610</v>
       </c>
       <c r="I162" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="163" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="14">
         <v>162</v>
       </c>
       <c r="B163" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C163" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D163" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="E163" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="F163" s="14" t="s">
         <v>611</v>
       </c>
-      <c r="E163" s="14" t="s">
+      <c r="G163" s="14" t="s">
         <v>612</v>
       </c>
-      <c r="F163" s="14" t="s">
+      <c r="H163" s="14" t="s">
         <v>613</v>
-      </c>
-      <c r="G163" s="14" t="s">
-        <v>614</v>
-      </c>
-      <c r="H163" s="14" t="s">
-        <v>615</v>
       </c>
       <c r="I163" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="14">
         <v>163</v>
       </c>
       <c r="B164" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C164" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D164" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="E164" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="F164" s="14" t="s">
         <v>616</v>
       </c>
-      <c r="E164" s="14" t="s">
+      <c r="G164" s="14" t="s">
         <v>617</v>
       </c>
-      <c r="F164" s="14" t="s">
+      <c r="H164" s="14" t="s">
         <v>618</v>
-      </c>
-      <c r="G164" s="14" t="s">
-        <v>619</v>
-      </c>
-      <c r="H164" s="14" t="s">
-        <v>620</v>
       </c>
       <c r="I164" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="165" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:9" s="26" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="14">
         <v>164</v>
       </c>
       <c r="B165" s="25" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="C165" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D165" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="E165" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="F165" s="14" t="s">
         <v>621</v>
       </c>
-      <c r="E165" s="14" t="s">
+      <c r="G165" s="14" t="s">
         <v>622</v>
       </c>
-      <c r="F165" s="14" t="s">
+      <c r="H165" s="14" t="s">
         <v>623</v>
-      </c>
-      <c r="G165" s="14" t="s">
-        <v>624</v>
-      </c>
-      <c r="H165" s="14" t="s">
-        <v>625</v>
       </c>
       <c r="I165" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5">
         <v>165</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C166" s="5" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
@@ -9190,18 +9167,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5">
         <v>166</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C167" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="E167" s="5"/>
       <c r="F167" s="5"/>
@@ -9211,131 +9188,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5">
         <v>167</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C168" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>629</v>
-      </c>
-      <c r="E168" s="5" t="s">
-        <v>630</v>
-      </c>
+        <v>1163</v>
+      </c>
+      <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
-      <c r="I168" s="4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I168" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5">
         <v>168</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C169" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D169" s="5" t="s">
+        <v>627</v>
+      </c>
+      <c r="E169" s="5" t="s">
+        <v>628</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>629</v>
+      </c>
+      <c r="G169" s="5" t="s">
+        <v>630</v>
+      </c>
+      <c r="H169" s="5" t="s">
         <v>631</v>
-      </c>
-      <c r="E169" s="5" t="s">
-        <v>632</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>633</v>
-      </c>
-      <c r="G169" s="5" t="s">
-        <v>634</v>
-      </c>
-      <c r="H169" s="5" t="s">
-        <v>635</v>
       </c>
       <c r="I169" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5">
         <v>169</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C170" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D170" s="5" t="s">
+        <v>632</v>
+      </c>
+      <c r="E170" s="5" t="s">
+        <v>633</v>
+      </c>
+      <c r="F170" s="5" t="s">
+        <v>634</v>
+      </c>
+      <c r="G170" s="5" t="s">
+        <v>635</v>
+      </c>
+      <c r="H170" s="5" t="s">
         <v>636</v>
-      </c>
-      <c r="E170" s="5" t="s">
-        <v>637</v>
-      </c>
-      <c r="F170" s="5" t="s">
-        <v>638</v>
-      </c>
-      <c r="G170" s="5" t="s">
-        <v>639</v>
-      </c>
-      <c r="H170" s="5" t="s">
-        <v>640</v>
       </c>
       <c r="I170" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5">
         <v>170</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C171" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D171" s="5" t="s">
+        <v>637</v>
+      </c>
+      <c r="E171" s="5" t="s">
+        <v>638</v>
+      </c>
+      <c r="F171" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="G171" s="5" t="s">
+        <v>640</v>
+      </c>
+      <c r="H171" s="5" t="s">
         <v>641</v>
-      </c>
-      <c r="E171" s="5" t="s">
-        <v>642</v>
-      </c>
-      <c r="F171" s="5" t="s">
-        <v>643</v>
-      </c>
-      <c r="G171" s="5" t="s">
-        <v>644</v>
-      </c>
-      <c r="H171" s="5" t="s">
-        <v>645</v>
       </c>
       <c r="I171" s="4" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5">
         <v>171</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C172" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>646</v>
+        <v>1164</v>
       </c>
       <c r="E172" s="5" t="s">
-        <v>647</v>
+        <v>642</v>
       </c>
       <c r="F172" s="5"/>
       <c r="G172" s="5"/>
@@ -9344,395 +9319,395 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5">
         <v>172</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C173" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D173" s="5" t="s">
-        <v>648</v>
+        <v>643</v>
       </c>
       <c r="E173" s="5" t="s">
-        <v>649</v>
+        <v>644</v>
       </c>
       <c r="F173" s="5" t="s">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="G173" s="5" t="s">
-        <v>651</v>
+        <v>646</v>
       </c>
       <c r="H173" s="5" t="s">
-        <v>652</v>
+        <v>647</v>
       </c>
       <c r="I173" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5">
         <v>173</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C174" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>653</v>
+        <v>648</v>
       </c>
       <c r="E174" s="5" t="s">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="F174" s="5" t="s">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="G174" s="5" t="s">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="H174" s="5" t="s">
-        <v>657</v>
+        <v>652</v>
       </c>
       <c r="I174" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5">
         <v>174</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C175" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D175" s="5" t="s">
-        <v>658</v>
+        <v>653</v>
       </c>
       <c r="E175" s="5" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="F175" s="5" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="G175" s="5" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="H175" s="5" t="s">
-        <v>662</v>
+        <v>657</v>
       </c>
       <c r="I175" s="4" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="14">
         <v>175</v>
       </c>
       <c r="B176" s="25" t="s">
+        <v>658</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D176" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="E176" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="F176" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="G176" s="14" t="s">
+        <v>662</v>
+      </c>
+      <c r="H176" s="14" t="s">
         <v>663</v>
-      </c>
-      <c r="C176" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D176" s="14" t="s">
-        <v>664</v>
-      </c>
-      <c r="E176" s="14" t="s">
-        <v>665</v>
-      </c>
-      <c r="F176" s="14" t="s">
-        <v>666</v>
-      </c>
-      <c r="G176" s="14" t="s">
-        <v>667</v>
-      </c>
-      <c r="H176" s="14" t="s">
-        <v>668</v>
       </c>
       <c r="I176" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="14">
         <v>176</v>
       </c>
       <c r="B177" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D177" s="14" t="s">
-        <v>669</v>
+        <v>664</v>
       </c>
       <c r="E177" s="14" t="s">
-        <v>670</v>
+        <v>665</v>
       </c>
       <c r="F177" s="14" t="s">
-        <v>671</v>
+        <v>666</v>
       </c>
       <c r="G177" s="14" t="s">
-        <v>672</v>
+        <v>667</v>
       </c>
       <c r="H177" s="14" t="s">
-        <v>673</v>
+        <v>668</v>
       </c>
       <c r="I177" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="178" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="14">
         <v>177</v>
       </c>
       <c r="B178" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C178" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D178" s="14" t="s">
-        <v>674</v>
+        <v>669</v>
       </c>
       <c r="E178" s="14" t="s">
-        <v>675</v>
+        <v>670</v>
       </c>
       <c r="F178" s="14" t="s">
-        <v>676</v>
+        <v>671</v>
       </c>
       <c r="G178" s="14" t="s">
-        <v>677</v>
+        <v>672</v>
       </c>
       <c r="H178" s="14" t="s">
-        <v>678</v>
+        <v>673</v>
       </c>
       <c r="I178" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="179" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="14">
         <v>178</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C179" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D179" s="14" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="E179" s="14" t="s">
-        <v>680</v>
+        <v>675</v>
       </c>
       <c r="F179" s="14" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="G179" s="14" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="H179" s="14" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="I179" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="180" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="14">
         <v>179</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="14" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="E180" s="14" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="F180" s="14" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="G180" s="14" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="H180" s="14" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
       <c r="I180" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="181" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="14">
         <v>180</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D181" s="14" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="E181" s="14" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
       <c r="F181" s="14" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="G181" s="14" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
       <c r="H181" s="14" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="I181" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="182" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="14">
         <v>181</v>
       </c>
       <c r="B182" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D182" s="14" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
       <c r="E182" s="14" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="F182" s="14" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
       <c r="G182" s="14" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="H182" s="14" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="I182" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="183" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="14">
         <v>182</v>
       </c>
       <c r="B183" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D183" s="14" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="E183" s="14" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="F183" s="14" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="G183" s="14" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
       <c r="H183" s="14" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="I183" s="23" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="14">
         <v>183</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="14" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
       <c r="E184" s="14" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="F184" s="14" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
       <c r="G184" s="14" t="s">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="H184" s="14" t="s">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="I184" s="23" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="185" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="14">
         <v>184</v>
       </c>
       <c r="B185" s="25" t="s">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="C185" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D185" s="14" t="s">
-        <v>709</v>
+        <v>704</v>
       </c>
       <c r="E185" s="14" t="s">
-        <v>710</v>
+        <v>705</v>
       </c>
       <c r="F185" s="14" t="s">
-        <v>711</v>
+        <v>706</v>
       </c>
       <c r="G185" s="14" t="s">
-        <v>712</v>
+        <v>707</v>
       </c>
       <c r="H185" s="14" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="I185" s="23" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="186" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5">
         <v>185</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>715</v>
+        <v>710</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
@@ -9742,18 +9717,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5">
         <v>186</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>716</v>
+        <v>711</v>
       </c>
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
@@ -9763,18 +9738,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5">
         <v>187</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
@@ -9784,18 +9759,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5">
         <v>188</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>718</v>
+        <v>713</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
@@ -9805,18 +9780,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5">
         <v>189</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
@@ -9826,163 +9801,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5">
         <v>190</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D191" s="6" t="s">
-        <v>720</v>
+        <v>715</v>
       </c>
       <c r="E191" s="6" t="s">
-        <v>721</v>
+        <v>716</v>
       </c>
       <c r="F191" s="6" t="s">
-        <v>722</v>
+        <v>717</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="H191" s="6" t="s">
-        <v>724</v>
+        <v>719</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="192" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5">
         <v>191</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>725</v>
+        <v>720</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="F192" s="6" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="G192" s="6" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="H192" s="6" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="193" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5">
         <v>192</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>730</v>
+        <v>725</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="F193" s="6" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="G193" s="6" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="H193" s="6" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="194" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5">
         <v>193</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="F194" s="6" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="G194" s="6" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="H194" s="6" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="195" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5">
         <v>194</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D195" s="5" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="E195" s="6" t="s">
-        <v>740</v>
+        <v>735</v>
       </c>
       <c r="F195" s="6" t="s">
-        <v>741</v>
+        <v>736</v>
       </c>
       <c r="G195" s="6" t="s">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="H195" s="6" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="196" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="14">
         <v>195</v>
       </c>
       <c r="B196" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>745</v>
+        <v>740</v>
       </c>
       <c r="E196" s="17"/>
       <c r="F196" s="17"/>
@@ -9992,18 +9967,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="14">
         <v>196</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C197" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>717</v>
+        <v>712</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="17"/>
@@ -10013,18 +9988,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="14">
         <v>197</v>
       </c>
       <c r="B198" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="17"/>
@@ -10034,18 +10009,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="14">
         <v>198</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>747</v>
+        <v>742</v>
       </c>
       <c r="E199" s="17"/>
       <c r="F199" s="17"/>
@@ -10055,18 +10030,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="14">
         <v>199</v>
       </c>
       <c r="B200" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C200" s="14" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D200" s="16" t="s">
-        <v>748</v>
+        <v>743</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="17"/>
@@ -10076,163 +10051,163 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="14">
         <v>200</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D201" s="17" t="s">
-        <v>749</v>
+        <v>744</v>
       </c>
       <c r="E201" s="17" t="s">
-        <v>750</v>
+        <v>745</v>
       </c>
       <c r="F201" s="17" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="G201" s="17" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H201" s="17" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="I201" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="202" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="14">
         <v>201</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D202" s="17" t="s">
-        <v>754</v>
+        <v>749</v>
       </c>
       <c r="E202" s="17" t="s">
-        <v>755</v>
+        <v>750</v>
       </c>
       <c r="F202" s="17" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="G202" s="17" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="H202" s="17" t="s">
-        <v>758</v>
+        <v>753</v>
       </c>
       <c r="I202" s="16" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="203" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="14">
         <v>202</v>
       </c>
       <c r="B203" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D203" s="16" t="s">
-        <v>759</v>
+        <v>754</v>
       </c>
       <c r="E203" s="17" t="s">
-        <v>760</v>
+        <v>755</v>
       </c>
       <c r="F203" s="17" t="s">
-        <v>761</v>
+        <v>756</v>
       </c>
       <c r="G203" s="17" t="s">
-        <v>762</v>
+        <v>757</v>
       </c>
       <c r="H203" s="17" t="s">
-        <v>763</v>
+        <v>758</v>
       </c>
       <c r="I203" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="204" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="14">
         <v>203</v>
       </c>
       <c r="B204" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D204" s="16" t="s">
-        <v>764</v>
+        <v>759</v>
       </c>
       <c r="E204" s="17" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="F204" s="17" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="G204" s="17" t="s">
-        <v>767</v>
+        <v>762</v>
       </c>
       <c r="H204" s="17" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="I204" s="21" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="14">
         <v>204</v>
       </c>
       <c r="B205" s="27" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D205" s="16" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="E205" s="17" t="s">
-        <v>770</v>
+        <v>765</v>
       </c>
       <c r="F205" s="17" t="s">
-        <v>771</v>
+        <v>766</v>
       </c>
       <c r="G205" s="17" t="s">
-        <v>772</v>
+        <v>767</v>
       </c>
       <c r="H205" s="17" t="s">
-        <v>773</v>
+        <v>768</v>
       </c>
       <c r="I205" s="16" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="206" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5">
         <v>205</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>775</v>
+        <v>770</v>
       </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
@@ -10242,18 +10217,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5">
         <v>206</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>830</v>
+        <v>825</v>
       </c>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
@@ -10263,18 +10238,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5">
         <v>207</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>776</v>
+        <v>771</v>
       </c>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
@@ -10284,18 +10259,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5">
         <v>208</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>777</v>
+        <v>772</v>
       </c>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
@@ -10305,18 +10280,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="5">
         <v>209</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
@@ -10326,163 +10301,163 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="5">
         <v>210</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>779</v>
+        <v>774</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F211" s="6" t="s">
-        <v>780</v>
+        <v>775</v>
       </c>
       <c r="G211" s="6" t="s">
-        <v>781</v>
+        <v>776</v>
       </c>
       <c r="H211" s="6" t="s">
-        <v>782</v>
+        <v>777</v>
       </c>
       <c r="I211" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="212" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="5">
         <v>211</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D212" s="7" t="s">
-        <v>783</v>
+        <v>778</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="F212" s="6" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="G212" s="6" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="H212" s="6" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="213" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="5">
         <v>212</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D213" s="7" t="s">
-        <v>788</v>
+        <v>783</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="F213" s="5" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="G213" s="6" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="H213" s="6" t="s">
-        <v>792</v>
+        <v>787</v>
       </c>
       <c r="I213" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="214" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="5">
         <v>213</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="F214" s="6" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="G214" s="6" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="H214" s="6" t="s">
-        <v>797</v>
+        <v>792</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="215" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5">
         <v>214</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>774</v>
+        <v>769</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D215" s="7" t="s">
-        <v>798</v>
+        <v>793</v>
       </c>
       <c r="E215" s="6" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="F215" s="6" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="G215" s="6" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="H215" s="6" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="I215" s="11" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="216" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="14">
         <v>215</v>
       </c>
       <c r="B216" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>803</v>
+        <v>798</v>
       </c>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
@@ -10492,18 +10467,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="14">
         <v>216</v>
       </c>
       <c r="B217" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="E217" s="17"/>
       <c r="F217" s="17"/>
@@ -10513,18 +10488,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="14">
         <v>217</v>
       </c>
       <c r="B218" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>805</v>
+        <v>800</v>
       </c>
       <c r="E218" s="17"/>
       <c r="F218" s="17"/>
@@ -10534,18 +10509,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="14">
         <v>218</v>
       </c>
       <c r="B219" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C219" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D219" s="17" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="17"/>
@@ -10555,18 +10530,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="14">
         <v>219</v>
       </c>
       <c r="B220" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D220" s="17" t="s">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="17"/>
@@ -10576,366 +10551,366 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="14">
         <v>220</v>
       </c>
       <c r="B221" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C221" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D221" s="16" t="s">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="E221" s="17" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="F221" s="17" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="G221" s="17" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="H221" s="17" t="s">
-        <v>811</v>
+        <v>806</v>
       </c>
       <c r="I221" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="222" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="14">
         <v>221</v>
       </c>
       <c r="B222" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C222" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D222" s="17" t="s">
-        <v>829</v>
+        <v>824</v>
       </c>
       <c r="E222" s="17" t="s">
-        <v>735</v>
+        <v>730</v>
       </c>
       <c r="F222" s="17" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="G222" s="17" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="H222" s="17" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="I222" s="21" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="223" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="14">
         <v>222</v>
       </c>
       <c r="B223" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C223" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D223" s="22" t="s">
-        <v>812</v>
+        <v>807</v>
       </c>
       <c r="E223" s="17" t="s">
-        <v>813</v>
+        <v>808</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>43</v>
       </c>
       <c r="G223" s="17" t="s">
-        <v>814</v>
+        <v>809</v>
       </c>
       <c r="H223" s="17" t="s">
-        <v>815</v>
+        <v>810</v>
       </c>
       <c r="I223" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="224" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="14">
         <v>223</v>
       </c>
       <c r="B224" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C224" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D224" s="17" t="s">
-        <v>816</v>
+        <v>811</v>
       </c>
       <c r="E224" s="17" t="s">
-        <v>817</v>
+        <v>812</v>
       </c>
       <c r="F224" s="17" t="s">
-        <v>818</v>
+        <v>813</v>
       </c>
       <c r="G224" s="17" t="s">
-        <v>819</v>
+        <v>814</v>
       </c>
       <c r="H224" s="17" t="s">
-        <v>820</v>
+        <v>815</v>
       </c>
       <c r="I224" s="21" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="225" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="14">
         <v>224</v>
       </c>
       <c r="B225" s="27" t="s">
-        <v>802</v>
+        <v>797</v>
       </c>
       <c r="C225" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D225" s="16" t="s">
-        <v>821</v>
+        <v>816</v>
       </c>
       <c r="E225" s="20" t="s">
-        <v>822</v>
+        <v>817</v>
       </c>
       <c r="F225" s="20" t="s">
-        <v>823</v>
+        <v>818</v>
       </c>
       <c r="G225" s="20" t="s">
-        <v>824</v>
+        <v>819</v>
       </c>
       <c r="H225" s="20" t="s">
-        <v>825</v>
+        <v>820</v>
       </c>
       <c r="I225" s="21" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="226" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5">
         <v>225</v>
       </c>
       <c r="B226" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>833</v>
+      </c>
+      <c r="E226" s="5" t="s">
+        <v>834</v>
+      </c>
+      <c r="F226" s="5" t="s">
+        <v>835</v>
+      </c>
+      <c r="G226" s="5" t="s">
+        <v>836</v>
+      </c>
+      <c r="H226" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="C226" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D226" s="5" t="s">
-        <v>838</v>
-      </c>
-      <c r="E226" s="5" t="s">
-        <v>839</v>
-      </c>
-      <c r="F226" s="5" t="s">
-        <v>840</v>
-      </c>
-      <c r="G226" s="5" t="s">
-        <v>841</v>
-      </c>
-      <c r="H226" s="5" t="s">
-        <v>842</v>
       </c>
       <c r="I226" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="227" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5">
         <v>226</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>843</v>
+        <v>838</v>
       </c>
       <c r="E227" s="5" t="s">
-        <v>844</v>
+        <v>839</v>
       </c>
       <c r="F227" s="5" t="s">
-        <v>845</v>
+        <v>840</v>
       </c>
       <c r="G227" s="5" t="s">
-        <v>846</v>
+        <v>841</v>
       </c>
       <c r="H227" s="5" t="s">
-        <v>847</v>
+        <v>842</v>
       </c>
       <c r="I227" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="228" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5">
         <v>227</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C228" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D228" s="5" t="s">
-        <v>848</v>
+        <v>843</v>
       </c>
       <c r="E228" s="5" t="s">
-        <v>849</v>
+        <v>844</v>
       </c>
       <c r="F228" s="5" t="s">
-        <v>850</v>
+        <v>845</v>
       </c>
       <c r="G228" s="5" t="s">
-        <v>851</v>
+        <v>846</v>
       </c>
       <c r="H228" s="5" t="s">
-        <v>852</v>
+        <v>847</v>
       </c>
       <c r="I228" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5">
         <v>228</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D229" s="5" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="E229" s="5" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="F229" s="5" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="G229" s="5" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="H229" s="5" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="I229" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="230" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5">
         <v>229</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D230" s="5" t="s">
-        <v>858</v>
+        <v>853</v>
       </c>
       <c r="E230" s="5" t="s">
-        <v>859</v>
+        <v>854</v>
       </c>
       <c r="F230" s="5" t="s">
-        <v>860</v>
+        <v>855</v>
       </c>
       <c r="G230" s="5" t="s">
-        <v>861</v>
+        <v>856</v>
       </c>
       <c r="H230" s="5" t="s">
-        <v>862</v>
+        <v>857</v>
       </c>
       <c r="I230" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5">
         <v>230</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C231" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D231" s="5" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="E231" s="5" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="F231" s="5" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="G231" s="5" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="H231" s="5" t="s">
-        <v>867</v>
+        <v>862</v>
       </c>
       <c r="I231" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="232" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5">
         <v>231</v>
       </c>
       <c r="B232" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C232" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>863</v>
+      </c>
+      <c r="E232" s="5" t="s">
+        <v>864</v>
+      </c>
+      <c r="F232" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="G232" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="H232" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="C232" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D232" s="5" t="s">
-        <v>868</v>
-      </c>
-      <c r="E232" s="5" t="s">
-        <v>869</v>
-      </c>
-      <c r="F232" s="5" t="s">
-        <v>870</v>
-      </c>
-      <c r="G232" s="5" t="s">
-        <v>871</v>
-      </c>
-      <c r="H232" s="5" t="s">
-        <v>842</v>
       </c>
       <c r="I232" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="233" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5">
         <v>232</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C233" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E233" s="5"/>
       <c r="F233" s="5"/>
@@ -10945,47 +10920,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5">
         <v>233</v>
       </c>
       <c r="B234" s="8" t="s">
+        <v>832</v>
+      </c>
+      <c r="C234" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="E234" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="F234" s="5" t="s">
+        <v>870</v>
+      </c>
+      <c r="G234" s="5" t="s">
+        <v>871</v>
+      </c>
+      <c r="H234" s="5" t="s">
         <v>837</v>
-      </c>
-      <c r="C234" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D234" s="5" t="s">
-        <v>873</v>
-      </c>
-      <c r="E234" s="5" t="s">
-        <v>874</v>
-      </c>
-      <c r="F234" s="5" t="s">
-        <v>875</v>
-      </c>
-      <c r="G234" s="5" t="s">
-        <v>876</v>
-      </c>
-      <c r="H234" s="5" t="s">
-        <v>842</v>
       </c>
       <c r="I234" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="235" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5">
         <v>234</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>837</v>
+        <v>832</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E235" s="5">
         <v>1</v>
@@ -11000,50 +10975,50 @@
         <v>6</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="236" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="31">
         <v>235</v>
       </c>
       <c r="B236" s="32" t="s">
+        <v>874</v>
+      </c>
+      <c r="C236" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D236" s="31" t="s">
+        <v>875</v>
+      </c>
+      <c r="E236" s="31" t="s">
+        <v>876</v>
+      </c>
+      <c r="F236" s="31" t="s">
+        <v>877</v>
+      </c>
+      <c r="G236" s="31" t="s">
+        <v>878</v>
+      </c>
+      <c r="H236" s="31" t="s">
         <v>879</v>
-      </c>
-      <c r="C236" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D236" s="31" t="s">
-        <v>880</v>
-      </c>
-      <c r="E236" s="31" t="s">
-        <v>881</v>
-      </c>
-      <c r="F236" s="31" t="s">
-        <v>882</v>
-      </c>
-      <c r="G236" s="31" t="s">
-        <v>883</v>
-      </c>
-      <c r="H236" s="31" t="s">
-        <v>884</v>
       </c>
       <c r="I236" s="31" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="237" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="5">
         <v>236</v>
       </c>
       <c r="B237" s="8" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C237" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D237" s="5" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E237" s="5"/>
       <c r="F237" s="5"/>
@@ -11053,47 +11028,47 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="31">
         <v>237</v>
       </c>
       <c r="B238" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C238" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D238" s="31" t="s">
-        <v>885</v>
+        <v>880</v>
       </c>
       <c r="E238" s="31" t="s">
-        <v>886</v>
+        <v>881</v>
       </c>
       <c r="F238" s="31" t="s">
-        <v>887</v>
+        <v>882</v>
       </c>
       <c r="G238" s="31" t="s">
-        <v>888</v>
+        <v>883</v>
       </c>
       <c r="H238" s="31" t="s">
-        <v>889</v>
+        <v>884</v>
       </c>
       <c r="I238" s="31" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="31">
         <v>238</v>
       </c>
       <c r="B239" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C239" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D239" s="31" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E239" s="31">
         <v>1</v>
@@ -11108,224 +11083,224 @@
         <v>6</v>
       </c>
       <c r="I239" s="31" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="240" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="31">
         <v>239</v>
       </c>
       <c r="B240" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C240" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D240" s="31" t="s">
+        <v>885</v>
+      </c>
+      <c r="E240" s="31" t="s">
+        <v>886</v>
+      </c>
+      <c r="F240" s="31" t="s">
+        <v>887</v>
+      </c>
+      <c r="G240" s="31" t="s">
+        <v>888</v>
+      </c>
+      <c r="H240" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="I240" s="31" t="s">
         <v>890</v>
       </c>
-      <c r="E240" s="31" t="s">
-        <v>891</v>
-      </c>
-      <c r="F240" s="31" t="s">
-        <v>892</v>
-      </c>
-      <c r="G240" s="31" t="s">
-        <v>893</v>
-      </c>
-      <c r="H240" s="31" t="s">
-        <v>894</v>
-      </c>
-      <c r="I240" s="31" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="241" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="31">
         <v>240</v>
       </c>
       <c r="B241" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C241" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D241" s="31" t="s">
-        <v>896</v>
+        <v>891</v>
       </c>
       <c r="E241" s="31" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="F241" s="31" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="G241" s="31" t="s">
-        <v>899</v>
+        <v>894</v>
       </c>
       <c r="H241" s="31" t="s">
-        <v>900</v>
+        <v>895</v>
       </c>
       <c r="I241" s="31" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="242" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="31">
         <v>241</v>
       </c>
       <c r="B242" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C242" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D242" s="31" t="s">
-        <v>901</v>
+        <v>896</v>
       </c>
       <c r="E242" s="31" t="s">
-        <v>902</v>
+        <v>897</v>
       </c>
       <c r="F242" s="31" t="s">
-        <v>903</v>
+        <v>898</v>
       </c>
       <c r="G242" s="31" t="s">
-        <v>904</v>
+        <v>899</v>
       </c>
       <c r="H242" s="31" t="s">
-        <v>905</v>
+        <v>900</v>
       </c>
       <c r="I242" s="31" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="243" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="31">
         <v>242</v>
       </c>
       <c r="B243" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C243" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D243" s="31" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="E243" s="31" t="s">
-        <v>907</v>
+        <v>902</v>
       </c>
       <c r="F243" s="31" t="s">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="G243" s="31" t="s">
-        <v>909</v>
+        <v>904</v>
       </c>
       <c r="H243" s="31" t="s">
-        <v>910</v>
+        <v>905</v>
       </c>
       <c r="I243" s="31" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="244" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="31">
         <v>243</v>
       </c>
       <c r="B244" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C244" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D244" s="31" t="s">
-        <v>911</v>
+        <v>906</v>
       </c>
       <c r="E244" s="31" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="F244" s="31" t="s">
-        <v>913</v>
+        <v>908</v>
       </c>
       <c r="G244" s="31" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="H244" s="31" t="s">
-        <v>915</v>
+        <v>910</v>
       </c>
       <c r="I244" s="31" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="245" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="31">
         <v>244</v>
       </c>
       <c r="B245" s="32" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C245" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D245" s="31" t="s">
-        <v>916</v>
+        <v>911</v>
       </c>
       <c r="E245" s="31" t="s">
-        <v>917</v>
+        <v>912</v>
       </c>
       <c r="F245" s="31" t="s">
-        <v>918</v>
+        <v>913</v>
       </c>
       <c r="G245" s="31" t="s">
-        <v>919</v>
+        <v>914</v>
       </c>
       <c r="H245" s="31" t="s">
-        <v>920</v>
+        <v>915</v>
       </c>
       <c r="I245" s="31" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="246" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="14">
         <v>245</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C246" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D246" s="14" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="E246" s="14" t="s">
-        <v>881</v>
+        <v>876</v>
       </c>
       <c r="F246" s="14" t="s">
-        <v>882</v>
+        <v>877</v>
       </c>
       <c r="G246" s="14" t="s">
-        <v>883</v>
+        <v>878</v>
       </c>
       <c r="H246" s="14" t="s">
-        <v>884</v>
+        <v>879</v>
       </c>
       <c r="I246" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="247" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="14">
         <v>246</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C247" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="E247" s="14"/>
       <c r="F247" s="14"/>
@@ -11335,18 +11310,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="248" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="14">
         <v>247</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C248" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>922</v>
+        <v>917</v>
       </c>
       <c r="E248" s="14"/>
       <c r="F248" s="14"/>
@@ -11356,18 +11331,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="14">
         <v>248</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C249" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="E249" s="14">
         <v>1</v>
@@ -11382,146 +11357,146 @@
         <v>6</v>
       </c>
       <c r="I249" s="14" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="250" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="14">
         <v>249</v>
       </c>
       <c r="B250" s="15" t="s">
+        <v>916</v>
+      </c>
+      <c r="C250" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D250" s="14" t="s">
+        <v>918</v>
+      </c>
+      <c r="E250" s="14" t="s">
+        <v>919</v>
+      </c>
+      <c r="F250" s="14" t="s">
+        <v>920</v>
+      </c>
+      <c r="G250" s="14" t="s">
         <v>921</v>
       </c>
-      <c r="C250" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D250" s="14" t="s">
-        <v>923</v>
-      </c>
-      <c r="E250" s="14" t="s">
-        <v>924</v>
-      </c>
-      <c r="F250" s="14" t="s">
-        <v>925</v>
-      </c>
-      <c r="G250" s="14" t="s">
-        <v>926</v>
-      </c>
       <c r="H250" s="14" t="s">
-        <v>927</v>
+        <v>922</v>
       </c>
       <c r="I250" s="14" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="251" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="14">
         <v>250</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C251" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>928</v>
+        <v>923</v>
       </c>
       <c r="E251" s="14" t="s">
-        <v>929</v>
+        <v>924</v>
       </c>
       <c r="F251" s="14" t="s">
-        <v>930</v>
+        <v>925</v>
       </c>
       <c r="G251" s="14" t="s">
-        <v>931</v>
+        <v>926</v>
       </c>
       <c r="H251" s="14" t="s">
-        <v>932</v>
+        <v>927</v>
       </c>
       <c r="I251" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="14">
         <v>251</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C252" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D252" s="14" t="s">
-        <v>933</v>
+        <v>928</v>
       </c>
       <c r="E252" s="14" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="F252" s="14" t="s">
-        <v>935</v>
+        <v>930</v>
       </c>
       <c r="G252" s="14" t="s">
-        <v>936</v>
+        <v>931</v>
       </c>
       <c r="H252" s="14" t="s">
-        <v>937</v>
+        <v>932</v>
       </c>
       <c r="I252" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="253" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="14">
         <v>252</v>
       </c>
       <c r="B253" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C253" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D253" s="14" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
       <c r="E253" s="14" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
       <c r="F253" s="14" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
       <c r="G253" s="14" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
       <c r="H253" s="14" t="s">
-        <v>842</v>
+        <v>837</v>
       </c>
       <c r="I253" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="14">
         <v>253</v>
       </c>
       <c r="B254" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C254" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D254" s="14" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="E254" s="14" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="F254" s="14" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="G254" s="14" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="H254" s="14" t="s">
         <v>4</v>
@@ -11530,21 +11505,21 @@
         <v>7</v>
       </c>
     </row>
-    <row r="255" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="14">
         <v>254</v>
       </c>
       <c r="B255" s="15" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="C255" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="F255" s="14" t="s">
         <v>5</v>
@@ -11553,24 +11528,24 @@
         <v>4</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="I255" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5">
         <v>255</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C256" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="E256" s="5"/>
       <c r="F256" s="5"/>
@@ -11581,18 +11556,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5">
         <v>256</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
@@ -11603,18 +11578,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5">
         <v>257</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C258" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
@@ -11625,18 +11600,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="5">
         <v>258</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="E259" s="5"/>
       <c r="F259" s="5"/>
@@ -11647,18 +11622,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5">
         <v>259</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
@@ -11669,18 +11644,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5">
         <v>260</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
@@ -11691,18 +11666,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="5">
         <v>261</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C262" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="E262" s="5"/>
       <c r="F262" s="5"/>
@@ -11713,18 +11688,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5">
         <v>262</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C263" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
@@ -11735,18 +11710,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5">
         <v>263</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C264" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
@@ -11757,18 +11732,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5">
         <v>264</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
       <c r="E265" s="5"/>
       <c r="F265" s="5"/>
@@ -11779,569 +11754,569 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="14">
         <v>265</v>
       </c>
       <c r="B266" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C266" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D266" s="27" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="E266" s="29" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="F266" s="29" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="G266" s="29" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="H266" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I266" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="267" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="14">
         <v>266</v>
       </c>
       <c r="B267" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C267" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D267" s="27" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="E267" s="29" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="F267" s="29" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="G267" s="29" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="H267" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I267" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="268" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="14">
         <v>267</v>
       </c>
       <c r="B268" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C268" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D268" s="27" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
       <c r="E268" s="29" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="G268" s="29" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="H268" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I268" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="269" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="14">
         <v>268</v>
       </c>
       <c r="B269" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C269" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D269" s="27" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="E269" s="29" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
       <c r="F269" s="29" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="G269" s="29" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="H269" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I269" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="270" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="14">
         <v>269</v>
       </c>
       <c r="B270" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C270" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D270" s="27" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="E270" s="29" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="F270" s="29" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
       <c r="G270" s="29" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="H270" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I270" s="29" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="271" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="14">
         <v>270</v>
       </c>
       <c r="B271" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C271" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D271" s="27" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="E271" s="29" t="s">
-        <v>981</v>
+        <v>976</v>
       </c>
       <c r="F271" s="29" t="s">
-        <v>982</v>
+        <v>977</v>
       </c>
       <c r="G271" s="29" t="s">
-        <v>983</v>
+        <v>978</v>
       </c>
       <c r="H271" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I271" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="272" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="14">
         <v>271</v>
       </c>
       <c r="B272" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C272" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D272" s="27" t="s">
-        <v>984</v>
+        <v>979</v>
       </c>
       <c r="E272" s="29" t="s">
-        <v>985</v>
+        <v>980</v>
       </c>
       <c r="F272" s="29" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="G272" s="29" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="H272" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I272" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="273" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="14">
         <v>272</v>
       </c>
       <c r="B273" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C273" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D273" s="27" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
       <c r="E273" s="29" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="F273" s="29" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="G273" s="29" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="H273" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I273" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="274" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="274" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="14">
         <v>273</v>
       </c>
       <c r="B274" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C274" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D274" s="27" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="E274" s="29" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
       <c r="F274" s="29" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="G274" s="29" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="H274" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I274" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="275" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="275" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="14">
         <v>274</v>
       </c>
       <c r="B275" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C275" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D275" s="27" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="E275" s="29" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F275" s="29" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="G275" s="29" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
       <c r="H275" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I275" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="276" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="276" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="14">
         <v>275</v>
       </c>
       <c r="B276" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C276" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D276" s="27" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="E276" s="29" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="F276" s="29" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="G276" s="29" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="H276" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I276" s="29" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="277" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="277" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="14">
         <v>276</v>
       </c>
       <c r="B277" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C277" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D277" s="27" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
       <c r="E277" s="29" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="F277" s="29" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="G277" s="29" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="H277" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I277" s="29" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="278" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="278" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="14">
         <v>277</v>
       </c>
       <c r="B278" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C278" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="E278" s="29" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
       <c r="F278" s="29" t="s">
-        <v>1009</v>
+        <v>1004</v>
       </c>
       <c r="G278" s="29" t="s">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="H278" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I278" s="29" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="279" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="279" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="14">
         <v>278</v>
       </c>
       <c r="B279" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C279" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D279" s="27" t="s">
-        <v>1011</v>
+        <v>1006</v>
       </c>
       <c r="E279" s="29" t="s">
-        <v>1012</v>
+        <v>1007</v>
       </c>
       <c r="F279" s="29" t="s">
-        <v>1013</v>
+        <v>1008</v>
       </c>
       <c r="G279" s="29" t="s">
-        <v>1014</v>
+        <v>1009</v>
       </c>
       <c r="H279" s="14" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
       <c r="I279" s="29" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="280" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="280" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="14">
         <v>279</v>
       </c>
       <c r="B280" s="28" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C280" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D280" s="27" t="s">
-        <v>1015</v>
+        <v>1010</v>
       </c>
       <c r="E280" s="29" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F280" s="29" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G280" s="29" t="s">
+        <v>1013</v>
+      </c>
+      <c r="H280" s="14" t="s">
         <v>1016</v>
       </c>
-      <c r="F280" s="29" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G280" s="29" t="s">
-        <v>1018</v>
-      </c>
-      <c r="H280" s="14" t="s">
-        <v>1021</v>
-      </c>
       <c r="I280" s="29" t="s">
-        <v>878</v>
-      </c>
-    </row>
-    <row r="281" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="281" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5">
         <v>280</v>
       </c>
       <c r="B281" s="8" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D281" s="13" t="s">
+        <v>1019</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F281" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G281" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="H281" s="13" t="s">
         <v>1023</v>
-      </c>
-      <c r="C281" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D281" s="13" t="s">
-        <v>1024</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F281" s="13" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G281" s="13" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H281" s="13" t="s">
-        <v>1028</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="282" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5">
         <v>281</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C282" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D282" s="13" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="E282" s="13" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="F282" s="13" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
       <c r="G282" s="13" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="H282" s="13" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="283" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5">
         <v>282</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C283" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D283" s="13" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="E283" s="13" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="F283" s="13" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
       <c r="G283" s="13" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="H283" s="13" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="284" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5">
         <v>283</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C284" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D284" s="13" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="E284" s="13" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="F284" s="13" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
       <c r="G284" s="13" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="H284" s="13" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="285" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5">
         <v>284</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C285" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="E285" s="13">
         <v>2</v>
@@ -12359,74 +12334,74 @@
         <v>124</v>
       </c>
     </row>
-    <row r="286" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5">
         <v>285</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="E286" s="13" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
       <c r="F286" s="13" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="G286" s="13" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="H286" s="13"/>
       <c r="I286" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="287" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5">
         <v>286</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D287" s="13" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="E287" s="13" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="F287" s="13" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
       <c r="G287" s="13" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="H287" s="13" t="s">
-        <v>1053</v>
+        <v>1048</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="288" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5">
         <v>287</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C288" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D288" s="13" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="E288" s="13"/>
       <c r="F288" s="13"/>
@@ -12436,18 +12411,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5">
         <v>288</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C289" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="E289" s="13"/>
       <c r="F289" s="13"/>
@@ -12457,18 +12432,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="5">
         <v>289</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C290" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="E290" s="13"/>
       <c r="F290" s="13"/>
@@ -12478,18 +12453,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5">
         <v>290</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C291" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="E291" s="13"/>
       <c r="F291" s="13"/>
@@ -12499,18 +12474,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5">
         <v>291</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C292" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D292" s="13" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="E292" s="13"/>
       <c r="F292" s="13"/>
@@ -12520,45 +12495,47 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="14">
         <v>292</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C293" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D293" s="30" t="s">
-        <v>1060</v>
+        <v>1055</v>
       </c>
       <c r="E293" s="30" t="s">
-        <v>1061</v>
+        <v>1056</v>
       </c>
       <c r="F293" s="30" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="G293" s="30" t="s">
-        <v>1063</v>
-      </c>
-      <c r="H293" s="30"/>
+        <v>1058</v>
+      </c>
+      <c r="H293" s="30" t="s">
+        <v>1076</v>
+      </c>
       <c r="I293" s="24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="294" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="14">
         <v>293</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C294" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D294" s="30" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="E294" s="30"/>
       <c r="F294" s="30"/>
@@ -12568,72 +12545,76 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="14">
         <v>294</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C295" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D295" s="30" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="E295" s="30" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
       <c r="F295" s="30" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="G295" s="30" t="s">
-        <v>1068</v>
-      </c>
-      <c r="H295" s="30"/>
+        <v>1063</v>
+      </c>
+      <c r="H295" s="30" t="s">
+        <v>1076</v>
+      </c>
       <c r="I295" s="24" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="296" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="14">
         <v>295</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C296" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D296" s="30" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="E296" s="30" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="F296" s="30" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="G296" s="30" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H296" s="30"/>
+        <v>1066</v>
+      </c>
+      <c r="H296" s="30" t="s">
+        <v>1076</v>
+      </c>
       <c r="I296" s="24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="297" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="14">
         <v>296</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C297" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D297" s="30" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="E297" s="30"/>
       <c r="F297" s="30"/>
@@ -12643,130 +12624,134 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="14">
         <v>297</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C298" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D298" s="30" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="E298" s="30" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="F298" s="30" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="G298" s="30" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H298" s="30" t="s">
         <v>1076</v>
       </c>
-      <c r="H298" s="30"/>
       <c r="I298" s="24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="299" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="14">
         <v>298</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C299" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D299" s="29" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="E299" s="30" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="F299" s="30" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="G299" s="30" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="H299" s="30" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
       <c r="I299" s="30" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="300" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="14">
         <v>299</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C300" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D300" s="30" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="E300" s="30" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="F300" s="30" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="G300" s="30" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H300" s="30"/>
+        <v>1080</v>
+      </c>
+      <c r="H300" s="30" t="s">
+        <v>1076</v>
+      </c>
       <c r="I300" s="24" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="301" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5">
         <v>300</v>
       </c>
       <c r="B301" s="8" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D301" s="13" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F301" s="13" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G301" s="13" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H301" s="13" t="s">
         <v>1086</v>
-      </c>
-      <c r="C301" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D301" s="13" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E301" s="13" t="s">
-        <v>1088</v>
-      </c>
-      <c r="F301" s="13" t="s">
-        <v>1089</v>
-      </c>
-      <c r="G301" s="13" t="s">
-        <v>1090</v>
-      </c>
-      <c r="H301" s="13" t="s">
-        <v>1091</v>
       </c>
       <c r="I301" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="302" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5">
         <v>301</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C302" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D302" s="13" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="E302" s="13">
         <v>155</v>
@@ -12784,76 +12769,76 @@
         <v>123</v>
       </c>
     </row>
-    <row r="303" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5">
         <v>302</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C303" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D303" s="13" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="E303" s="13" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="F303" s="13" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="G303" s="13" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
       <c r="H303" s="13" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="I303" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="304" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5">
         <v>303</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C304" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="E304" s="13" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F304" s="13" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="G304" s="13" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="H304" s="13" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="I304" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="305" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5">
         <v>304</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C305" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D305" s="13" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="E305" s="13">
         <v>20</v>
@@ -12871,146 +12856,146 @@
         <v>123</v>
       </c>
     </row>
-    <row r="306" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5">
         <v>305</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C306" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D306" s="13" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="E306" s="13" t="s">
-        <v>1103</v>
+        <v>1098</v>
       </c>
       <c r="F306" s="13" t="s">
-        <v>1104</v>
+        <v>1099</v>
       </c>
       <c r="G306" s="13" t="s">
-        <v>1105</v>
+        <v>1100</v>
       </c>
       <c r="H306" s="13" t="s">
-        <v>1106</v>
+        <v>1101</v>
       </c>
       <c r="I306" s="5" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="307" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5">
         <v>306</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C307" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D307" s="13" t="s">
-        <v>1107</v>
+        <v>1102</v>
       </c>
       <c r="E307" s="13" t="s">
-        <v>1108</v>
+        <v>1103</v>
       </c>
       <c r="F307" s="13" t="s">
-        <v>1109</v>
+        <v>1104</v>
       </c>
       <c r="G307" s="13" t="s">
-        <v>1110</v>
+        <v>1105</v>
       </c>
       <c r="H307" s="13" t="s">
-        <v>1111</v>
+        <v>1106</v>
       </c>
       <c r="I307" s="5" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="308" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="5">
         <v>307</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C308" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="E308" s="13" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F308" s="13" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="G308" s="13" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="H308" s="13" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="I308" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="309" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5">
         <v>308</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C309" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="E309" s="13" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="G309" s="13" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
       <c r="H309" s="13" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="I309" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="310" spans="1:9" ht="20.100000000000001" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5">
         <v>309</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
       <c r="C310" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D310" s="13" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="E310" s="13" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="F310" s="13" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="G310" s="13" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="H310" s="13" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
       <c r="I310" s="5" t="s">
         <v>7</v>
@@ -13021,25 +13006,25 @@
         <v>310</v>
       </c>
       <c r="B311" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C311" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D311" s="30" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="E311" s="30" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="F311" s="30" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="G311" s="30" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
       <c r="H311" s="30" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="I311" s="14" t="s">
         <v>13</v>
@@ -13050,25 +13035,25 @@
         <v>311</v>
       </c>
       <c r="B312" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C312" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D312" s="30" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="E312" s="30" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="F312" s="30" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="G312" s="30" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
       <c r="H312" s="30" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="I312" s="14" t="s">
         <v>13</v>
@@ -13079,25 +13064,25 @@
         <v>312</v>
       </c>
       <c r="B313" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C313" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D313" s="30" t="s">
-        <v>1128</v>
+        <v>1123</v>
       </c>
       <c r="E313" s="30" t="s">
-        <v>1129</v>
+        <v>1124</v>
       </c>
       <c r="F313" s="30" t="s">
-        <v>1130</v>
+        <v>1125</v>
       </c>
       <c r="G313" s="30" t="s">
-        <v>1131</v>
+        <v>1126</v>
       </c>
       <c r="H313" s="30" t="s">
-        <v>1132</v>
+        <v>1127</v>
       </c>
       <c r="I313" s="14" t="s">
         <v>123</v>
@@ -13108,25 +13093,25 @@
         <v>313</v>
       </c>
       <c r="B314" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C314" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D314" s="30" t="s">
-        <v>1133</v>
+        <v>1128</v>
       </c>
       <c r="E314" s="30" t="s">
-        <v>1134</v>
+        <v>1129</v>
       </c>
       <c r="F314" s="30" t="s">
-        <v>1135</v>
+        <v>1130</v>
       </c>
       <c r="G314" s="30" t="s">
-        <v>1136</v>
+        <v>1131</v>
       </c>
       <c r="H314" s="30" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="I314" s="14" t="s">
         <v>124</v>
@@ -13137,25 +13122,25 @@
         <v>314</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C315" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D315" s="30" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="E315" s="30" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="F315" s="30" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="G315" s="30" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
       <c r="H315" s="30" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="I315" s="14" t="s">
         <v>13</v>
@@ -13166,25 +13151,25 @@
         <v>315</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C316" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D316" s="30" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="E316" s="30" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="F316" s="30" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="G316" s="30" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
       <c r="H316" s="30" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="I316" s="14" t="s">
         <v>7</v>
@@ -13195,25 +13180,25 @@
         <v>316</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C317" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D317" s="30" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="E317" s="30" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="F317" s="30" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="G317" s="30" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
       <c r="H317" s="30" t="s">
-        <v>1152</v>
+        <v>1147</v>
       </c>
       <c r="I317" s="14" t="s">
         <v>123</v>
@@ -13224,25 +13209,25 @@
         <v>317</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C318" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D318" s="30" t="s">
-        <v>1153</v>
+        <v>1148</v>
       </c>
       <c r="E318" s="30" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="F318" s="30" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="G318" s="30" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="H318" s="30" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="I318" s="14" t="s">
         <v>124</v>
@@ -13253,25 +13238,25 @@
         <v>318</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C319" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D319" s="30" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="E319" s="30" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="F319" s="30" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="G319" s="30" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="H319" s="30" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
       <c r="I319" s="14" t="s">
         <v>13</v>
@@ -13282,42 +13267,42 @@
         <v>319</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C320" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D320" s="30" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="E320" s="30" t="s">
-        <v>1154</v>
+        <v>1149</v>
       </c>
       <c r="F320" s="30" t="s">
-        <v>1155</v>
+        <v>1150</v>
       </c>
       <c r="G320" s="30" t="s">
-        <v>1156</v>
+        <v>1151</v>
       </c>
       <c r="H320" s="30" t="s">
-        <v>1157</v>
+        <v>1152</v>
       </c>
       <c r="I320" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A321" s="8">
         <v>327</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C321" s="9" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D321" s="13" t="s">
-        <v>1054</v>
+        <v>1049</v>
       </c>
       <c r="E321" s="13"/>
       <c r="F321" s="13"/>
@@ -13327,18 +13312,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A322" s="8">
         <v>328</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C322" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>1055</v>
+        <v>1050</v>
       </c>
       <c r="E322" s="13"/>
       <c r="F322" s="13"/>
@@ -13348,18 +13333,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A323" s="8">
         <v>329</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C323" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D323" s="13" t="s">
-        <v>1056</v>
+        <v>1051</v>
       </c>
       <c r="E323" s="13"/>
       <c r="F323" s="13"/>
@@ -13369,18 +13354,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A324" s="8">
         <v>330</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C324" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D324" s="13" t="s">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="E324" s="13"/>
       <c r="F324" s="13"/>
@@ -13390,18 +13375,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A325" s="8">
         <v>331</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="C325" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D325" s="13" t="s">
-        <v>1058</v>
+        <v>1053</v>
       </c>
       <c r="E325" s="13"/>
       <c r="F325" s="13"/>
@@ -13411,18 +13396,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A326" s="8">
         <v>333</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C326" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D326" s="13" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="E326" s="13"/>
       <c r="F326" s="13"/>
@@ -13432,18 +13417,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:9" ht="18" hidden="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A327" s="8">
         <v>336</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>1059</v>
+        <v>1054</v>
       </c>
       <c r="C327" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="E327" s="13"/>
       <c r="F327" s="13"/>

--- a/Extra Data for project/Questions files/Questions Full Data.xlsx
+++ b/Extra Data for project/Questions files/Questions Full Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{817DEB56-94E4-4B10-AC0D-D7B56166C45E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{340CBE77-C59F-48B0-B7F5-754DA8D8EB7E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" xr2:uid="{669F632A-8C17-464B-B497-7F400C39EC04}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2102" uniqueCount="1165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2196" uniqueCount="1163">
   <si>
     <t>5S</t>
   </si>
@@ -1954,9 +1954,6 @@
   </si>
   <si>
     <t>الحفاظ على الخرطوم من الثني أثناء التصريف</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ربط غطاء وصلة الصرف لتحقيق العزم المطلوب </t>
   </si>
   <si>
     <t>ما فائدة الفلتر 12/10</t>
@@ -2731,9 +2728,6 @@
     <t>ماهى عدد الاقتراحات المطلوبه من الفنى خلال الشهر؟</t>
   </si>
   <si>
-    <t>c</t>
-  </si>
-  <si>
     <t>تخطيط المصنع-ورشة البايبكس</t>
   </si>
   <si>
@@ -2780,9 +2774,6 @@
   </si>
   <si>
     <t>الرفع بيد واحدة فقط مع إبعاد الحمل عن الجسم.</t>
-  </si>
-  <si>
-    <t>b</t>
   </si>
   <si>
     <t>عند نقل عربات البايبكس المليئة بالمكونات داخل صالة الإنتاج، أيهما أفضل صحياً وأماناً للفني ولماذا؟</t>
@@ -3079,9 +3070,6 @@
     <t>كهنه</t>
   </si>
   <si>
-    <t>a</t>
-  </si>
-  <si>
     <t xml:space="preserve">يتم قياس عزل لماتور عن طريق  </t>
   </si>
   <si>
@@ -3823,6 +3811,12 @@
   </si>
   <si>
     <t xml:space="preserve">هل فائدة مفك تربيط وصلة الصرف 7/10 هي ربط غطاء وصلة الصرف لتحقيق العزم المطلوب </t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
   </si>
 </sst>
 </file>
@@ -4386,6 +4380,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{41C0B1BB-6F04-448A-B009-4F47191C9A95}" name="Table1" displayName="Table1" ref="A1:I327" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
+  <autoFilter ref="A1:I327" xr:uid="{8297F3F0-65A1-470E-A4DE-C6E4949A0EA3}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{5C073B83-7C73-4184-8CC7-F33AC31FB225}" name="Q_ID" dataDxfId="8"/>
     <tableColumn id="2" xr3:uid="{5A4F9621-DF8D-4586-86DF-8B411C00F3E2}" name="Category" dataDxfId="7"/>
@@ -4702,10 +4697,10 @@
   <sheetFormatPr defaultColWidth="25.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="3" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" style="3" customWidth="1"/>
-    <col min="4" max="4" width="63.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="40.5703125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9.28515625" style="3" customWidth="1"/>
+    <col min="4" max="4" width="89.140625" style="3" customWidth="1"/>
+    <col min="5" max="5" width="26.7109375" style="3" customWidth="1"/>
     <col min="6" max="6" width="31.140625" style="3" customWidth="1"/>
     <col min="7" max="7" width="34.7109375" style="3" customWidth="1"/>
     <col min="8" max="8" width="30" style="3" customWidth="1"/>
@@ -5194,8 +5189,8 @@
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="14"/>
-      <c r="I17" s="14">
-        <v>1</v>
+      <c r="I17" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5215,8 +5210,8 @@
       <c r="F18" s="14"/>
       <c r="G18" s="14"/>
       <c r="H18" s="14"/>
-      <c r="I18" s="14">
-        <v>0</v>
+      <c r="I18" s="14" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="19" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5236,8 +5231,8 @@
       <c r="F19" s="14"/>
       <c r="G19" s="14"/>
       <c r="H19" s="14"/>
-      <c r="I19" s="14">
-        <v>1</v>
+      <c r="I19" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5257,8 +5252,8 @@
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
       <c r="H20" s="14"/>
-      <c r="I20" s="14">
-        <v>0</v>
+      <c r="I20" s="14" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5278,8 +5273,8 @@
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
       <c r="H21" s="14"/>
-      <c r="I21" s="14">
-        <v>1</v>
+      <c r="I21" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5299,8 +5294,8 @@
       <c r="F22" s="14"/>
       <c r="G22" s="14"/>
       <c r="H22" s="14"/>
-      <c r="I22" s="14">
-        <v>1</v>
+      <c r="I22" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5320,8 +5315,8 @@
       <c r="F23" s="14"/>
       <c r="G23" s="14"/>
       <c r="H23" s="14"/>
-      <c r="I23" s="14">
-        <v>0</v>
+      <c r="I23" s="14" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5341,8 +5336,8 @@
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
       <c r="H24" s="14"/>
-      <c r="I24" s="14">
-        <v>1</v>
+      <c r="I24" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="25" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5362,8 +5357,8 @@
       <c r="F25" s="14"/>
       <c r="G25" s="14"/>
       <c r="H25" s="14"/>
-      <c r="I25" s="14">
-        <v>0</v>
+      <c r="I25" s="14" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5383,8 +5378,8 @@
       <c r="F26" s="14"/>
       <c r="G26" s="14"/>
       <c r="H26" s="14"/>
-      <c r="I26" s="14">
-        <v>1</v>
+      <c r="I26" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5839,8 +5834,8 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
-      <c r="I42" s="5">
-        <v>1</v>
+      <c r="I42" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="43" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5860,8 +5855,8 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
-      <c r="I43" s="5">
-        <v>0</v>
+      <c r="I43" s="5" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="44" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5881,8 +5876,8 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
-      <c r="I44" s="5">
-        <v>1</v>
+      <c r="I44" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="45" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5902,8 +5897,8 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
-      <c r="I45" s="5">
-        <v>1</v>
+      <c r="I45" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="46" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5923,8 +5918,8 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="5">
-        <v>0</v>
+      <c r="I46" s="5" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="47" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5944,8 +5939,8 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="5">
-        <v>1</v>
+      <c r="I47" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="48" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5965,8 +5960,8 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48" s="5">
-        <v>1</v>
+      <c r="I48" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5986,8 +5981,8 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="5">
-        <v>0</v>
+      <c r="I49" s="5" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="50" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6007,8 +6002,8 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="5">
-        <v>1</v>
+      <c r="I50" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6028,8 +6023,8 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51" s="5">
-        <v>1</v>
+      <c r="I51" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="52" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6101,10 +6096,10 @@
         <v>76</v>
       </c>
       <c r="D54" s="16" t="s">
+        <v>827</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>828</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>829</v>
       </c>
       <c r="F54" s="17" t="s">
         <v>177</v>
@@ -6188,7 +6183,7 @@
         <v>76</v>
       </c>
       <c r="D57" s="16" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E57" s="20">
         <v>0.1</v>
@@ -6252,8 +6247,8 @@
       <c r="F59" s="22"/>
       <c r="G59" s="22"/>
       <c r="H59" s="22"/>
-      <c r="I59" s="22">
-        <v>0</v>
+      <c r="I59" s="22" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="60" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6273,8 +6268,8 @@
       <c r="F60" s="22"/>
       <c r="G60" s="22"/>
       <c r="H60" s="22"/>
-      <c r="I60" s="22">
-        <v>1</v>
+      <c r="I60" s="22" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="61" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -6317,7 +6312,7 @@
         <v>76</v>
       </c>
       <c r="D62" s="16" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E62" s="20">
         <v>0.3</v>
@@ -7019,8 +7014,8 @@
       <c r="F86" s="1"/>
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
-      <c r="I86" s="1">
-        <v>1</v>
+      <c r="I86" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="87" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7214,8 +7209,8 @@
       <c r="F93" s="1"/>
       <c r="G93" s="1"/>
       <c r="H93" s="1"/>
-      <c r="I93" s="1">
-        <v>1</v>
+      <c r="I93" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="94" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7235,8 +7230,8 @@
       <c r="F94" s="1"/>
       <c r="G94" s="1"/>
       <c r="H94" s="1"/>
-      <c r="I94" s="1">
-        <v>1</v>
+      <c r="I94" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="95" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7256,8 +7251,8 @@
       <c r="F95" s="1"/>
       <c r="G95" s="1"/>
       <c r="H95" s="1"/>
-      <c r="I95" s="1">
-        <v>1</v>
+      <c r="I95" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="96" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7857,8 +7852,8 @@
       <c r="F116" s="25"/>
       <c r="G116" s="25"/>
       <c r="H116" s="25"/>
-      <c r="I116" s="23">
-        <v>0</v>
+      <c r="I116" s="23" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="117" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7878,8 +7873,8 @@
       <c r="F117" s="25"/>
       <c r="G117" s="25"/>
       <c r="H117" s="25"/>
-      <c r="I117" s="14">
-        <v>1</v>
+      <c r="I117" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="118" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7899,8 +7894,8 @@
       <c r="F118" s="25"/>
       <c r="G118" s="25"/>
       <c r="H118" s="25"/>
-      <c r="I118" s="23">
-        <v>0</v>
+      <c r="I118" s="23" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="119" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7920,8 +7915,8 @@
       <c r="F119" s="25"/>
       <c r="G119" s="25"/>
       <c r="H119" s="25"/>
-      <c r="I119" s="14">
-        <v>1</v>
+      <c r="I119" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="120" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7941,8 +7936,8 @@
       <c r="F120" s="25"/>
       <c r="G120" s="25"/>
       <c r="H120" s="25"/>
-      <c r="I120" s="23">
-        <v>0</v>
+      <c r="I120" s="23" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="121" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -7962,8 +7957,8 @@
       <c r="F121" s="14"/>
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
-      <c r="I121" s="14">
-        <v>1</v>
+      <c r="I121" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="122" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8099,8 +8094,8 @@
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
       <c r="H126" s="2"/>
-      <c r="I126" s="4">
-        <v>0</v>
+      <c r="I126" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="127" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8236,8 +8231,8 @@
       <c r="F131" s="5"/>
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
-      <c r="I131" s="4">
-        <v>0</v>
+      <c r="I131" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="132" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8257,8 +8252,8 @@
       <c r="F132" s="5"/>
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
-      <c r="I132" s="4">
-        <v>0</v>
+      <c r="I132" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="133" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8278,8 +8273,8 @@
       <c r="F133" s="5"/>
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
-      <c r="I133" s="4">
-        <v>0</v>
+      <c r="I133" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="134" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8299,8 +8294,8 @@
       <c r="F134" s="5"/>
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
-      <c r="I134" s="4">
-        <v>0</v>
+      <c r="I134" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="135" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8320,8 +8315,8 @@
       <c r="F135" s="5"/>
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
-      <c r="I135" s="4">
-        <v>0</v>
+      <c r="I135" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="136" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8393,7 +8388,7 @@
         <v>1</v>
       </c>
       <c r="D138" s="14" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E138" s="14" t="s">
         <v>487</v>
@@ -8608,7 +8603,7 @@
         <v>523</v>
       </c>
       <c r="H145" s="14" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="I145" s="23" t="s">
         <v>13</v>
@@ -8631,8 +8626,8 @@
       <c r="F146" s="5"/>
       <c r="G146" s="5"/>
       <c r="H146" s="5"/>
-      <c r="I146" s="4">
-        <v>0</v>
+      <c r="I146" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="147" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8652,8 +8647,8 @@
       <c r="F147" s="5"/>
       <c r="G147" s="5"/>
       <c r="H147" s="5"/>
-      <c r="I147" s="4">
-        <v>0</v>
+      <c r="I147" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="148" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8673,8 +8668,8 @@
       <c r="F148" s="5"/>
       <c r="G148" s="5"/>
       <c r="H148" s="5"/>
-      <c r="I148" s="4">
-        <v>0</v>
+      <c r="I148" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="149" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8694,8 +8689,8 @@
       <c r="F149" s="5"/>
       <c r="G149" s="5"/>
       <c r="H149" s="5"/>
-      <c r="I149" s="4">
-        <v>0</v>
+      <c r="I149" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="150" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8715,8 +8710,8 @@
       <c r="F150" s="5"/>
       <c r="G150" s="5"/>
       <c r="H150" s="5"/>
-      <c r="I150" s="5">
-        <v>1</v>
+      <c r="I150" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="151" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8730,14 +8725,14 @@
         <v>65</v>
       </c>
       <c r="D151" s="5" t="s">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
       <c r="G151" s="5"/>
       <c r="H151" s="5"/>
-      <c r="I151" s="4">
-        <v>1</v>
+      <c r="I151" s="4" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="152" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -8792,7 +8787,7 @@
         <v>538</v>
       </c>
       <c r="H153" s="5" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="I153" s="4" t="s">
         <v>123</v>
@@ -8847,10 +8842,10 @@
         <v>546</v>
       </c>
       <c r="G155" s="5" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="H155" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="I155" s="4" t="s">
         <v>7</v>
@@ -9163,8 +9158,8 @@
       <c r="F166" s="5"/>
       <c r="G166" s="5"/>
       <c r="H166" s="5"/>
-      <c r="I166" s="4">
-        <v>0</v>
+      <c r="I166" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="167" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9184,8 +9179,8 @@
       <c r="F167" s="5"/>
       <c r="G167" s="5"/>
       <c r="H167" s="5"/>
-      <c r="I167" s="4">
-        <v>0</v>
+      <c r="I167" s="4" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="168" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9196,17 +9191,17 @@
         <v>624</v>
       </c>
       <c r="C168" s="5" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>1163</v>
+        <v>1159</v>
       </c>
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="5"/>
       <c r="H168" s="5"/>
-      <c r="I168" s="4">
-        <v>1</v>
+      <c r="I168" s="4" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="169" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9304,19 +9299,17 @@
         <v>624</v>
       </c>
       <c r="C172" s="5" t="s">
-        <v>1</v>
+        <v>65</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E172" s="5" t="s">
-        <v>642</v>
-      </c>
+        <v>1160</v>
+      </c>
+      <c r="E172" s="5"/>
       <c r="F172" s="5"/>
       <c r="G172" s="5"/>
       <c r="H172" s="5"/>
       <c r="I172" s="4" t="s">
-        <v>7</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="173" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9330,19 +9323,19 @@
         <v>1</v>
       </c>
       <c r="D173" s="5" t="s">
+        <v>642</v>
+      </c>
+      <c r="E173" s="5" t="s">
         <v>643</v>
       </c>
-      <c r="E173" s="5" t="s">
+      <c r="F173" s="5" t="s">
         <v>644</v>
       </c>
-      <c r="F173" s="5" t="s">
+      <c r="G173" s="5" t="s">
         <v>645</v>
       </c>
-      <c r="G173" s="5" t="s">
+      <c r="H173" s="5" t="s">
         <v>646</v>
-      </c>
-      <c r="H173" s="5" t="s">
-        <v>647</v>
       </c>
       <c r="I173" s="4" t="s">
         <v>123</v>
@@ -9359,19 +9352,19 @@
         <v>1</v>
       </c>
       <c r="D174" s="5" t="s">
+        <v>647</v>
+      </c>
+      <c r="E174" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="E174" s="5" t="s">
+      <c r="F174" s="5" t="s">
         <v>649</v>
       </c>
-      <c r="F174" s="5" t="s">
+      <c r="G174" s="5" t="s">
         <v>650</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="H174" s="5" t="s">
         <v>651</v>
-      </c>
-      <c r="H174" s="5" t="s">
-        <v>652</v>
       </c>
       <c r="I174" s="4" t="s">
         <v>7</v>
@@ -9388,19 +9381,19 @@
         <v>1</v>
       </c>
       <c r="D175" s="5" t="s">
+        <v>652</v>
+      </c>
+      <c r="E175" s="5" t="s">
         <v>653</v>
       </c>
-      <c r="E175" s="5" t="s">
+      <c r="F175" s="5" t="s">
         <v>654</v>
       </c>
-      <c r="F175" s="5" t="s">
+      <c r="G175" s="5" t="s">
         <v>655</v>
       </c>
-      <c r="G175" s="5" t="s">
+      <c r="H175" s="5" t="s">
         <v>656</v>
-      </c>
-      <c r="H175" s="5" t="s">
-        <v>657</v>
       </c>
       <c r="I175" s="4" t="s">
         <v>123</v>
@@ -9411,25 +9404,25 @@
         <v>175</v>
       </c>
       <c r="B176" s="25" t="s">
+        <v>657</v>
+      </c>
+      <c r="C176" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D176" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="C176" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D176" s="14" t="s">
+      <c r="E176" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="E176" s="14" t="s">
+      <c r="F176" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="F176" s="14" t="s">
+      <c r="G176" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="G176" s="14" t="s">
+      <c r="H176" s="14" t="s">
         <v>662</v>
-      </c>
-      <c r="H176" s="14" t="s">
-        <v>663</v>
       </c>
       <c r="I176" s="23" t="s">
         <v>7</v>
@@ -9440,25 +9433,25 @@
         <v>176</v>
       </c>
       <c r="B177" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C177" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D177" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="E177" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="E177" s="14" t="s">
+      <c r="F177" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="F177" s="14" t="s">
+      <c r="G177" s="14" t="s">
         <v>666</v>
       </c>
-      <c r="G177" s="14" t="s">
+      <c r="H177" s="14" t="s">
         <v>667</v>
-      </c>
-      <c r="H177" s="14" t="s">
-        <v>668</v>
       </c>
       <c r="I177" s="23" t="s">
         <v>13</v>
@@ -9469,25 +9462,25 @@
         <v>177</v>
       </c>
       <c r="B178" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C178" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D178" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="E178" s="14" t="s">
         <v>669</v>
       </c>
-      <c r="E178" s="14" t="s">
+      <c r="F178" s="14" t="s">
         <v>670</v>
       </c>
-      <c r="F178" s="14" t="s">
+      <c r="G178" s="14" t="s">
         <v>671</v>
       </c>
-      <c r="G178" s="14" t="s">
+      <c r="H178" s="14" t="s">
         <v>672</v>
-      </c>
-      <c r="H178" s="14" t="s">
-        <v>673</v>
       </c>
       <c r="I178" s="23" t="s">
         <v>123</v>
@@ -9498,25 +9491,25 @@
         <v>178</v>
       </c>
       <c r="B179" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C179" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D179" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="E179" s="14" t="s">
         <v>674</v>
       </c>
-      <c r="E179" s="14" t="s">
+      <c r="F179" s="14" t="s">
         <v>675</v>
       </c>
-      <c r="F179" s="14" t="s">
+      <c r="G179" s="14" t="s">
         <v>676</v>
       </c>
-      <c r="G179" s="14" t="s">
+      <c r="H179" s="14" t="s">
         <v>677</v>
-      </c>
-      <c r="H179" s="14" t="s">
-        <v>678</v>
       </c>
       <c r="I179" s="23" t="s">
         <v>124</v>
@@ -9527,25 +9520,25 @@
         <v>179</v>
       </c>
       <c r="B180" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C180" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D180" s="14" t="s">
+        <v>678</v>
+      </c>
+      <c r="E180" s="14" t="s">
         <v>679</v>
       </c>
-      <c r="E180" s="14" t="s">
+      <c r="F180" s="14" t="s">
         <v>680</v>
       </c>
-      <c r="F180" s="14" t="s">
+      <c r="G180" s="14" t="s">
         <v>681</v>
       </c>
-      <c r="G180" s="14" t="s">
+      <c r="H180" s="14" t="s">
         <v>682</v>
-      </c>
-      <c r="H180" s="14" t="s">
-        <v>683</v>
       </c>
       <c r="I180" s="23" t="s">
         <v>123</v>
@@ -9556,25 +9549,25 @@
         <v>180</v>
       </c>
       <c r="B181" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C181" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D181" s="14" t="s">
+        <v>683</v>
+      </c>
+      <c r="E181" s="14" t="s">
         <v>684</v>
       </c>
-      <c r="E181" s="14" t="s">
+      <c r="F181" s="14" t="s">
         <v>685</v>
       </c>
-      <c r="F181" s="14" t="s">
+      <c r="G181" s="14" t="s">
         <v>686</v>
       </c>
-      <c r="G181" s="14" t="s">
+      <c r="H181" s="14" t="s">
         <v>687</v>
-      </c>
-      <c r="H181" s="14" t="s">
-        <v>688</v>
       </c>
       <c r="I181" s="23" t="s">
         <v>124</v>
@@ -9585,25 +9578,25 @@
         <v>181</v>
       </c>
       <c r="B182" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C182" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D182" s="14" t="s">
+        <v>688</v>
+      </c>
+      <c r="E182" s="14" t="s">
         <v>689</v>
       </c>
-      <c r="E182" s="14" t="s">
+      <c r="F182" s="14" t="s">
         <v>690</v>
       </c>
-      <c r="F182" s="14" t="s">
+      <c r="G182" s="14" t="s">
         <v>691</v>
       </c>
-      <c r="G182" s="14" t="s">
+      <c r="H182" s="14" t="s">
         <v>692</v>
-      </c>
-      <c r="H182" s="14" t="s">
-        <v>693</v>
       </c>
       <c r="I182" s="23" t="s">
         <v>13</v>
@@ -9614,25 +9607,25 @@
         <v>182</v>
       </c>
       <c r="B183" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C183" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D183" s="14" t="s">
+        <v>693</v>
+      </c>
+      <c r="E183" s="14" t="s">
         <v>694</v>
       </c>
-      <c r="E183" s="14" t="s">
+      <c r="F183" s="14" t="s">
         <v>695</v>
       </c>
-      <c r="F183" s="14" t="s">
+      <c r="G183" s="14" t="s">
         <v>696</v>
       </c>
-      <c r="G183" s="14" t="s">
+      <c r="H183" s="14" t="s">
         <v>697</v>
-      </c>
-      <c r="H183" s="14" t="s">
-        <v>698</v>
       </c>
       <c r="I183" s="23" t="s">
         <v>7</v>
@@ -9643,25 +9636,25 @@
         <v>183</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C184" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D184" s="14" t="s">
+        <v>698</v>
+      </c>
+      <c r="E184" s="14" t="s">
         <v>699</v>
       </c>
-      <c r="E184" s="14" t="s">
+      <c r="F184" s="14" t="s">
         <v>700</v>
       </c>
-      <c r="F184" s="14" t="s">
+      <c r="G184" s="14" t="s">
         <v>701</v>
       </c>
-      <c r="G184" s="14" t="s">
+      <c r="H184" s="14" t="s">
         <v>702</v>
-      </c>
-      <c r="H184" s="14" t="s">
-        <v>703</v>
       </c>
       <c r="I184" s="23" t="s">
         <v>123</v>
@@ -9672,25 +9665,25 @@
         <v>184</v>
       </c>
       <c r="B185" s="25" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C185" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D185" s="14" t="s">
+        <v>703</v>
+      </c>
+      <c r="E185" s="14" t="s">
         <v>704</v>
       </c>
-      <c r="E185" s="14" t="s">
+      <c r="F185" s="14" t="s">
         <v>705</v>
       </c>
-      <c r="F185" s="14" t="s">
+      <c r="G185" s="14" t="s">
         <v>706</v>
       </c>
-      <c r="G185" s="14" t="s">
+      <c r="H185" s="14" t="s">
         <v>707</v>
-      </c>
-      <c r="H185" s="14" t="s">
-        <v>708</v>
       </c>
       <c r="I185" s="23" t="s">
         <v>124</v>
@@ -9701,20 +9694,20 @@
         <v>185</v>
       </c>
       <c r="B186" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C186" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D186" s="6" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E186" s="6"/>
       <c r="F186" s="6"/>
       <c r="G186" s="6"/>
       <c r="H186" s="6"/>
-      <c r="I186" s="7">
-        <v>1</v>
+      <c r="I186" s="7" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="187" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9722,20 +9715,20 @@
         <v>186</v>
       </c>
       <c r="B187" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C187" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D187" s="6" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E187" s="6"/>
       <c r="F187" s="6"/>
       <c r="G187" s="6"/>
       <c r="H187" s="6"/>
-      <c r="I187" s="7">
-        <v>0</v>
+      <c r="I187" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="188" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9743,20 +9736,20 @@
         <v>187</v>
       </c>
       <c r="B188" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C188" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D188" s="6" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E188" s="6"/>
       <c r="F188" s="6"/>
       <c r="G188" s="6"/>
       <c r="H188" s="6"/>
-      <c r="I188" s="7">
-        <v>0</v>
+      <c r="I188" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="189" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9764,20 +9757,20 @@
         <v>188</v>
       </c>
       <c r="B189" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C189" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E189" s="6"/>
       <c r="F189" s="6"/>
       <c r="G189" s="6"/>
       <c r="H189" s="6"/>
-      <c r="I189" s="7">
-        <v>0</v>
+      <c r="I189" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="190" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9785,20 +9778,20 @@
         <v>189</v>
       </c>
       <c r="B190" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C190" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D190" s="6" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E190" s="6"/>
       <c r="F190" s="6"/>
       <c r="G190" s="6"/>
       <c r="H190" s="6"/>
-      <c r="I190" s="7">
-        <v>0</v>
+      <c r="I190" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="191" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9806,25 +9799,25 @@
         <v>190</v>
       </c>
       <c r="B191" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C191" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D191" s="6" t="s">
+        <v>714</v>
+      </c>
+      <c r="E191" s="6" t="s">
         <v>715</v>
       </c>
-      <c r="E191" s="6" t="s">
+      <c r="F191" s="6" t="s">
         <v>716</v>
       </c>
-      <c r="F191" s="6" t="s">
+      <c r="G191" s="6" t="s">
         <v>717</v>
       </c>
-      <c r="G191" s="6" t="s">
+      <c r="H191" s="6" t="s">
         <v>718</v>
-      </c>
-      <c r="H191" s="6" t="s">
-        <v>719</v>
       </c>
       <c r="I191" s="7" t="s">
         <v>123</v>
@@ -9835,25 +9828,25 @@
         <v>191</v>
       </c>
       <c r="B192" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C192" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D192" s="6" t="s">
+        <v>719</v>
+      </c>
+      <c r="E192" s="6" t="s">
         <v>720</v>
       </c>
-      <c r="E192" s="6" t="s">
+      <c r="F192" s="6" t="s">
         <v>721</v>
       </c>
-      <c r="F192" s="6" t="s">
+      <c r="G192" s="6" t="s">
         <v>722</v>
       </c>
-      <c r="G192" s="6" t="s">
+      <c r="H192" s="6" t="s">
         <v>723</v>
-      </c>
-      <c r="H192" s="6" t="s">
-        <v>724</v>
       </c>
       <c r="I192" s="7" t="s">
         <v>7</v>
@@ -9864,25 +9857,25 @@
         <v>192</v>
       </c>
       <c r="B193" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C193" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D193" s="6" t="s">
+        <v>724</v>
+      </c>
+      <c r="E193" s="6" t="s">
         <v>725</v>
       </c>
-      <c r="E193" s="6" t="s">
+      <c r="F193" s="6" t="s">
         <v>726</v>
       </c>
-      <c r="F193" s="6" t="s">
+      <c r="G193" s="6" t="s">
         <v>727</v>
       </c>
-      <c r="G193" s="6" t="s">
+      <c r="H193" s="6" t="s">
         <v>728</v>
-      </c>
-      <c r="H193" s="6" t="s">
-        <v>729</v>
       </c>
       <c r="I193" s="7" t="s">
         <v>13</v>
@@ -9893,25 +9886,25 @@
         <v>193</v>
       </c>
       <c r="B194" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C194" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E194" s="6" t="s">
+        <v>729</v>
+      </c>
+      <c r="F194" s="6" t="s">
         <v>730</v>
       </c>
-      <c r="F194" s="6" t="s">
+      <c r="G194" s="6" t="s">
         <v>731</v>
       </c>
-      <c r="G194" s="6" t="s">
+      <c r="H194" s="6" t="s">
         <v>732</v>
-      </c>
-      <c r="H194" s="6" t="s">
-        <v>733</v>
       </c>
       <c r="I194" s="7" t="s">
         <v>13</v>
@@ -9922,25 +9915,25 @@
         <v>194</v>
       </c>
       <c r="B195" s="10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C195" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D195" s="5" t="s">
+        <v>733</v>
+      </c>
+      <c r="E195" s="6" t="s">
         <v>734</v>
       </c>
-      <c r="E195" s="6" t="s">
+      <c r="F195" s="6" t="s">
         <v>735</v>
       </c>
-      <c r="F195" s="6" t="s">
+      <c r="G195" s="6" t="s">
         <v>736</v>
       </c>
-      <c r="G195" s="6" t="s">
+      <c r="H195" s="6" t="s">
         <v>737</v>
-      </c>
-      <c r="H195" s="6" t="s">
-        <v>738</v>
       </c>
       <c r="I195" s="7" t="s">
         <v>124</v>
@@ -9951,20 +9944,20 @@
         <v>195</v>
       </c>
       <c r="B196" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C196" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E196" s="17"/>
       <c r="F196" s="17"/>
       <c r="G196" s="17"/>
       <c r="H196" s="17"/>
-      <c r="I196" s="16">
-        <v>1</v>
+      <c r="I196" s="16" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="197" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9972,20 +9965,20 @@
         <v>196</v>
       </c>
       <c r="B197" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C197" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D197" s="17" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E197" s="17"/>
       <c r="F197" s="17"/>
       <c r="G197" s="17"/>
       <c r="H197" s="17"/>
-      <c r="I197" s="16">
-        <v>0</v>
+      <c r="I197" s="16" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="198" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -9993,20 +9986,20 @@
         <v>197</v>
       </c>
       <c r="B198" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C198" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D198" s="17" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E198" s="17"/>
       <c r="F198" s="17"/>
       <c r="G198" s="17"/>
       <c r="H198" s="17"/>
-      <c r="I198" s="16">
-        <v>1</v>
+      <c r="I198" s="16" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="199" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10014,20 +10007,20 @@
         <v>198</v>
       </c>
       <c r="B199" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C199" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D199" s="17" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E199" s="17"/>
       <c r="F199" s="17"/>
       <c r="G199" s="17"/>
       <c r="H199" s="17"/>
-      <c r="I199" s="16">
-        <v>1</v>
+      <c r="I199" s="16" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="200" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10035,20 +10028,20 @@
         <v>199</v>
       </c>
       <c r="B200" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C200" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D200" s="16" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E200" s="17"/>
       <c r="F200" s="17"/>
       <c r="G200" s="17"/>
       <c r="H200" s="17"/>
-      <c r="I200" s="16">
-        <v>1</v>
+      <c r="I200" s="16" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="201" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10056,25 +10049,25 @@
         <v>200</v>
       </c>
       <c r="B201" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C201" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D201" s="17" t="s">
+        <v>743</v>
+      </c>
+      <c r="E201" s="17" t="s">
         <v>744</v>
       </c>
-      <c r="E201" s="17" t="s">
+      <c r="F201" s="17" t="s">
         <v>745</v>
       </c>
-      <c r="F201" s="17" t="s">
+      <c r="G201" s="17" t="s">
         <v>746</v>
       </c>
-      <c r="G201" s="17" t="s">
+      <c r="H201" s="17" t="s">
         <v>747</v>
-      </c>
-      <c r="H201" s="17" t="s">
-        <v>748</v>
       </c>
       <c r="I201" s="16" t="s">
         <v>123</v>
@@ -10085,25 +10078,25 @@
         <v>201</v>
       </c>
       <c r="B202" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C202" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D202" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="E202" s="17" t="s">
         <v>749</v>
       </c>
-      <c r="E202" s="17" t="s">
+      <c r="F202" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="F202" s="17" t="s">
+      <c r="G202" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="G202" s="17" t="s">
+      <c r="H202" s="17" t="s">
         <v>752</v>
-      </c>
-      <c r="H202" s="17" t="s">
-        <v>753</v>
       </c>
       <c r="I202" s="16" t="s">
         <v>124</v>
@@ -10114,25 +10107,25 @@
         <v>202</v>
       </c>
       <c r="B203" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C203" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D203" s="16" t="s">
+        <v>753</v>
+      </c>
+      <c r="E203" s="17" t="s">
         <v>754</v>
       </c>
-      <c r="E203" s="17" t="s">
+      <c r="F203" s="17" t="s">
         <v>755</v>
       </c>
-      <c r="F203" s="17" t="s">
+      <c r="G203" s="17" t="s">
         <v>756</v>
       </c>
-      <c r="G203" s="17" t="s">
+      <c r="H203" s="17" t="s">
         <v>757</v>
-      </c>
-      <c r="H203" s="17" t="s">
-        <v>758</v>
       </c>
       <c r="I203" s="21" t="s">
         <v>13</v>
@@ -10143,25 +10136,25 @@
         <v>203</v>
       </c>
       <c r="B204" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C204" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D204" s="16" t="s">
+        <v>758</v>
+      </c>
+      <c r="E204" s="17" t="s">
         <v>759</v>
       </c>
-      <c r="E204" s="17" t="s">
+      <c r="F204" s="17" t="s">
         <v>760</v>
       </c>
-      <c r="F204" s="17" t="s">
+      <c r="G204" s="17" t="s">
         <v>761</v>
       </c>
-      <c r="G204" s="17" t="s">
+      <c r="H204" s="17" t="s">
         <v>762</v>
-      </c>
-      <c r="H204" s="17" t="s">
-        <v>763</v>
       </c>
       <c r="I204" s="21" t="s">
         <v>7</v>
@@ -10172,25 +10165,25 @@
         <v>204</v>
       </c>
       <c r="B205" s="27" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C205" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D205" s="16" t="s">
+        <v>763</v>
+      </c>
+      <c r="E205" s="17" t="s">
         <v>764</v>
       </c>
-      <c r="E205" s="17" t="s">
+      <c r="F205" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="F205" s="17" t="s">
+      <c r="G205" s="17" t="s">
         <v>766</v>
       </c>
-      <c r="G205" s="17" t="s">
+      <c r="H205" s="17" t="s">
         <v>767</v>
-      </c>
-      <c r="H205" s="17" t="s">
-        <v>768</v>
       </c>
       <c r="I205" s="16" t="s">
         <v>123</v>
@@ -10201,20 +10194,20 @@
         <v>205</v>
       </c>
       <c r="B206" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D206" s="6" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="E206" s="6"/>
       <c r="F206" s="6"/>
       <c r="G206" s="6"/>
       <c r="H206" s="6"/>
-      <c r="I206" s="7">
-        <v>1</v>
+      <c r="I206" s="7" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="207" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10222,20 +10215,20 @@
         <v>206</v>
       </c>
       <c r="B207" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E207" s="6"/>
       <c r="F207" s="6"/>
       <c r="G207" s="6"/>
       <c r="H207" s="6"/>
-      <c r="I207" s="7">
-        <v>0</v>
+      <c r="I207" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="208" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10243,20 +10236,20 @@
         <v>207</v>
       </c>
       <c r="B208" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D208" s="7" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E208" s="6"/>
       <c r="F208" s="6"/>
       <c r="G208" s="6"/>
       <c r="H208" s="6"/>
-      <c r="I208" s="7">
-        <v>1</v>
+      <c r="I208" s="7" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="209" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10264,20 +10257,20 @@
         <v>208</v>
       </c>
       <c r="B209" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E209" s="6"/>
       <c r="F209" s="6"/>
       <c r="G209" s="6"/>
       <c r="H209" s="6"/>
-      <c r="I209" s="7">
-        <v>1</v>
+      <c r="I209" s="7" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="210" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10285,20 +10278,20 @@
         <v>209</v>
       </c>
       <c r="B210" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E210" s="6"/>
       <c r="F210" s="6"/>
       <c r="G210" s="6"/>
       <c r="H210" s="6"/>
-      <c r="I210" s="7">
-        <v>0</v>
+      <c r="I210" s="7" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="211" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10306,25 +10299,25 @@
         <v>210</v>
       </c>
       <c r="B211" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="E211" s="6" t="s">
         <v>81</v>
       </c>
       <c r="F211" s="6" t="s">
+        <v>774</v>
+      </c>
+      <c r="G211" s="6" t="s">
         <v>775</v>
       </c>
-      <c r="G211" s="6" t="s">
+      <c r="H211" s="6" t="s">
         <v>776</v>
-      </c>
-      <c r="H211" s="6" t="s">
-        <v>777</v>
       </c>
       <c r="I211" s="11" t="s">
         <v>13</v>
@@ -10335,25 +10328,25 @@
         <v>211</v>
       </c>
       <c r="B212" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D212" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="E212" s="6" t="s">
         <v>778</v>
       </c>
-      <c r="E212" s="6" t="s">
+      <c r="F212" s="6" t="s">
         <v>779</v>
       </c>
-      <c r="F212" s="6" t="s">
+      <c r="G212" s="6" t="s">
         <v>780</v>
       </c>
-      <c r="G212" s="6" t="s">
+      <c r="H212" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="H212" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="I212" s="11" t="s">
         <v>123</v>
@@ -10364,25 +10357,25 @@
         <v>212</v>
       </c>
       <c r="B213" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D213" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="E213" s="6" t="s">
         <v>783</v>
       </c>
-      <c r="E213" s="6" t="s">
+      <c r="F213" s="5" t="s">
         <v>784</v>
       </c>
-      <c r="F213" s="5" t="s">
+      <c r="G213" s="6" t="s">
         <v>785</v>
       </c>
-      <c r="G213" s="6" t="s">
+      <c r="H213" s="6" t="s">
         <v>786</v>
-      </c>
-      <c r="H213" s="6" t="s">
-        <v>787</v>
       </c>
       <c r="I213" s="11" t="s">
         <v>13</v>
@@ -10393,25 +10386,25 @@
         <v>213</v>
       </c>
       <c r="B214" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D214" s="6" t="s">
+        <v>787</v>
+      </c>
+      <c r="E214" s="6" t="s">
         <v>788</v>
       </c>
-      <c r="E214" s="6" t="s">
+      <c r="F214" s="6" t="s">
         <v>789</v>
       </c>
-      <c r="F214" s="6" t="s">
+      <c r="G214" s="6" t="s">
         <v>790</v>
       </c>
-      <c r="G214" s="6" t="s">
+      <c r="H214" s="6" t="s">
         <v>791</v>
-      </c>
-      <c r="H214" s="6" t="s">
-        <v>792</v>
       </c>
       <c r="I214" s="11" t="s">
         <v>13</v>
@@ -10422,25 +10415,25 @@
         <v>214</v>
       </c>
       <c r="B215" s="10" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>76</v>
       </c>
       <c r="D215" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="E215" s="6" t="s">
         <v>793</v>
       </c>
-      <c r="E215" s="6" t="s">
+      <c r="F215" s="6" t="s">
         <v>794</v>
       </c>
-      <c r="F215" s="6" t="s">
+      <c r="G215" s="6" t="s">
         <v>795</v>
       </c>
-      <c r="G215" s="6" t="s">
-        <v>796</v>
-      </c>
       <c r="H215" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I215" s="11" t="s">
         <v>124</v>
@@ -10451,20 +10444,20 @@
         <v>215</v>
       </c>
       <c r="B216" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C216" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D216" s="17" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E216" s="17"/>
       <c r="F216" s="17"/>
       <c r="G216" s="17"/>
       <c r="H216" s="17"/>
-      <c r="I216" s="19">
-        <v>1</v>
+      <c r="I216" s="19" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="217" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10472,20 +10465,20 @@
         <v>216</v>
       </c>
       <c r="B217" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C217" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D217" s="17" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E217" s="17"/>
       <c r="F217" s="17"/>
       <c r="G217" s="17"/>
       <c r="H217" s="17"/>
-      <c r="I217" s="16">
-        <v>0</v>
+      <c r="I217" s="16" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="218" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10493,20 +10486,20 @@
         <v>217</v>
       </c>
       <c r="B218" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C218" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D218" s="17" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E218" s="17"/>
       <c r="F218" s="17"/>
       <c r="G218" s="17"/>
       <c r="H218" s="17"/>
-      <c r="I218" s="19">
-        <v>1</v>
+      <c r="I218" s="19" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="219" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10514,20 +10507,20 @@
         <v>218</v>
       </c>
       <c r="B219" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C219" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D219" s="17" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E219" s="17"/>
       <c r="F219" s="17"/>
       <c r="G219" s="17"/>
       <c r="H219" s="17"/>
-      <c r="I219" s="16">
-        <v>0</v>
+      <c r="I219" s="16" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="220" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10535,20 +10528,20 @@
         <v>219</v>
       </c>
       <c r="B220" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C220" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D220" s="17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E220" s="17"/>
       <c r="F220" s="17"/>
       <c r="G220" s="17"/>
       <c r="H220" s="17"/>
-      <c r="I220" s="19">
-        <v>1</v>
+      <c r="I220" s="19" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="221" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10556,25 +10549,25 @@
         <v>220</v>
       </c>
       <c r="B221" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C221" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D221" s="16" t="s">
+        <v>801</v>
+      </c>
+      <c r="E221" s="17" t="s">
         <v>802</v>
       </c>
-      <c r="E221" s="17" t="s">
+      <c r="F221" s="17" t="s">
         <v>803</v>
       </c>
-      <c r="F221" s="17" t="s">
+      <c r="G221" s="17" t="s">
         <v>804</v>
       </c>
-      <c r="G221" s="17" t="s">
+      <c r="H221" s="17" t="s">
         <v>805</v>
-      </c>
-      <c r="H221" s="17" t="s">
-        <v>806</v>
       </c>
       <c r="I221" s="21" t="s">
         <v>13</v>
@@ -10585,25 +10578,25 @@
         <v>221</v>
       </c>
       <c r="B222" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C222" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D222" s="17" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E222" s="17" t="s">
+        <v>729</v>
+      </c>
+      <c r="F222" s="17" t="s">
         <v>730</v>
       </c>
-      <c r="F222" s="17" t="s">
+      <c r="G222" s="17" t="s">
         <v>731</v>
       </c>
-      <c r="G222" s="17" t="s">
+      <c r="H222" s="17" t="s">
         <v>732</v>
-      </c>
-      <c r="H222" s="17" t="s">
-        <v>733</v>
       </c>
       <c r="I222" s="21" t="s">
         <v>13</v>
@@ -10614,25 +10607,25 @@
         <v>222</v>
       </c>
       <c r="B223" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C223" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D223" s="22" t="s">
+        <v>806</v>
+      </c>
+      <c r="E223" s="17" t="s">
         <v>807</v>
-      </c>
-      <c r="E223" s="17" t="s">
-        <v>808</v>
       </c>
       <c r="F223" s="17" t="s">
         <v>43</v>
       </c>
       <c r="G223" s="17" t="s">
+        <v>808</v>
+      </c>
+      <c r="H223" s="17" t="s">
         <v>809</v>
-      </c>
-      <c r="H223" s="17" t="s">
-        <v>810</v>
       </c>
       <c r="I223" s="21" t="s">
         <v>123</v>
@@ -10643,25 +10636,25 @@
         <v>223</v>
       </c>
       <c r="B224" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C224" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D224" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="E224" s="17" t="s">
         <v>811</v>
       </c>
-      <c r="E224" s="17" t="s">
+      <c r="F224" s="17" t="s">
         <v>812</v>
       </c>
-      <c r="F224" s="17" t="s">
+      <c r="G224" s="17" t="s">
         <v>813</v>
       </c>
-      <c r="G224" s="17" t="s">
+      <c r="H224" s="17" t="s">
         <v>814</v>
-      </c>
-      <c r="H224" s="17" t="s">
-        <v>815</v>
       </c>
       <c r="I224" s="21" t="s">
         <v>124</v>
@@ -10672,25 +10665,25 @@
         <v>224</v>
       </c>
       <c r="B225" s="27" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C225" s="14" t="s">
         <v>76</v>
       </c>
       <c r="D225" s="16" t="s">
+        <v>815</v>
+      </c>
+      <c r="E225" s="20" t="s">
         <v>816</v>
       </c>
-      <c r="E225" s="20" t="s">
+      <c r="F225" s="20" t="s">
         <v>817</v>
       </c>
-      <c r="F225" s="20" t="s">
+      <c r="G225" s="20" t="s">
         <v>818</v>
       </c>
-      <c r="G225" s="20" t="s">
+      <c r="H225" s="20" t="s">
         <v>819</v>
-      </c>
-      <c r="H225" s="20" t="s">
-        <v>820</v>
       </c>
       <c r="I225" s="21" t="s">
         <v>123</v>
@@ -10701,25 +10694,25 @@
         <v>225</v>
       </c>
       <c r="B226" s="8" t="s">
+        <v>831</v>
+      </c>
+      <c r="C226" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="D226" s="5" t="s">
         <v>832</v>
       </c>
-      <c r="C226" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D226" s="5" t="s">
+      <c r="E226" s="5" t="s">
         <v>833</v>
       </c>
-      <c r="E226" s="5" t="s">
+      <c r="F226" s="5" t="s">
         <v>834</v>
       </c>
-      <c r="F226" s="5" t="s">
+      <c r="G226" s="5" t="s">
         <v>835</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="H226" s="5" t="s">
         <v>836</v>
-      </c>
-      <c r="H226" s="5" t="s">
-        <v>837</v>
       </c>
       <c r="I226" s="5" t="s">
         <v>124</v>
@@ -10730,25 +10723,25 @@
         <v>226</v>
       </c>
       <c r="B227" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C227" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D227" s="5" t="s">
+        <v>837</v>
+      </c>
+      <c r="E227" s="5" t="s">
         <v>838</v>
       </c>
-      <c r="E227" s="5" t="s">
+      <c r="F227" s="5" t="s">
         <v>839</v>
       </c>
-      <c r="F227" s="5" t="s">
+      <c r="G227" s="5" t="s">
         <v>840</v>
       </c>
-      <c r="G227" s="5" t="s">
+      <c r="H227" s="5" t="s">
         <v>841</v>
-      </c>
-      <c r="H227" s="5" t="s">
-        <v>842</v>
       </c>
       <c r="I227" s="5" t="s">
         <v>124</v>
@@ -10759,25 +10752,25 @@
         <v>227</v>
       </c>
       <c r="B228" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C228" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D228" s="5" t="s">
+        <v>842</v>
+      </c>
+      <c r="E228" s="5" t="s">
         <v>843</v>
       </c>
-      <c r="E228" s="5" t="s">
+      <c r="F228" s="5" t="s">
         <v>844</v>
       </c>
-      <c r="F228" s="5" t="s">
+      <c r="G228" s="5" t="s">
         <v>845</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="H228" s="5" t="s">
         <v>846</v>
-      </c>
-      <c r="H228" s="5" t="s">
-        <v>847</v>
       </c>
       <c r="I228" s="5" t="s">
         <v>7</v>
@@ -10788,25 +10781,25 @@
         <v>228</v>
       </c>
       <c r="B229" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C229" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D229" s="5" t="s">
+        <v>847</v>
+      </c>
+      <c r="E229" s="5" t="s">
         <v>848</v>
       </c>
-      <c r="E229" s="5" t="s">
+      <c r="F229" s="5" t="s">
         <v>849</v>
       </c>
-      <c r="F229" s="5" t="s">
+      <c r="G229" s="5" t="s">
         <v>850</v>
       </c>
-      <c r="G229" s="5" t="s">
+      <c r="H229" s="5" t="s">
         <v>851</v>
-      </c>
-      <c r="H229" s="5" t="s">
-        <v>852</v>
       </c>
       <c r="I229" s="5" t="s">
         <v>13</v>
@@ -10817,25 +10810,25 @@
         <v>229</v>
       </c>
       <c r="B230" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C230" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D230" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="E230" s="5" t="s">
         <v>853</v>
       </c>
-      <c r="E230" s="5" t="s">
+      <c r="F230" s="5" t="s">
         <v>854</v>
       </c>
-      <c r="F230" s="5" t="s">
+      <c r="G230" s="5" t="s">
         <v>855</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="H230" s="5" t="s">
         <v>856</v>
-      </c>
-      <c r="H230" s="5" t="s">
-        <v>857</v>
       </c>
       <c r="I230" s="5" t="s">
         <v>7</v>
@@ -10846,25 +10839,25 @@
         <v>230</v>
       </c>
       <c r="B231" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C231" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D231" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="E231" s="5" t="s">
         <v>858</v>
       </c>
-      <c r="E231" s="5" t="s">
+      <c r="F231" s="5" t="s">
         <v>859</v>
       </c>
-      <c r="F231" s="5" t="s">
+      <c r="G231" s="5" t="s">
         <v>860</v>
       </c>
-      <c r="G231" s="5" t="s">
+      <c r="H231" s="5" t="s">
         <v>861</v>
-      </c>
-      <c r="H231" s="5" t="s">
-        <v>862</v>
       </c>
       <c r="I231" s="5" t="s">
         <v>124</v>
@@ -10875,25 +10868,25 @@
         <v>231</v>
       </c>
       <c r="B232" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C232" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D232" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="E232" s="5" t="s">
         <v>863</v>
       </c>
-      <c r="E232" s="5" t="s">
+      <c r="F232" s="5" t="s">
         <v>864</v>
       </c>
-      <c r="F232" s="5" t="s">
+      <c r="G232" s="5" t="s">
         <v>865</v>
       </c>
-      <c r="G232" s="5" t="s">
-        <v>866</v>
-      </c>
       <c r="H232" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I232" s="5" t="s">
         <v>124</v>
@@ -10904,20 +10897,20 @@
         <v>232</v>
       </c>
       <c r="B233" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C233" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D233" s="5" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E233" s="5"/>
       <c r="F233" s="5"/>
       <c r="G233" s="5"/>
       <c r="H233" s="5"/>
-      <c r="I233" s="5">
-        <v>0</v>
+      <c r="I233" s="5" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="234" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10925,25 +10918,25 @@
         <v>233</v>
       </c>
       <c r="B234" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C234" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D234" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="E234" s="5" t="s">
         <v>868</v>
       </c>
-      <c r="E234" s="5" t="s">
+      <c r="F234" s="5" t="s">
         <v>869</v>
       </c>
-      <c r="F234" s="5" t="s">
+      <c r="G234" s="5" t="s">
         <v>870</v>
       </c>
-      <c r="G234" s="5" t="s">
-        <v>871</v>
-      </c>
       <c r="H234" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I234" s="5" t="s">
         <v>124</v>
@@ -10954,13 +10947,13 @@
         <v>234</v>
       </c>
       <c r="B235" s="8" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C235" s="5" t="s">
         <v>1</v>
       </c>
       <c r="D235" s="5" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E235" s="5">
         <v>1</v>
@@ -10975,7 +10968,7 @@
         <v>6</v>
       </c>
       <c r="I235" s="5" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="236" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -10983,49 +10976,49 @@
         <v>235</v>
       </c>
       <c r="B236" s="32" t="s">
+        <v>872</v>
+      </c>
+      <c r="C236" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="D236" s="31" t="s">
+        <v>873</v>
+      </c>
+      <c r="E236" s="31" t="s">
         <v>874</v>
       </c>
-      <c r="C236" s="31" t="s">
-        <v>1</v>
-      </c>
-      <c r="D236" s="31" t="s">
+      <c r="F236" s="31" t="s">
         <v>875</v>
       </c>
-      <c r="E236" s="31" t="s">
+      <c r="G236" s="31" t="s">
         <v>876</v>
       </c>
-      <c r="F236" s="31" t="s">
+      <c r="H236" s="31" t="s">
         <v>877</v>
-      </c>
-      <c r="G236" s="31" t="s">
-        <v>878</v>
-      </c>
-      <c r="H236" s="31" t="s">
-        <v>879</v>
       </c>
       <c r="I236" s="31" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="237" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="5">
+      <c r="A237" s="31">
         <v>236</v>
       </c>
-      <c r="B237" s="8" t="s">
-        <v>874</v>
-      </c>
-      <c r="C237" s="5" t="s">
+      <c r="B237" s="32" t="s">
+        <v>872</v>
+      </c>
+      <c r="C237" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="D237" s="5" t="s">
-        <v>867</v>
-      </c>
-      <c r="E237" s="5"/>
-      <c r="F237" s="5"/>
-      <c r="G237" s="5"/>
-      <c r="H237" s="5"/>
-      <c r="I237" s="5">
-        <v>0</v>
+      <c r="D237" s="31" t="s">
+        <v>866</v>
+      </c>
+      <c r="E237" s="31"/>
+      <c r="F237" s="31"/>
+      <c r="G237" s="31"/>
+      <c r="H237" s="31"/>
+      <c r="I237" s="31" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="238" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11033,25 +11026,25 @@
         <v>237</v>
       </c>
       <c r="B238" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C238" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D238" s="31" t="s">
+        <v>878</v>
+      </c>
+      <c r="E238" s="31" t="s">
+        <v>879</v>
+      </c>
+      <c r="F238" s="31" t="s">
         <v>880</v>
       </c>
-      <c r="E238" s="31" t="s">
+      <c r="G238" s="31" t="s">
         <v>881</v>
       </c>
-      <c r="F238" s="31" t="s">
+      <c r="H238" s="31" t="s">
         <v>882</v>
-      </c>
-      <c r="G238" s="31" t="s">
-        <v>883</v>
-      </c>
-      <c r="H238" s="31" t="s">
-        <v>884</v>
       </c>
       <c r="I238" s="31" t="s">
         <v>7</v>
@@ -11062,13 +11055,13 @@
         <v>238</v>
       </c>
       <c r="B239" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C239" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D239" s="31" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E239" s="31">
         <v>1</v>
@@ -11083,7 +11076,7 @@
         <v>6</v>
       </c>
       <c r="I239" s="31" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="240" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11091,28 +11084,28 @@
         <v>239</v>
       </c>
       <c r="B240" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C240" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D240" s="31" t="s">
+        <v>883</v>
+      </c>
+      <c r="E240" s="31" t="s">
+        <v>884</v>
+      </c>
+      <c r="F240" s="31" t="s">
         <v>885</v>
       </c>
-      <c r="E240" s="31" t="s">
+      <c r="G240" s="31" t="s">
         <v>886</v>
       </c>
-      <c r="F240" s="31" t="s">
+      <c r="H240" s="31" t="s">
         <v>887</v>
       </c>
-      <c r="G240" s="31" t="s">
-        <v>888</v>
-      </c>
-      <c r="H240" s="31" t="s">
-        <v>889</v>
-      </c>
       <c r="I240" s="31" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="241" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11120,28 +11113,28 @@
         <v>240</v>
       </c>
       <c r="B241" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C241" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D241" s="31" t="s">
+        <v>888</v>
+      </c>
+      <c r="E241" s="31" t="s">
+        <v>889</v>
+      </c>
+      <c r="F241" s="31" t="s">
+        <v>890</v>
+      </c>
+      <c r="G241" s="31" t="s">
         <v>891</v>
       </c>
-      <c r="E241" s="31" t="s">
+      <c r="H241" s="31" t="s">
         <v>892</v>
       </c>
-      <c r="F241" s="31" t="s">
-        <v>893</v>
-      </c>
-      <c r="G241" s="31" t="s">
-        <v>894</v>
-      </c>
-      <c r="H241" s="31" t="s">
-        <v>895</v>
-      </c>
       <c r="I241" s="31" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="242" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11149,28 +11142,28 @@
         <v>241</v>
       </c>
       <c r="B242" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C242" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D242" s="31" t="s">
+        <v>893</v>
+      </c>
+      <c r="E242" s="31" t="s">
+        <v>894</v>
+      </c>
+      <c r="F242" s="31" t="s">
+        <v>895</v>
+      </c>
+      <c r="G242" s="31" t="s">
         <v>896</v>
       </c>
-      <c r="E242" s="31" t="s">
+      <c r="H242" s="31" t="s">
         <v>897</v>
       </c>
-      <c r="F242" s="31" t="s">
-        <v>898</v>
-      </c>
-      <c r="G242" s="31" t="s">
-        <v>899</v>
-      </c>
-      <c r="H242" s="31" t="s">
-        <v>900</v>
-      </c>
       <c r="I242" s="31" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="243" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11178,28 +11171,28 @@
         <v>242</v>
       </c>
       <c r="B243" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C243" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D243" s="31" t="s">
+        <v>898</v>
+      </c>
+      <c r="E243" s="31" t="s">
+        <v>899</v>
+      </c>
+      <c r="F243" s="31" t="s">
+        <v>900</v>
+      </c>
+      <c r="G243" s="31" t="s">
         <v>901</v>
       </c>
-      <c r="E243" s="31" t="s">
+      <c r="H243" s="31" t="s">
         <v>902</v>
       </c>
-      <c r="F243" s="31" t="s">
-        <v>903</v>
-      </c>
-      <c r="G243" s="31" t="s">
-        <v>904</v>
-      </c>
-      <c r="H243" s="31" t="s">
-        <v>905</v>
-      </c>
       <c r="I243" s="31" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="244" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11207,28 +11200,28 @@
         <v>243</v>
       </c>
       <c r="B244" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C244" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D244" s="31" t="s">
+        <v>903</v>
+      </c>
+      <c r="E244" s="31" t="s">
+        <v>904</v>
+      </c>
+      <c r="F244" s="31" t="s">
+        <v>905</v>
+      </c>
+      <c r="G244" s="31" t="s">
         <v>906</v>
       </c>
-      <c r="E244" s="31" t="s">
+      <c r="H244" s="31" t="s">
         <v>907</v>
       </c>
-      <c r="F244" s="31" t="s">
-        <v>908</v>
-      </c>
-      <c r="G244" s="31" t="s">
-        <v>909</v>
-      </c>
-      <c r="H244" s="31" t="s">
-        <v>910</v>
-      </c>
       <c r="I244" s="31" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="245" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11236,28 +11229,28 @@
         <v>244</v>
       </c>
       <c r="B245" s="32" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C245" s="31" t="s">
         <v>1</v>
       </c>
       <c r="D245" s="31" t="s">
+        <v>908</v>
+      </c>
+      <c r="E245" s="31" t="s">
+        <v>909</v>
+      </c>
+      <c r="F245" s="31" t="s">
+        <v>910</v>
+      </c>
+      <c r="G245" s="31" t="s">
         <v>911</v>
       </c>
-      <c r="E245" s="31" t="s">
+      <c r="H245" s="31" t="s">
         <v>912</v>
       </c>
-      <c r="F245" s="31" t="s">
-        <v>913</v>
-      </c>
-      <c r="G245" s="31" t="s">
-        <v>914</v>
-      </c>
-      <c r="H245" s="31" t="s">
-        <v>915</v>
-      </c>
       <c r="I245" s="31" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="246" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11265,25 +11258,25 @@
         <v>245</v>
       </c>
       <c r="B246" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C246" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D246" s="14" t="s">
+        <v>873</v>
+      </c>
+      <c r="E246" s="14" t="s">
+        <v>874</v>
+      </c>
+      <c r="F246" s="14" t="s">
         <v>875</v>
       </c>
-      <c r="E246" s="14" t="s">
+      <c r="G246" s="14" t="s">
         <v>876</v>
       </c>
-      <c r="F246" s="14" t="s">
+      <c r="H246" s="14" t="s">
         <v>877</v>
-      </c>
-      <c r="G246" s="14" t="s">
-        <v>878</v>
-      </c>
-      <c r="H246" s="14" t="s">
-        <v>879</v>
       </c>
       <c r="I246" s="14" t="s">
         <v>123</v>
@@ -11294,20 +11287,20 @@
         <v>246</v>
       </c>
       <c r="B247" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C247" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E247" s="14"/>
       <c r="F247" s="14"/>
       <c r="G247" s="14"/>
       <c r="H247" s="14"/>
-      <c r="I247" s="14">
-        <v>0</v>
+      <c r="I247" s="14" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="248" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11315,20 +11308,20 @@
         <v>247</v>
       </c>
       <c r="B248" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C248" s="14" t="s">
         <v>65</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>917</v>
+        <v>914</v>
       </c>
       <c r="E248" s="14"/>
       <c r="F248" s="14"/>
       <c r="G248" s="14"/>
       <c r="H248" s="14"/>
-      <c r="I248" s="14">
-        <v>1</v>
+      <c r="I248" s="14" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="249" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11336,13 +11329,13 @@
         <v>248</v>
       </c>
       <c r="B249" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C249" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D249" s="14" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E249" s="14">
         <v>1</v>
@@ -11357,7 +11350,7 @@
         <v>6</v>
       </c>
       <c r="I249" s="14" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="250" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11365,25 +11358,25 @@
         <v>249</v>
       </c>
       <c r="B250" s="15" t="s">
+        <v>913</v>
+      </c>
+      <c r="C250" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D250" s="14" t="s">
+        <v>915</v>
+      </c>
+      <c r="E250" s="14" t="s">
         <v>916</v>
       </c>
-      <c r="C250" s="14" t="s">
-        <v>1</v>
-      </c>
-      <c r="D250" s="14" t="s">
+      <c r="F250" s="14" t="s">
+        <v>917</v>
+      </c>
+      <c r="G250" s="14" t="s">
         <v>918</v>
       </c>
-      <c r="E250" s="14" t="s">
+      <c r="H250" s="14" t="s">
         <v>919</v>
-      </c>
-      <c r="F250" s="14" t="s">
-        <v>920</v>
-      </c>
-      <c r="G250" s="14" t="s">
-        <v>921</v>
-      </c>
-      <c r="H250" s="14" t="s">
-        <v>922</v>
       </c>
       <c r="I250" s="14" t="s">
         <v>13</v>
@@ -11394,25 +11387,25 @@
         <v>250</v>
       </c>
       <c r="B251" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C251" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D251" s="14" t="s">
+        <v>920</v>
+      </c>
+      <c r="E251" s="14" t="s">
+        <v>921</v>
+      </c>
+      <c r="F251" s="14" t="s">
+        <v>922</v>
+      </c>
+      <c r="G251" s="14" t="s">
         <v>923</v>
       </c>
-      <c r="E251" s="14" t="s">
+      <c r="H251" s="14" t="s">
         <v>924</v>
-      </c>
-      <c r="F251" s="14" t="s">
-        <v>925</v>
-      </c>
-      <c r="G251" s="14" t="s">
-        <v>926</v>
-      </c>
-      <c r="H251" s="14" t="s">
-        <v>927</v>
       </c>
       <c r="I251" s="14" t="s">
         <v>7</v>
@@ -11423,25 +11416,25 @@
         <v>251</v>
       </c>
       <c r="B252" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C252" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D252" s="14" t="s">
+        <v>925</v>
+      </c>
+      <c r="E252" s="14" t="s">
+        <v>926</v>
+      </c>
+      <c r="F252" s="14" t="s">
+        <v>927</v>
+      </c>
+      <c r="G252" s="14" t="s">
         <v>928</v>
       </c>
-      <c r="E252" s="14" t="s">
+      <c r="H252" s="14" t="s">
         <v>929</v>
-      </c>
-      <c r="F252" s="14" t="s">
-        <v>930</v>
-      </c>
-      <c r="G252" s="14" t="s">
-        <v>931</v>
-      </c>
-      <c r="H252" s="14" t="s">
-        <v>932</v>
       </c>
       <c r="I252" s="14" t="s">
         <v>7</v>
@@ -11452,25 +11445,25 @@
         <v>252</v>
       </c>
       <c r="B253" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C253" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D253" s="14" t="s">
+        <v>930</v>
+      </c>
+      <c r="E253" s="14" t="s">
+        <v>931</v>
+      </c>
+      <c r="F253" s="14" t="s">
+        <v>932</v>
+      </c>
+      <c r="G253" s="14" t="s">
         <v>933</v>
       </c>
-      <c r="E253" s="14" t="s">
-        <v>934</v>
-      </c>
-      <c r="F253" s="14" t="s">
-        <v>935</v>
-      </c>
-      <c r="G253" s="14" t="s">
-        <v>936</v>
-      </c>
       <c r="H253" s="14" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="I253" s="14" t="s">
         <v>7</v>
@@ -11481,22 +11474,22 @@
         <v>253</v>
       </c>
       <c r="B254" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C254" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D254" s="14" t="s">
+        <v>934</v>
+      </c>
+      <c r="E254" s="14" t="s">
+        <v>935</v>
+      </c>
+      <c r="F254" s="14" t="s">
+        <v>936</v>
+      </c>
+      <c r="G254" s="14" t="s">
         <v>937</v>
-      </c>
-      <c r="E254" s="14" t="s">
-        <v>938</v>
-      </c>
-      <c r="F254" s="14" t="s">
-        <v>939</v>
-      </c>
-      <c r="G254" s="14" t="s">
-        <v>940</v>
       </c>
       <c r="H254" s="14" t="s">
         <v>4</v>
@@ -11510,16 +11503,16 @@
         <v>254</v>
       </c>
       <c r="B255" s="15" t="s">
-        <v>916</v>
+        <v>913</v>
       </c>
       <c r="C255" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D255" s="14" t="s">
-        <v>941</v>
+        <v>938</v>
       </c>
       <c r="E255" s="14" t="s">
-        <v>942</v>
+        <v>939</v>
       </c>
       <c r="F255" s="14" t="s">
         <v>5</v>
@@ -11528,7 +11521,7 @@
         <v>4</v>
       </c>
       <c r="H255" s="14" t="s">
-        <v>943</v>
+        <v>940</v>
       </c>
       <c r="I255" s="14" t="s">
         <v>7</v>
@@ -11539,21 +11532,20 @@
         <v>255</v>
       </c>
       <c r="B256" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C256" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D256" s="5" t="s">
-        <v>945</v>
+        <v>942</v>
       </c>
       <c r="E256" s="5"/>
       <c r="F256" s="5"/>
       <c r="G256" s="5"/>
       <c r="H256" s="5"/>
-      <c r="I256" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I256" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="257" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11561,21 +11553,20 @@
         <v>256</v>
       </c>
       <c r="B257" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C257" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D257" s="5" t="s">
-        <v>946</v>
+        <v>943</v>
       </c>
       <c r="E257" s="5"/>
       <c r="F257" s="5"/>
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
-      <c r="I257" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I257" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="258" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11583,21 +11574,20 @@
         <v>257</v>
       </c>
       <c r="B258" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C258" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D258" s="5" t="s">
-        <v>947</v>
+        <v>944</v>
       </c>
       <c r="E258" s="5"/>
       <c r="F258" s="5"/>
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
-      <c r="I258" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I258" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="259" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11605,21 +11595,20 @@
         <v>258</v>
       </c>
       <c r="B259" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C259" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D259" s="5" t="s">
-        <v>948</v>
+        <v>945</v>
       </c>
       <c r="E259" s="5"/>
       <c r="F259" s="5"/>
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
-      <c r="I259" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I259" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="260" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11627,21 +11616,20 @@
         <v>259</v>
       </c>
       <c r="B260" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C260" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D260" s="5" t="s">
-        <v>949</v>
+        <v>946</v>
       </c>
       <c r="E260" s="5"/>
       <c r="F260" s="5"/>
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
-      <c r="I260" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I260" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="261" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11649,21 +11637,20 @@
         <v>260</v>
       </c>
       <c r="B261" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C261" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D261" s="5" t="s">
-        <v>950</v>
+        <v>947</v>
       </c>
       <c r="E261" s="5"/>
       <c r="F261" s="5"/>
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
-      <c r="I261" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I261" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="262" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11671,21 +11658,20 @@
         <v>261</v>
       </c>
       <c r="B262" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C262" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D262" s="5" t="s">
-        <v>951</v>
+        <v>948</v>
       </c>
       <c r="E262" s="5"/>
       <c r="F262" s="5"/>
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
-      <c r="I262" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I262" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="263" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11693,21 +11679,20 @@
         <v>262</v>
       </c>
       <c r="B263" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C263" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D263" s="5" t="s">
-        <v>952</v>
+        <v>949</v>
       </c>
       <c r="E263" s="5"/>
       <c r="F263" s="5"/>
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
-      <c r="I263" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I263" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="264" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11715,21 +11700,20 @@
         <v>263</v>
       </c>
       <c r="B264" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C264" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D264" s="5" t="s">
-        <v>953</v>
+        <v>950</v>
       </c>
       <c r="E264" s="5"/>
       <c r="F264" s="5"/>
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
-      <c r="I264" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I264" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="265" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11737,21 +11721,20 @@
         <v>264</v>
       </c>
       <c r="B265" s="8" t="s">
-        <v>944</v>
+        <v>941</v>
       </c>
       <c r="C265" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D265" s="5" t="s">
-        <v>954</v>
+        <v>951</v>
       </c>
       <c r="E265" s="5"/>
       <c r="F265" s="5"/>
       <c r="G265" s="5"/>
       <c r="H265" s="5"/>
-      <c r="I265" s="5">
-        <f>IF(Table1[[#This Row],[Opt_A]]="خطأ",0,1)</f>
-        <v>1</v>
+      <c r="I265" s="5" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="266" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11759,28 +11742,28 @@
         <v>265</v>
       </c>
       <c r="B266" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C266" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D266" s="27" t="s">
+        <v>952</v>
+      </c>
+      <c r="E266" s="29" t="s">
+        <v>953</v>
+      </c>
+      <c r="F266" s="29" t="s">
+        <v>954</v>
+      </c>
+      <c r="G266" s="29" t="s">
         <v>955</v>
       </c>
-      <c r="E266" s="29" t="s">
-        <v>956</v>
-      </c>
-      <c r="F266" s="29" t="s">
-        <v>957</v>
-      </c>
-      <c r="G266" s="29" t="s">
-        <v>958</v>
-      </c>
       <c r="H266" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I266" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="267" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11788,28 +11771,28 @@
         <v>266</v>
       </c>
       <c r="B267" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C267" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D267" s="27" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="E267" s="29" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="F267" s="29" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="G267" s="29" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="H267" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I267" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="268" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11817,28 +11800,28 @@
         <v>267</v>
       </c>
       <c r="B268" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C268" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D268" s="27" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="E268" s="29" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="F268" s="29" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="G268" s="29" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="H268" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I268" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="269" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11846,28 +11829,28 @@
         <v>268</v>
       </c>
       <c r="B269" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C269" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D269" s="27" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="E269" s="29" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="F269" s="29" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="G269" s="29" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="H269" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I269" s="29" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="270" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11875,28 +11858,28 @@
         <v>269</v>
       </c>
       <c r="B270" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C270" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D270" s="27" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="E270" s="29" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="F270" s="29" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="G270" s="29" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="H270" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I270" s="29" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="271" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11904,28 +11887,28 @@
         <v>270</v>
       </c>
       <c r="B271" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C271" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D271" s="27" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="E271" s="29" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="F271" s="29" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="G271" s="29" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="H271" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I271" s="29" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="272" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11933,28 +11916,28 @@
         <v>271</v>
       </c>
       <c r="B272" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C272" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D272" s="27" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="E272" s="29" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="F272" s="29" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="G272" s="29" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="H272" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I272" s="29" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="273" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11962,28 +11945,28 @@
         <v>272</v>
       </c>
       <c r="B273" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C273" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D273" s="27" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="E273" s="29" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="F273" s="29" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="G273" s="29" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="H273" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I273" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="274" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -11991,28 +11974,28 @@
         <v>273</v>
       </c>
       <c r="B274" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C274" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D274" s="27" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="E274" s="29" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="F274" s="29" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="G274" s="29" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="H274" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I274" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="275" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12020,28 +12003,28 @@
         <v>274</v>
       </c>
       <c r="B275" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C275" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D275" s="27" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="E275" s="29" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="F275" s="29" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G275" s="29" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="H275" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I275" s="29" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="276" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12049,28 +12032,28 @@
         <v>275</v>
       </c>
       <c r="B276" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C276" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D276" s="27" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="E276" s="29" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="F276" s="29" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="G276" s="29" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="H276" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I276" s="29" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="277" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12078,28 +12061,28 @@
         <v>276</v>
       </c>
       <c r="B277" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C277" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D277" s="27" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="E277" s="29" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="F277" s="29" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="G277" s="29" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="H277" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I277" s="29" t="s">
-        <v>959</v>
+        <v>7</v>
       </c>
     </row>
     <row r="278" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12107,28 +12090,28 @@
         <v>277</v>
       </c>
       <c r="B278" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C278" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D278" s="27" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="E278" s="29" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="F278" s="29" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="G278" s="29" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="H278" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I278" s="29" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="279" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12136,28 +12119,28 @@
         <v>278</v>
       </c>
       <c r="B279" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C279" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D279" s="27" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="E279" s="29" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F279" s="29" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="G279" s="29" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="H279" s="14" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="I279" s="29" t="s">
-        <v>890</v>
+        <v>13</v>
       </c>
     </row>
     <row r="280" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12165,28 +12148,28 @@
         <v>279</v>
       </c>
       <c r="B280" s="28" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C280" s="14" t="s">
         <v>1</v>
       </c>
       <c r="D280" s="27" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="E280" s="29" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="F280" s="29" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G280" s="29" t="s">
+        <v>1009</v>
+      </c>
+      <c r="H280" s="14" t="s">
         <v>1012</v>
       </c>
-      <c r="G280" s="29" t="s">
-        <v>1013</v>
-      </c>
-      <c r="H280" s="14" t="s">
-        <v>1016</v>
-      </c>
       <c r="I280" s="29" t="s">
-        <v>873</v>
+        <v>123</v>
       </c>
     </row>
     <row r="281" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12194,25 +12177,25 @@
         <v>280</v>
       </c>
       <c r="B281" s="8" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C281" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D281" s="13" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E281" s="13" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F281" s="13" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G281" s="13" t="s">
         <v>1018</v>
       </c>
-      <c r="C281" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D281" s="13" t="s">
+      <c r="H281" s="13" t="s">
         <v>1019</v>
-      </c>
-      <c r="E281" s="13" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F281" s="13" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G281" s="13" t="s">
-        <v>1022</v>
-      </c>
-      <c r="H281" s="13" t="s">
-        <v>1023</v>
       </c>
       <c r="I281" s="1" t="s">
         <v>123</v>
@@ -12223,25 +12206,25 @@
         <v>281</v>
       </c>
       <c r="B282" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C282" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D282" s="13" t="s">
+        <v>1020</v>
+      </c>
+      <c r="E282" s="13" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F282" s="13" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G282" s="13" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H282" s="13" t="s">
         <v>1024</v>
-      </c>
-      <c r="E282" s="13" t="s">
-        <v>1025</v>
-      </c>
-      <c r="F282" s="13" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G282" s="13" t="s">
-        <v>1027</v>
-      </c>
-      <c r="H282" s="13" t="s">
-        <v>1028</v>
       </c>
       <c r="I282" s="1" t="s">
         <v>13</v>
@@ -12252,25 +12235,25 @@
         <v>282</v>
       </c>
       <c r="B283" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C283" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D283" s="13" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E283" s="13" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F283" s="13" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G283" s="13" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H283" s="13" t="s">
         <v>1029</v>
-      </c>
-      <c r="E283" s="13" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F283" s="13" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G283" s="13" t="s">
-        <v>1032</v>
-      </c>
-      <c r="H283" s="13" t="s">
-        <v>1033</v>
       </c>
       <c r="I283" s="1" t="s">
         <v>7</v>
@@ -12281,25 +12264,25 @@
         <v>283</v>
       </c>
       <c r="B284" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C284" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D284" s="13" t="s">
+        <v>1030</v>
+      </c>
+      <c r="E284" s="13" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F284" s="13" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G284" s="13" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H284" s="13" t="s">
         <v>1034</v>
-      </c>
-      <c r="E284" s="13" t="s">
-        <v>1035</v>
-      </c>
-      <c r="F284" s="13" t="s">
-        <v>1036</v>
-      </c>
-      <c r="G284" s="13" t="s">
-        <v>1037</v>
-      </c>
-      <c r="H284" s="13" t="s">
-        <v>1038</v>
       </c>
       <c r="I284" s="1" t="s">
         <v>7</v>
@@ -12310,13 +12293,13 @@
         <v>284</v>
       </c>
       <c r="B285" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C285" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D285" s="13" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="E285" s="13">
         <v>2</v>
@@ -12339,22 +12322,22 @@
         <v>285</v>
       </c>
       <c r="B286" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C286" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D286" s="13" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="E286" s="13" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="F286" s="13" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="G286" s="13" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="H286" s="13"/>
       <c r="I286" s="1" t="s">
@@ -12366,25 +12349,25 @@
         <v>286</v>
       </c>
       <c r="B287" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C287" s="9" t="s">
         <v>76</v>
       </c>
       <c r="D287" s="13" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E287" s="13" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F287" s="13" t="s">
+        <v>1042</v>
+      </c>
+      <c r="G287" s="13" t="s">
+        <v>1043</v>
+      </c>
+      <c r="H287" s="13" t="s">
         <v>1044</v>
-      </c>
-      <c r="E287" s="13" t="s">
-        <v>1045</v>
-      </c>
-      <c r="F287" s="13" t="s">
-        <v>1046</v>
-      </c>
-      <c r="G287" s="13" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H287" s="13" t="s">
-        <v>1048</v>
       </c>
       <c r="I287" s="1" t="s">
         <v>123</v>
@@ -12395,20 +12378,20 @@
         <v>287</v>
       </c>
       <c r="B288" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C288" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D288" s="13" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E288" s="13"/>
       <c r="F288" s="13"/>
       <c r="G288" s="13"/>
       <c r="H288" s="13"/>
-      <c r="I288" s="1">
-        <v>0</v>
+      <c r="I288" s="1" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="289" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12416,20 +12399,20 @@
         <v>288</v>
       </c>
       <c r="B289" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C289" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D289" s="13" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="E289" s="13"/>
       <c r="F289" s="13"/>
       <c r="G289" s="13"/>
       <c r="H289" s="13"/>
-      <c r="I289" s="1">
-        <v>0</v>
+      <c r="I289" s="1" t="s">
+        <v>1162</v>
       </c>
     </row>
     <row r="290" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12437,20 +12420,20 @@
         <v>289</v>
       </c>
       <c r="B290" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C290" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D290" s="13" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="E290" s="13"/>
       <c r="F290" s="13"/>
       <c r="G290" s="13"/>
       <c r="H290" s="13"/>
-      <c r="I290" s="1">
-        <v>1</v>
+      <c r="I290" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="291" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12458,20 +12441,20 @@
         <v>290</v>
       </c>
       <c r="B291" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C291" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D291" s="13" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E291" s="13"/>
       <c r="F291" s="13"/>
       <c r="G291" s="13"/>
       <c r="H291" s="13"/>
-      <c r="I291" s="1">
-        <v>1</v>
+      <c r="I291" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="292" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12479,20 +12462,20 @@
         <v>291</v>
       </c>
       <c r="B292" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C292" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D292" s="13" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="E292" s="13"/>
       <c r="F292" s="13"/>
       <c r="G292" s="13"/>
       <c r="H292" s="13"/>
-      <c r="I292" s="1">
-        <v>1</v>
+      <c r="I292" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="293" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12500,25 +12483,25 @@
         <v>292</v>
       </c>
       <c r="B293" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C293" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D293" s="30" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="E293" s="30" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="F293" s="30" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="G293" s="30" t="s">
-        <v>1058</v>
+        <v>1054</v>
       </c>
       <c r="H293" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I293" s="24" t="s">
         <v>7</v>
@@ -12529,20 +12512,20 @@
         <v>293</v>
       </c>
       <c r="B294" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C294" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D294" s="30" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="E294" s="30"/>
       <c r="F294" s="30"/>
       <c r="G294" s="30"/>
       <c r="H294" s="30"/>
-      <c r="I294" s="24">
-        <v>1</v>
+      <c r="I294" s="24" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="295" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12550,25 +12533,25 @@
         <v>294</v>
       </c>
       <c r="B295" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C295" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D295" s="30" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="E295" s="30" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="F295" s="30" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="G295" s="30" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="H295" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I295" s="24" t="s">
         <v>123</v>
@@ -12579,25 +12562,25 @@
         <v>295</v>
       </c>
       <c r="B296" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C296" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D296" s="30" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="E296" s="30" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="F296" s="30" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G296" s="30" t="s">
         <v>1062</v>
       </c>
-      <c r="G296" s="30" t="s">
-        <v>1066</v>
-      </c>
       <c r="H296" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I296" s="24" t="s">
         <v>13</v>
@@ -12608,20 +12591,20 @@
         <v>296</v>
       </c>
       <c r="B297" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C297" s="29" t="s">
         <v>65</v>
       </c>
       <c r="D297" s="30" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="E297" s="30"/>
       <c r="F297" s="30"/>
       <c r="G297" s="30"/>
       <c r="H297" s="30"/>
-      <c r="I297" s="24">
-        <v>1</v>
+      <c r="I297" s="24" t="s">
+        <v>1161</v>
       </c>
     </row>
     <row r="298" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -12629,25 +12612,25 @@
         <v>297</v>
       </c>
       <c r="B298" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C298" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D298" s="30" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="E298" s="30" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="F298" s="30" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="G298" s="30" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="H298" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I298" s="24" t="s">
         <v>13</v>
@@ -12658,25 +12641,25 @@
         <v>298</v>
       </c>
       <c r="B299" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C299" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D299" s="29" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E299" s="30" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F299" s="30" t="s">
+        <v>1070</v>
+      </c>
+      <c r="G299" s="30" t="s">
+        <v>1071</v>
+      </c>
+      <c r="H299" s="30" t="s">
         <v>1072</v>
-      </c>
-      <c r="E299" s="30" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F299" s="30" t="s">
-        <v>1074</v>
-      </c>
-      <c r="G299" s="30" t="s">
-        <v>1075</v>
-      </c>
-      <c r="H299" s="30" t="s">
-        <v>1076</v>
       </c>
       <c r="I299" s="30" t="s">
         <v>124</v>
@@ -12687,25 +12670,25 @@
         <v>299</v>
       </c>
       <c r="B300" s="15" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C300" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D300" s="30" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="E300" s="30" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="F300" s="30" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="G300" s="30" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="H300" s="30" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="I300" s="24" t="s">
         <v>13</v>
@@ -12716,25 +12699,25 @@
         <v>300</v>
       </c>
       <c r="B301" s="8" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C301" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D301" s="13" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E301" s="13" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F301" s="13" t="s">
+        <v>1080</v>
+      </c>
+      <c r="G301" s="13" t="s">
         <v>1081</v>
       </c>
-      <c r="C301" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D301" s="13" t="s">
+      <c r="H301" s="13" t="s">
         <v>1082</v>
-      </c>
-      <c r="E301" s="13" t="s">
-        <v>1083</v>
-      </c>
-      <c r="F301" s="13" t="s">
-        <v>1084</v>
-      </c>
-      <c r="G301" s="13" t="s">
-        <v>1085</v>
-      </c>
-      <c r="H301" s="13" t="s">
-        <v>1086</v>
       </c>
       <c r="I301" s="5" t="s">
         <v>13</v>
@@ -12745,13 +12728,13 @@
         <v>301</v>
       </c>
       <c r="B302" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C302" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D302" s="13" t="s">
-        <v>1087</v>
+        <v>1083</v>
       </c>
       <c r="E302" s="13">
         <v>155</v>
@@ -12774,25 +12757,25 @@
         <v>302</v>
       </c>
       <c r="B303" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C303" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D303" s="13" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E303" s="13" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F303" s="13" t="s">
+        <v>1086</v>
+      </c>
+      <c r="G303" s="13" t="s">
+        <v>1087</v>
+      </c>
+      <c r="H303" s="13" t="s">
         <v>1088</v>
-      </c>
-      <c r="E303" s="13" t="s">
-        <v>1089</v>
-      </c>
-      <c r="F303" s="13" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G303" s="13" t="s">
-        <v>1091</v>
-      </c>
-      <c r="H303" s="13" t="s">
-        <v>1092</v>
       </c>
       <c r="I303" s="5" t="s">
         <v>13</v>
@@ -12803,25 +12786,25 @@
         <v>303</v>
       </c>
       <c r="B304" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C304" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D304" s="13" t="s">
-        <v>1159</v>
+        <v>1155</v>
       </c>
       <c r="E304" s="13" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="F304" s="13" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G304" s="13" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="H304" s="13" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I304" s="5" t="s">
         <v>7</v>
@@ -12832,13 +12815,13 @@
         <v>304</v>
       </c>
       <c r="B305" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C305" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D305" s="13" t="s">
-        <v>1160</v>
+        <v>1156</v>
       </c>
       <c r="E305" s="13">
         <v>20</v>
@@ -12861,25 +12844,25 @@
         <v>305</v>
       </c>
       <c r="B306" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C306" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D306" s="13" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E306" s="13" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F306" s="13" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G306" s="13" t="s">
+        <v>1096</v>
+      </c>
+      <c r="H306" s="13" t="s">
         <v>1097</v>
-      </c>
-      <c r="E306" s="13" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F306" s="13" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G306" s="13" t="s">
-        <v>1100</v>
-      </c>
-      <c r="H306" s="13" t="s">
-        <v>1101</v>
       </c>
       <c r="I306" s="5" t="s">
         <v>124</v>
@@ -12890,25 +12873,25 @@
         <v>306</v>
       </c>
       <c r="B307" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C307" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D307" s="13" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E307" s="13" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F307" s="13" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G307" s="13" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H307" s="13" t="s">
         <v>1102</v>
-      </c>
-      <c r="E307" s="13" t="s">
-        <v>1103</v>
-      </c>
-      <c r="F307" s="13" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G307" s="13" t="s">
-        <v>1105</v>
-      </c>
-      <c r="H307" s="13" t="s">
-        <v>1106</v>
       </c>
       <c r="I307" s="5" t="s">
         <v>7</v>
@@ -12919,25 +12902,25 @@
         <v>307</v>
       </c>
       <c r="B308" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C308" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D308" s="13" t="s">
-        <v>1107</v>
+        <v>1103</v>
       </c>
       <c r="E308" s="13" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="F308" s="13" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G308" s="13" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="H308" s="13" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I308" s="5" t="s">
         <v>123</v>
@@ -12948,25 +12931,25 @@
         <v>308</v>
       </c>
       <c r="B309" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C309" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D309" s="13" t="s">
-        <v>1108</v>
+        <v>1104</v>
       </c>
       <c r="E309" s="13" t="s">
-        <v>1109</v>
+        <v>1105</v>
       </c>
       <c r="F309" s="13" t="s">
-        <v>1110</v>
+        <v>1106</v>
       </c>
       <c r="G309" s="13" t="s">
-        <v>1111</v>
+        <v>1107</v>
       </c>
       <c r="H309" s="13" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="I309" s="5" t="s">
         <v>123</v>
@@ -12977,25 +12960,25 @@
         <v>309</v>
       </c>
       <c r="B310" s="8" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="C310" s="9" t="s">
         <v>1</v>
       </c>
       <c r="D310" s="13" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E310" s="13" t="s">
-        <v>1093</v>
+        <v>1089</v>
       </c>
       <c r="F310" s="13" t="s">
-        <v>1094</v>
+        <v>1090</v>
       </c>
       <c r="G310" s="13" t="s">
-        <v>1095</v>
+        <v>1091</v>
       </c>
       <c r="H310" s="13" t="s">
-        <v>1096</v>
+        <v>1092</v>
       </c>
       <c r="I310" s="5" t="s">
         <v>7</v>
@@ -13006,25 +12989,25 @@
         <v>310</v>
       </c>
       <c r="B311" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C311" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D311" s="30" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E311" s="30" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F311" s="30" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G311" s="30" t="s">
+        <v>1112</v>
+      </c>
+      <c r="H311" s="30" t="s">
         <v>1113</v>
-      </c>
-      <c r="E311" s="30" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F311" s="30" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G311" s="30" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H311" s="30" t="s">
-        <v>1117</v>
       </c>
       <c r="I311" s="14" t="s">
         <v>13</v>
@@ -13035,25 +13018,25 @@
         <v>311</v>
       </c>
       <c r="B312" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C312" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D312" s="30" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E312" s="30" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F312" s="30" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G312" s="30" t="s">
+        <v>1117</v>
+      </c>
+      <c r="H312" s="30" t="s">
         <v>1118</v>
-      </c>
-      <c r="E312" s="30" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F312" s="30" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G312" s="30" t="s">
-        <v>1121</v>
-      </c>
-      <c r="H312" s="30" t="s">
-        <v>1122</v>
       </c>
       <c r="I312" s="14" t="s">
         <v>13</v>
@@ -13064,25 +13047,25 @@
         <v>312</v>
       </c>
       <c r="B313" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C313" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D313" s="30" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E313" s="30" t="s">
+        <v>1120</v>
+      </c>
+      <c r="F313" s="30" t="s">
+        <v>1121</v>
+      </c>
+      <c r="G313" s="30" t="s">
+        <v>1122</v>
+      </c>
+      <c r="H313" s="30" t="s">
         <v>1123</v>
-      </c>
-      <c r="E313" s="30" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F313" s="30" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G313" s="30" t="s">
-        <v>1126</v>
-      </c>
-      <c r="H313" s="30" t="s">
-        <v>1127</v>
       </c>
       <c r="I313" s="14" t="s">
         <v>123</v>
@@ -13093,25 +13076,25 @@
         <v>313</v>
       </c>
       <c r="B314" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C314" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D314" s="30" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E314" s="30" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F314" s="30" t="s">
+        <v>1126</v>
+      </c>
+      <c r="G314" s="30" t="s">
+        <v>1127</v>
+      </c>
+      <c r="H314" s="30" t="s">
         <v>1128</v>
-      </c>
-      <c r="E314" s="30" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F314" s="30" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G314" s="30" t="s">
-        <v>1131</v>
-      </c>
-      <c r="H314" s="30" t="s">
-        <v>1132</v>
       </c>
       <c r="I314" s="14" t="s">
         <v>124</v>
@@ -13122,25 +13105,25 @@
         <v>314</v>
       </c>
       <c r="B315" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C315" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D315" s="30" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E315" s="30" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F315" s="30" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G315" s="30" t="s">
+        <v>1132</v>
+      </c>
+      <c r="H315" s="30" t="s">
         <v>1133</v>
-      </c>
-      <c r="E315" s="30" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F315" s="30" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G315" s="30" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H315" s="30" t="s">
-        <v>1137</v>
       </c>
       <c r="I315" s="14" t="s">
         <v>13</v>
@@ -13151,25 +13134,25 @@
         <v>315</v>
       </c>
       <c r="B316" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C316" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D316" s="30" t="s">
+        <v>1134</v>
+      </c>
+      <c r="E316" s="30" t="s">
+        <v>1135</v>
+      </c>
+      <c r="F316" s="30" t="s">
+        <v>1136</v>
+      </c>
+      <c r="G316" s="30" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H316" s="30" t="s">
         <v>1138</v>
-      </c>
-      <c r="E316" s="30" t="s">
-        <v>1139</v>
-      </c>
-      <c r="F316" s="30" t="s">
-        <v>1140</v>
-      </c>
-      <c r="G316" s="30" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H316" s="30" t="s">
-        <v>1142</v>
       </c>
       <c r="I316" s="14" t="s">
         <v>7</v>
@@ -13180,25 +13163,25 @@
         <v>316</v>
       </c>
       <c r="B317" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C317" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D317" s="30" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E317" s="30" t="s">
+        <v>1140</v>
+      </c>
+      <c r="F317" s="30" t="s">
+        <v>1141</v>
+      </c>
+      <c r="G317" s="30" t="s">
+        <v>1142</v>
+      </c>
+      <c r="H317" s="30" t="s">
         <v>1143</v>
-      </c>
-      <c r="E317" s="30" t="s">
-        <v>1144</v>
-      </c>
-      <c r="F317" s="30" t="s">
-        <v>1145</v>
-      </c>
-      <c r="G317" s="30" t="s">
-        <v>1146</v>
-      </c>
-      <c r="H317" s="30" t="s">
-        <v>1147</v>
       </c>
       <c r="I317" s="14" t="s">
         <v>123</v>
@@ -13209,25 +13192,25 @@
         <v>317</v>
       </c>
       <c r="B318" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C318" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D318" s="30" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E318" s="30" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F318" s="30" t="s">
+        <v>1146</v>
+      </c>
+      <c r="G318" s="30" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H318" s="30" t="s">
         <v>1148</v>
-      </c>
-      <c r="E318" s="30" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F318" s="30" t="s">
-        <v>1150</v>
-      </c>
-      <c r="G318" s="30" t="s">
-        <v>1151</v>
-      </c>
-      <c r="H318" s="30" t="s">
-        <v>1152</v>
       </c>
       <c r="I318" s="14" t="s">
         <v>124</v>
@@ -13238,25 +13221,25 @@
         <v>318</v>
       </c>
       <c r="B319" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C319" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D319" s="30" t="s">
+        <v>1149</v>
+      </c>
+      <c r="E319" s="30" t="s">
+        <v>1150</v>
+      </c>
+      <c r="F319" s="30" t="s">
+        <v>1151</v>
+      </c>
+      <c r="G319" s="30" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H319" s="30" t="s">
         <v>1153</v>
-      </c>
-      <c r="E319" s="30" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F319" s="30" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G319" s="30" t="s">
-        <v>1156</v>
-      </c>
-      <c r="H319" s="30" t="s">
-        <v>1157</v>
       </c>
       <c r="I319" s="14" t="s">
         <v>13</v>
@@ -13267,175 +13250,175 @@
         <v>319</v>
       </c>
       <c r="B320" s="15" t="s">
-        <v>1112</v>
+        <v>1108</v>
       </c>
       <c r="C320" s="29" t="s">
         <v>76</v>
       </c>
       <c r="D320" s="30" t="s">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="E320" s="30" t="s">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="F320" s="30" t="s">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="G320" s="30" t="s">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="H320" s="30" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="I320" s="14" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="321" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A321" s="8">
         <v>327</v>
       </c>
       <c r="B321" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C321" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D321" s="13" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="E321" s="13"/>
       <c r="F321" s="13"/>
       <c r="G321" s="13"/>
       <c r="H321" s="13"/>
-      <c r="I321" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I321" s="1" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="322" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A322" s="8">
         <v>328</v>
       </c>
       <c r="B322" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C322" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D322" s="13" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="E322" s="13"/>
       <c r="F322" s="13"/>
       <c r="G322" s="13"/>
       <c r="H322" s="13"/>
-      <c r="I322" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="323" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I322" s="1" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="323" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A323" s="8">
         <v>329</v>
       </c>
       <c r="B323" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C323" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D323" s="13" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="E323" s="13"/>
       <c r="F323" s="13"/>
       <c r="G323" s="13"/>
       <c r="H323" s="13"/>
-      <c r="I323" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="324" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I323" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="324" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A324" s="8">
         <v>330</v>
       </c>
       <c r="B324" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C324" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D324" s="13" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
       <c r="E324" s="13"/>
       <c r="F324" s="13"/>
       <c r="G324" s="13"/>
       <c r="H324" s="13"/>
-      <c r="I324" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I324" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="325" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A325" s="8">
         <v>331</v>
       </c>
       <c r="B325" s="8" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="C325" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D325" s="13" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="E325" s="13"/>
       <c r="F325" s="13"/>
       <c r="G325" s="13"/>
       <c r="H325" s="13"/>
-      <c r="I325" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I325" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="326" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A326" s="8">
         <v>333</v>
       </c>
       <c r="B326" s="8" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C326" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D326" s="13" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="E326" s="13"/>
       <c r="F326" s="13"/>
       <c r="G326" s="13"/>
       <c r="H326" s="13"/>
-      <c r="I326" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="327" spans="1:9" ht="18" x14ac:dyDescent="0.25">
+      <c r="I326" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="327" spans="1:9" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A327" s="8">
         <v>336</v>
       </c>
       <c r="B327" s="8" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="C327" s="9" t="s">
         <v>65</v>
       </c>
       <c r="D327" s="13" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="E327" s="13"/>
       <c r="F327" s="13"/>
       <c r="G327" s="13"/>
       <c r="H327" s="13"/>
-      <c r="I327" s="1">
-        <v>1</v>
+      <c r="I327" s="1" t="s">
+        <v>1161</v>
       </c>
     </row>
   </sheetData>
